--- a/Syriatel Cash Inventory.xlsx
+++ b/Syriatel Cash Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Melad Ibrahim\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF790673-CD2A-4676-9DB9-40049A683AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC98C4DC-2506-4BC6-A363-CD8DB89F9296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="96" yWindow="6120" windowWidth="23040" windowHeight="6216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10649,7 +10649,7 @@
       <c r="G495" s="3">
         <v>5400</v>
       </c>
-      <c r="H495" s="8" t="s">
+      <c r="H495" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -10671,7 +10671,7 @@
       <c r="G496" s="3">
         <v>998</v>
       </c>
-      <c r="H496" s="8" t="s">
+      <c r="H496" s="10" t="s">
         <v>214</v>
       </c>
     </row>
@@ -10803,7 +10803,7 @@
       <c r="G503" s="3">
         <v>84</v>
       </c>
-      <c r="H503" s="8" t="s">
+      <c r="H503" s="10" t="s">
         <v>392</v>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       <c r="C513" s="3">
         <v>500</v>
       </c>
-      <c r="D513" s="8" t="s">
+      <c r="D513" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E513" s="3"/>
@@ -10975,7 +10975,7 @@
       <c r="C514" s="3">
         <v>500</v>
       </c>
-      <c r="D514" s="8" t="s">
+      <c r="D514" s="10" t="s">
         <v>42</v>
       </c>
       <c r="E514" s="3"/>
@@ -10991,7 +10991,7 @@
       <c r="C515" s="3">
         <v>1000</v>
       </c>
-      <c r="D515" s="8" t="s">
+      <c r="D515" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E515" s="3"/>
@@ -11007,7 +11007,7 @@
       <c r="C516" s="3">
         <v>1000</v>
       </c>
-      <c r="D516" s="8" t="s">
+      <c r="D516" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E516" s="3"/>
@@ -11023,7 +11023,7 @@
       <c r="C517" s="3">
         <v>2000</v>
       </c>
-      <c r="D517" s="8" t="s">
+      <c r="D517" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E517" s="3"/>
@@ -11039,7 +11039,7 @@
       <c r="C518" s="3">
         <v>1000</v>
       </c>
-      <c r="D518" s="8">
+      <c r="D518" s="10">
         <v>741</v>
       </c>
       <c r="E518" s="3"/>
@@ -11055,7 +11055,7 @@
       <c r="C519" s="3">
         <v>500</v>
       </c>
-      <c r="D519" s="8">
+      <c r="D519" s="10">
         <v>741</v>
       </c>
       <c r="E519" s="3"/>
@@ -11071,7 +11071,7 @@
       <c r="C520" s="3">
         <v>500</v>
       </c>
-      <c r="D520" s="8">
+      <c r="D520" s="10">
         <v>741</v>
       </c>
       <c r="E520" s="3"/>
@@ -11087,7 +11087,7 @@
       <c r="C521" s="3">
         <v>1000</v>
       </c>
-      <c r="D521" s="8">
+      <c r="D521" s="10">
         <v>741</v>
       </c>
       <c r="E521" s="3"/>

--- a/Syriatel Cash Inventory.xlsx
+++ b/Syriatel Cash Inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Melad Ibrahim\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC98C4DC-2506-4BC6-A363-CD8DB89F9296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE6FC50-7CBD-4185-9A34-A61A71EA5D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="96" yWindow="6120" windowWidth="23040" windowHeight="6216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="493">
   <si>
     <t>التحويلات الواردة</t>
   </si>
@@ -1315,6 +1315,240 @@
   </si>
   <si>
     <t>8 01:11</t>
+  </si>
+  <si>
+    <t>8 22:35</t>
+  </si>
+  <si>
+    <t>331</t>
+  </si>
+  <si>
+    <t>8 22:40</t>
+  </si>
+  <si>
+    <t>11 19:37</t>
+  </si>
+  <si>
+    <t>12 23:24</t>
+  </si>
+  <si>
+    <t>14 22:13</t>
+  </si>
+  <si>
+    <t>19 23:43</t>
+  </si>
+  <si>
+    <t>869</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>8 22:15</t>
+  </si>
+  <si>
+    <t>8 22:18</t>
+  </si>
+  <si>
+    <t>8 22:19</t>
+  </si>
+  <si>
+    <t>437</t>
+  </si>
+  <si>
+    <t>16 23:13</t>
+  </si>
+  <si>
+    <t>18 16:09</t>
+  </si>
+  <si>
+    <t>622</t>
+  </si>
+  <si>
+    <t>12 23:25</t>
+  </si>
+  <si>
+    <t>9 16:30</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>9 21:58</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>9 22:05</t>
+  </si>
+  <si>
+    <t>12 00:36</t>
+  </si>
+  <si>
+    <t>13 17:20</t>
+  </si>
+  <si>
+    <t>16 01:10</t>
+  </si>
+  <si>
+    <t>16 22:39</t>
+  </si>
+  <si>
+    <t>18 22:19</t>
+  </si>
+  <si>
+    <t>8 22:45</t>
+  </si>
+  <si>
+    <t>8 23:04</t>
+  </si>
+  <si>
+    <t>9 00:52</t>
+  </si>
+  <si>
+    <t>9 01:06</t>
+  </si>
+  <si>
+    <t>12 12:19</t>
+  </si>
+  <si>
+    <t>13 14:44</t>
+  </si>
+  <si>
+    <t>13 23:04</t>
+  </si>
+  <si>
+    <t>13 23:23</t>
+  </si>
+  <si>
+    <t>14 20:09</t>
+  </si>
+  <si>
+    <t>14 22:15</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>14 23:30</t>
+  </si>
+  <si>
+    <t>14 23:37</t>
+  </si>
+  <si>
+    <t>16 00:16</t>
+  </si>
+  <si>
+    <t>16 01:53</t>
+  </si>
+  <si>
+    <t>16 18:15</t>
+  </si>
+  <si>
+    <t>16 21:39</t>
+  </si>
+  <si>
+    <t>16 22:35</t>
+  </si>
+  <si>
+    <t>16 23:07</t>
+  </si>
+  <si>
+    <t>18 12:34</t>
+  </si>
+  <si>
+    <t>18 19:29</t>
+  </si>
+  <si>
+    <t>19 23:48</t>
+  </si>
+  <si>
+    <t>19 23:50</t>
+  </si>
+  <si>
+    <t>9 01:16</t>
+  </si>
+  <si>
+    <t>9 22:06</t>
+  </si>
+  <si>
+    <t>`250</t>
+  </si>
+  <si>
+    <t>10 00:29</t>
+  </si>
+  <si>
+    <t>10 00:46</t>
+  </si>
+  <si>
+    <t>10 01:01</t>
+  </si>
+  <si>
+    <t>10 01:16</t>
+  </si>
+  <si>
+    <t>10 23:30</t>
+  </si>
+  <si>
+    <t>10 23:47</t>
+  </si>
+  <si>
+    <t>2753</t>
+  </si>
+  <si>
+    <t>10 23:48</t>
+  </si>
+  <si>
+    <t>11 22:52</t>
+  </si>
+  <si>
+    <t>11 23:46</t>
+  </si>
+  <si>
+    <t>12 00:22</t>
+  </si>
+  <si>
+    <t>12 17:34</t>
+  </si>
+  <si>
+    <t>12 18:08</t>
+  </si>
+  <si>
+    <t>12 21:08</t>
+  </si>
+  <si>
+    <t>12 22:47</t>
+  </si>
+  <si>
+    <t>16 23:14</t>
+  </si>
+  <si>
+    <t>16 23:15</t>
+  </si>
+  <si>
+    <t>16 23:46</t>
+  </si>
+  <si>
+    <t>17 01:04</t>
+  </si>
+  <si>
+    <t>17 01:08</t>
+  </si>
+  <si>
+    <t>17 13:40</t>
+  </si>
+  <si>
+    <t>329</t>
+  </si>
+  <si>
+    <t>17 20:14</t>
+  </si>
+  <si>
+    <t>17 20:40</t>
+  </si>
+  <si>
+    <t>17 20:59</t>
   </si>
 </sst>
 </file>
@@ -2373,7 +2607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J556"/>
+  <dimension ref="A1:J600"/>
   <sheetFormatPr defaultColWidth="17.69921875" defaultRowHeight="19.2" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.69921875" style="2" customWidth="1"/>
@@ -10693,7 +10927,7 @@
       <c r="G497" s="3">
         <v>4795</v>
       </c>
-      <c r="H497" s="8" t="s">
+      <c r="H497" s="10" t="s">
         <v>361</v>
       </c>
     </row>
@@ -10731,9 +10965,15 @@
         <v>16</v>
       </c>
       <c r="E499" s="3"/>
-      <c r="F499" s="8"/>
-      <c r="G499" s="3"/>
-      <c r="H499" s="8"/>
+      <c r="F499" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="G499" s="3">
+        <v>5400</v>
+      </c>
+      <c r="H499" s="8" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="500" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="3"/>
@@ -10747,9 +10987,15 @@
         <v>87</v>
       </c>
       <c r="E500" s="3"/>
-      <c r="F500" s="8"/>
-      <c r="G500" s="3"/>
-      <c r="H500" s="8"/>
+      <c r="F500" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="G500" s="3">
+        <v>5378</v>
+      </c>
+      <c r="H500" s="8" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="501" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="3"/>
@@ -10763,9 +11009,15 @@
         <v>42</v>
       </c>
       <c r="E501" s="3"/>
-      <c r="F501" s="8"/>
-      <c r="G501" s="3"/>
-      <c r="H501" s="8"/>
+      <c r="F501" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="G501" s="3">
+        <v>22</v>
+      </c>
+      <c r="H501" s="8" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="502" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="3"/>
@@ -10779,11 +11031,15 @@
         <v>371</v>
       </c>
       <c r="E502" s="3"/>
-      <c r="F502" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G502" s="3"/>
-      <c r="H502" s="8"/>
+      <c r="F502" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="G502" s="3">
+        <v>400</v>
+      </c>
+      <c r="H502" s="8" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="503" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="3"/>
@@ -10798,13 +11054,13 @@
       </c>
       <c r="E503" s="3"/>
       <c r="F503" s="8" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="G503" s="3">
-        <v>84</v>
-      </c>
-      <c r="H503" s="10" t="s">
-        <v>392</v>
+        <v>600</v>
+      </c>
+      <c r="H503" s="8" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="504" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -10819,9 +11075,15 @@
         <v>16</v>
       </c>
       <c r="E504" s="3"/>
-      <c r="F504" s="8"/>
-      <c r="G504" s="3"/>
-      <c r="H504" s="8"/>
+      <c r="F504" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="G504" s="3">
+        <v>460</v>
+      </c>
+      <c r="H504" s="8" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="505" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="3"/>
@@ -10835,9 +11097,15 @@
         <v>16</v>
       </c>
       <c r="E505" s="3"/>
-      <c r="F505" s="8"/>
-      <c r="G505" s="3"/>
-      <c r="H505" s="8"/>
+      <c r="F505" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="G505" s="3">
+        <v>5298</v>
+      </c>
+      <c r="H505" s="8" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="506" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="3"/>
@@ -10851,9 +11119,15 @@
         <v>16</v>
       </c>
       <c r="E506" s="3"/>
-      <c r="F506" s="8"/>
-      <c r="G506" s="3"/>
-      <c r="H506" s="8"/>
+      <c r="F506" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="G506" s="3">
+        <v>5360</v>
+      </c>
+      <c r="H506" s="8" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="507" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="3"/>
@@ -10867,9 +11141,15 @@
         <v>87</v>
       </c>
       <c r="E507" s="3"/>
-      <c r="F507" s="8"/>
-      <c r="G507" s="3"/>
-      <c r="H507" s="8"/>
+      <c r="F507" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="G507" s="3">
+        <v>5400</v>
+      </c>
+      <c r="H507" s="8" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="508" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="3"/>
@@ -10883,9 +11163,15 @@
         <v>16</v>
       </c>
       <c r="E508" s="3"/>
-      <c r="F508" s="8"/>
-      <c r="G508" s="3"/>
-      <c r="H508" s="8"/>
+      <c r="F508" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="G508" s="3">
+        <v>11584</v>
+      </c>
+      <c r="H508" s="8" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="509" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="3"/>
@@ -10899,9 +11185,15 @@
         <v>16</v>
       </c>
       <c r="E509" s="3"/>
-      <c r="F509" s="8"/>
-      <c r="G509" s="3"/>
-      <c r="H509" s="8"/>
+      <c r="F509" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="G509" s="3">
+        <v>2216</v>
+      </c>
+      <c r="H509" s="8" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="510" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="3"/>
@@ -11103,7 +11395,7 @@
       <c r="C522" s="3">
         <v>500</v>
       </c>
-      <c r="D522" s="8">
+      <c r="D522" s="10">
         <v>428</v>
       </c>
       <c r="E522" s="3"/>
@@ -11119,7 +11411,7 @@
       <c r="C523" s="3">
         <v>500</v>
       </c>
-      <c r="D523" s="8">
+      <c r="D523" s="10">
         <v>741</v>
       </c>
       <c r="E523" s="3"/>
@@ -11135,7 +11427,7 @@
       <c r="C524" s="3">
         <v>1000</v>
       </c>
-      <c r="D524" s="8">
+      <c r="D524" s="10">
         <v>741</v>
       </c>
       <c r="E524" s="3"/>
@@ -11171,115 +11463,243 @@
         <v>741</v>
       </c>
       <c r="E526" s="3"/>
-      <c r="F526" s="8"/>
+      <c r="F526" s="8" t="s">
+        <v>3</v>
+      </c>
       <c r="G526" s="3"/>
       <c r="H526" s="8"/>
     </row>
     <row r="527" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="3"/>
-      <c r="B527" s="8"/>
-      <c r="C527" s="3"/>
-      <c r="D527" s="8"/>
+      <c r="B527" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="C527" s="3">
+        <v>250</v>
+      </c>
+      <c r="D527" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E527" s="3"/>
-      <c r="F527" s="8"/>
-      <c r="G527" s="3"/>
-      <c r="H527" s="8"/>
+      <c r="F527" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="G527" s="3">
+        <v>84</v>
+      </c>
+      <c r="H527" s="10" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="528" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="3"/>
-      <c r="B528" s="8"/>
-      <c r="C528" s="3"/>
-      <c r="D528" s="8"/>
+      <c r="B528" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="C528" s="3">
+        <v>500</v>
+      </c>
+      <c r="D528" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E528" s="3"/>
-      <c r="F528" s="8"/>
-      <c r="G528" s="3"/>
-      <c r="H528" s="8"/>
+      <c r="F528" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="G528" s="3">
+        <v>208</v>
+      </c>
+      <c r="H528" s="8" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="529" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="3"/>
-      <c r="B529" s="8"/>
-      <c r="C529" s="3"/>
-      <c r="D529" s="8"/>
+      <c r="B529" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="C529" s="3">
+        <v>500</v>
+      </c>
+      <c r="D529" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E529" s="3"/>
-      <c r="F529" s="8"/>
-      <c r="G529" s="3"/>
-      <c r="H529" s="8"/>
+      <c r="F529" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G529" s="3">
+        <v>45</v>
+      </c>
+      <c r="H529" s="8" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="530" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="3"/>
-      <c r="B530" s="8"/>
-      <c r="C530" s="3"/>
-      <c r="D530" s="8"/>
+      <c r="B530" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="C530" s="3">
+        <v>500</v>
+      </c>
+      <c r="D530" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E530" s="3"/>
-      <c r="F530" s="8"/>
-      <c r="G530" s="3"/>
-      <c r="H530" s="8"/>
+      <c r="F530" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="G530" s="3">
+        <v>312</v>
+      </c>
+      <c r="H530" s="8" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="531" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="3"/>
-      <c r="B531" s="8"/>
-      <c r="C531" s="3"/>
-      <c r="D531" s="8"/>
+      <c r="B531" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="C531" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D531" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E531" s="3"/>
-      <c r="F531" s="8"/>
-      <c r="G531" s="3"/>
-      <c r="H531" s="8"/>
+      <c r="F531" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="G531" s="3">
+        <v>40</v>
+      </c>
+      <c r="H531" s="8" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="532" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="3"/>
-      <c r="B532" s="8"/>
-      <c r="C532" s="3"/>
-      <c r="D532" s="8"/>
+      <c r="B532" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="C532" s="3">
+        <v>500</v>
+      </c>
+      <c r="D532" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="E532" s="3"/>
-      <c r="F532" s="8"/>
-      <c r="G532" s="3"/>
-      <c r="H532" s="8"/>
+      <c r="F532" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="G532" s="3">
+        <v>208</v>
+      </c>
+      <c r="H532" s="8" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="533" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="3"/>
-      <c r="B533" s="8"/>
-      <c r="C533" s="3"/>
-      <c r="D533" s="8"/>
+      <c r="B533" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="C533" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D533" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E533" s="3"/>
-      <c r="F533" s="8"/>
-      <c r="G533" s="3"/>
-      <c r="H533" s="8"/>
+      <c r="F533" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="G533" s="3">
+        <v>80</v>
+      </c>
+      <c r="H533" s="8" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="534" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="3"/>
-      <c r="B534" s="8"/>
-      <c r="C534" s="3"/>
-      <c r="D534" s="8"/>
+      <c r="B534" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="C534" s="3">
+        <v>500</v>
+      </c>
+      <c r="D534" s="8" t="s">
+        <v>388</v>
+      </c>
       <c r="E534" s="3"/>
-      <c r="F534" s="8"/>
-      <c r="G534" s="3"/>
-      <c r="H534" s="8"/>
+      <c r="F534" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="G534" s="3">
+        <v>80</v>
+      </c>
+      <c r="H534" s="8" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="535" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="3"/>
-      <c r="B535" s="8"/>
-      <c r="C535" s="3"/>
-      <c r="D535" s="8"/>
+      <c r="B535" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="C535" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D535" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E535" s="3"/>
-      <c r="F535" s="8"/>
-      <c r="G535" s="3"/>
-      <c r="H535" s="8"/>
+      <c r="F535" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="G535" s="3">
+        <v>230</v>
+      </c>
+      <c r="H535" s="8" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="536" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="3"/>
-      <c r="B536" s="8"/>
-      <c r="C536" s="3"/>
-      <c r="D536" s="8"/>
+      <c r="B536" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="C536" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D536" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E536" s="3"/>
-      <c r="F536" s="8"/>
-      <c r="G536" s="3"/>
-      <c r="H536" s="8"/>
+      <c r="F536" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="G536" s="3">
+        <v>80</v>
+      </c>
+      <c r="H536" s="8" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="537" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="3"/>
-      <c r="B537" s="8"/>
-      <c r="C537" s="3"/>
-      <c r="D537" s="8"/>
+      <c r="B537" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="C537" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D537" s="8" t="s">
+        <v>388</v>
+      </c>
       <c r="E537" s="3"/>
       <c r="F537" s="8"/>
       <c r="G537" s="3"/>
@@ -11287,9 +11707,15 @@
     </row>
     <row r="538" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="3"/>
-      <c r="B538" s="8"/>
-      <c r="C538" s="3"/>
-      <c r="D538" s="8"/>
+      <c r="B538" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="C538" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D538" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E538" s="3"/>
       <c r="F538" s="8"/>
       <c r="G538" s="3"/>
@@ -11297,9 +11723,15 @@
     </row>
     <row r="539" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="3"/>
-      <c r="B539" s="8"/>
-      <c r="C539" s="3"/>
-      <c r="D539" s="8"/>
+      <c r="B539" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="C539" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D539" s="8" t="s">
+        <v>474</v>
+      </c>
       <c r="E539" s="3"/>
       <c r="F539" s="8"/>
       <c r="G539" s="3"/>
@@ -11307,29 +11739,55 @@
     </row>
     <row r="540" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="3"/>
-      <c r="B540" s="8"/>
-      <c r="C540" s="3"/>
-      <c r="D540" s="8"/>
+      <c r="B540" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="C540" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D540" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E540" s="3"/>
-      <c r="F540" s="8"/>
+      <c r="F540" s="8" t="s">
+        <v>2</v>
+      </c>
       <c r="G540" s="3"/>
       <c r="H540" s="8"/>
     </row>
     <row r="541" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="3"/>
-      <c r="B541" s="8"/>
-      <c r="C541" s="3"/>
-      <c r="D541" s="8"/>
+      <c r="B541" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="C541" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D541" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E541" s="3"/>
-      <c r="F541" s="8"/>
-      <c r="G541" s="3"/>
-      <c r="H541" s="8"/>
+      <c r="F541" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="G541" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H541" s="8" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="542" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="3"/>
-      <c r="B542" s="8"/>
-      <c r="C542" s="3"/>
-      <c r="D542" s="8"/>
+      <c r="B542" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="C542" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D542" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E542" s="3"/>
       <c r="F542" s="8"/>
       <c r="G542" s="3"/>
@@ -11337,9 +11795,15 @@
     </row>
     <row r="543" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="3"/>
-      <c r="B543" s="8"/>
-      <c r="C543" s="3"/>
-      <c r="D543" s="8"/>
+      <c r="B543" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="C543" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D543" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="E543" s="3"/>
       <c r="F543" s="8"/>
       <c r="G543" s="3"/>
@@ -11347,9 +11811,15 @@
     </row>
     <row r="544" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="3"/>
-      <c r="B544" s="8"/>
-      <c r="C544" s="3"/>
-      <c r="D544" s="8"/>
+      <c r="B544" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="C544" s="3">
+        <v>480</v>
+      </c>
+      <c r="D544" s="8" t="s">
+        <v>87</v>
+      </c>
       <c r="E544" s="3"/>
       <c r="F544" s="8"/>
       <c r="G544" s="3"/>
@@ -11357,9 +11827,15 @@
     </row>
     <row r="545" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="3"/>
-      <c r="B545" s="8"/>
-      <c r="C545" s="3"/>
-      <c r="D545" s="8"/>
+      <c r="B545" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="C545" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D545" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E545" s="3"/>
       <c r="F545" s="8"/>
       <c r="G545" s="3"/>
@@ -11367,9 +11843,15 @@
     </row>
     <row r="546" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="3"/>
-      <c r="B546" s="8"/>
-      <c r="C546" s="3"/>
-      <c r="D546" s="8"/>
+      <c r="B546" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="C546" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D546" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E546" s="3"/>
       <c r="F546" s="8"/>
       <c r="G546" s="3"/>
@@ -11377,9 +11859,15 @@
     </row>
     <row r="547" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="3"/>
-      <c r="B547" s="8"/>
-      <c r="C547" s="3"/>
-      <c r="D547" s="8"/>
+      <c r="B547" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="C547" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D547" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E547" s="3"/>
       <c r="F547" s="8"/>
       <c r="G547" s="3"/>
@@ -11387,9 +11875,15 @@
     </row>
     <row r="548" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="3"/>
-      <c r="B548" s="8"/>
-      <c r="C548" s="3"/>
-      <c r="D548" s="8"/>
+      <c r="B548" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="C548" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D548" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E548" s="3"/>
       <c r="F548" s="8"/>
       <c r="G548" s="3"/>
@@ -11397,9 +11891,15 @@
     </row>
     <row r="549" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="3"/>
-      <c r="B549" s="8"/>
-      <c r="C549" s="3"/>
-      <c r="D549" s="8"/>
+      <c r="B549" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="C549" s="3">
+        <v>500</v>
+      </c>
+      <c r="D549" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E549" s="3"/>
       <c r="F549" s="8"/>
       <c r="G549" s="3"/>
@@ -11407,9 +11907,15 @@
     </row>
     <row r="550" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="3"/>
-      <c r="B550" s="8"/>
-      <c r="C550" s="3"/>
-      <c r="D550" s="8"/>
+      <c r="B550" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="C550" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D550" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E550" s="3"/>
       <c r="F550" s="8"/>
       <c r="G550" s="3"/>
@@ -11417,9 +11923,15 @@
     </row>
     <row r="551" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="3"/>
-      <c r="B551" s="8"/>
-      <c r="C551" s="3"/>
-      <c r="D551" s="8"/>
+      <c r="B551" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="C551" s="3">
+        <v>2000</v>
+      </c>
+      <c r="D551" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E551" s="3"/>
       <c r="F551" s="8"/>
       <c r="G551" s="3"/>
@@ -11427,9 +11939,15 @@
     </row>
     <row r="552" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="3"/>
-      <c r="B552" s="8"/>
-      <c r="C552" s="3"/>
-      <c r="D552" s="8"/>
+      <c r="B552" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="C552" s="3">
+        <v>480</v>
+      </c>
+      <c r="D552" s="8" t="s">
+        <v>87</v>
+      </c>
       <c r="E552" s="3"/>
       <c r="F552" s="8"/>
       <c r="G552" s="3"/>
@@ -11437,9 +11955,15 @@
     </row>
     <row r="553" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="3"/>
-      <c r="B553" s="8"/>
-      <c r="C553" s="3"/>
-      <c r="D553" s="8"/>
+      <c r="B553" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="C553" s="3">
+        <v>970</v>
+      </c>
+      <c r="D553" s="8" t="s">
+        <v>452</v>
+      </c>
       <c r="E553" s="3"/>
       <c r="F553" s="8"/>
       <c r="G553" s="3"/>
@@ -11447,9 +11971,15 @@
     </row>
     <row r="554" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="3"/>
-      <c r="B554" s="8"/>
-      <c r="C554" s="3"/>
-      <c r="D554" s="8"/>
+      <c r="B554" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="C554" s="3">
+        <v>500</v>
+      </c>
+      <c r="D554" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E554" s="3"/>
       <c r="F554" s="8"/>
       <c r="G554" s="3"/>
@@ -11457,9 +11987,15 @@
     </row>
     <row r="555" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="3"/>
-      <c r="B555" s="8"/>
-      <c r="C555" s="3"/>
-      <c r="D555" s="8"/>
+      <c r="B555" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="C555" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D555" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E555" s="3"/>
       <c r="F555" s="8"/>
       <c r="G555" s="3"/>
@@ -11467,13 +12003,567 @@
     </row>
     <row r="556" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="3"/>
-      <c r="B556" s="8"/>
-      <c r="C556" s="3"/>
-      <c r="D556" s="8"/>
+      <c r="B556" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="C556" s="3">
+        <v>500</v>
+      </c>
+      <c r="D556" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E556" s="3"/>
       <c r="F556" s="8"/>
       <c r="G556" s="3"/>
       <c r="H556" s="8"/>
+    </row>
+    <row r="557" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A557" s="3"/>
+      <c r="B557" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="C557" s="3">
+        <v>250</v>
+      </c>
+      <c r="D557" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E557" s="3"/>
+      <c r="F557" s="8"/>
+      <c r="G557" s="3"/>
+      <c r="H557" s="8"/>
+    </row>
+    <row r="558" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A558" s="3"/>
+      <c r="B558" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="C558" s="3">
+        <v>480</v>
+      </c>
+      <c r="D558" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="E558" s="3"/>
+      <c r="F558" s="8"/>
+      <c r="G558" s="3"/>
+      <c r="H558" s="8"/>
+    </row>
+    <row r="559" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A559" s="3"/>
+      <c r="B559" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="C559" s="3">
+        <v>200</v>
+      </c>
+      <c r="D559" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="E559" s="3"/>
+      <c r="F559" s="8"/>
+      <c r="G559" s="3"/>
+      <c r="H559" s="8"/>
+    </row>
+    <row r="560" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A560" s="3"/>
+      <c r="B560" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="C560" s="3">
+        <v>500</v>
+      </c>
+      <c r="D560" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E560" s="3"/>
+      <c r="F560" s="8"/>
+      <c r="G560" s="3"/>
+      <c r="H560" s="8"/>
+    </row>
+    <row r="561" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A561" s="3"/>
+      <c r="B561" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C561" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D561" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="E561" s="3"/>
+      <c r="F561" s="8"/>
+      <c r="G561" s="3"/>
+      <c r="H561" s="8"/>
+    </row>
+    <row r="562" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A562" s="3"/>
+      <c r="B562" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="C562" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D562" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="E562" s="3"/>
+      <c r="F562" s="8"/>
+      <c r="G562" s="3"/>
+      <c r="H562" s="8"/>
+    </row>
+    <row r="563" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A563" s="3"/>
+      <c r="B563" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="C563" s="3">
+        <v>500</v>
+      </c>
+      <c r="D563" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E563" s="3"/>
+      <c r="F563" s="8"/>
+      <c r="G563" s="3"/>
+      <c r="H563" s="8"/>
+    </row>
+    <row r="564" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A564" s="3"/>
+      <c r="B564" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="C564" s="3">
+        <v>480</v>
+      </c>
+      <c r="D564" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E564" s="3"/>
+      <c r="F564" s="8"/>
+      <c r="G564" s="3"/>
+      <c r="H564" s="8"/>
+    </row>
+    <row r="565" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A565" s="3"/>
+      <c r="B565" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="C565" s="3">
+        <v>500</v>
+      </c>
+      <c r="D565" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E565" s="3"/>
+      <c r="F565" s="8"/>
+      <c r="G565" s="3"/>
+      <c r="H565" s="8"/>
+    </row>
+    <row r="566" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A566" s="3"/>
+      <c r="B566" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="C566" s="3">
+        <v>700</v>
+      </c>
+      <c r="D566" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="E566" s="3"/>
+      <c r="F566" s="8"/>
+      <c r="G566" s="3"/>
+      <c r="H566" s="8"/>
+    </row>
+    <row r="567" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A567" s="3"/>
+      <c r="B567" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="C567" s="3">
+        <v>500</v>
+      </c>
+      <c r="D567" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="E567" s="3"/>
+      <c r="F567" s="8"/>
+      <c r="G567" s="3"/>
+      <c r="H567" s="8"/>
+    </row>
+    <row r="568" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A568" s="3"/>
+      <c r="B568" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="C568" s="3">
+        <v>480</v>
+      </c>
+      <c r="D568" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="E568" s="3"/>
+      <c r="F568" s="8"/>
+      <c r="G568" s="3"/>
+      <c r="H568" s="8"/>
+    </row>
+    <row r="569" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A569" s="3"/>
+      <c r="B569" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="C569" s="3">
+        <v>480</v>
+      </c>
+      <c r="D569" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E569" s="3"/>
+      <c r="F569" s="8"/>
+      <c r="G569" s="3"/>
+      <c r="H569" s="8"/>
+    </row>
+    <row r="570" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A570" s="3"/>
+      <c r="B570" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="C570" s="3">
+        <v>500</v>
+      </c>
+      <c r="D570" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E570" s="3"/>
+      <c r="F570" s="8"/>
+      <c r="G570" s="3"/>
+      <c r="H570" s="8"/>
+    </row>
+    <row r="571" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A571" s="3"/>
+      <c r="B571" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="C571" s="3">
+        <v>450</v>
+      </c>
+      <c r="D571" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="E571" s="3"/>
+      <c r="F571" s="8"/>
+      <c r="G571" s="3"/>
+      <c r="H571" s="8"/>
+    </row>
+    <row r="572" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A572" s="3"/>
+      <c r="B572" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="C572" s="3">
+        <v>500</v>
+      </c>
+      <c r="D572" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E572" s="3"/>
+      <c r="F572" s="8"/>
+      <c r="G572" s="3"/>
+      <c r="H572" s="8"/>
+    </row>
+    <row r="573" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A573" s="3"/>
+      <c r="B573" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="C573" s="3">
+        <v>480</v>
+      </c>
+      <c r="D573" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="E573" s="3"/>
+      <c r="F573" s="8"/>
+      <c r="G573" s="3"/>
+      <c r="H573" s="8"/>
+    </row>
+    <row r="574" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A574" s="3"/>
+      <c r="B574" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="C574" s="3">
+        <v>500</v>
+      </c>
+      <c r="D574" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E574" s="3"/>
+      <c r="F574" s="8"/>
+      <c r="G574" s="3"/>
+      <c r="H574" s="8"/>
+    </row>
+    <row r="575" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A575" s="3"/>
+      <c r="B575" s="8"/>
+      <c r="C575" s="3"/>
+      <c r="D575" s="8"/>
+      <c r="E575" s="3"/>
+      <c r="F575" s="8"/>
+      <c r="G575" s="3"/>
+      <c r="H575" s="8"/>
+    </row>
+    <row r="576" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A576" s="3"/>
+      <c r="B576" s="8"/>
+      <c r="C576" s="3"/>
+      <c r="D576" s="8"/>
+      <c r="E576" s="3"/>
+      <c r="F576" s="8"/>
+      <c r="G576" s="3"/>
+      <c r="H576" s="8"/>
+    </row>
+    <row r="577" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A577" s="3"/>
+      <c r="B577" s="8"/>
+      <c r="C577" s="3"/>
+      <c r="D577" s="8"/>
+      <c r="E577" s="3"/>
+      <c r="F577" s="8"/>
+      <c r="G577" s="3"/>
+      <c r="H577" s="8"/>
+    </row>
+    <row r="578" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A578" s="3"/>
+      <c r="B578" s="8"/>
+      <c r="C578" s="3"/>
+      <c r="D578" s="8"/>
+      <c r="E578" s="3"/>
+      <c r="F578" s="8"/>
+      <c r="G578" s="3"/>
+      <c r="H578" s="8"/>
+    </row>
+    <row r="579" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A579" s="3"/>
+      <c r="B579" s="8"/>
+      <c r="C579" s="3"/>
+      <c r="D579" s="8"/>
+      <c r="E579" s="3"/>
+      <c r="F579" s="8"/>
+      <c r="G579" s="3"/>
+      <c r="H579" s="8"/>
+    </row>
+    <row r="580" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A580" s="3"/>
+      <c r="B580" s="8"/>
+      <c r="C580" s="3"/>
+      <c r="D580" s="8"/>
+      <c r="E580" s="3"/>
+      <c r="F580" s="8"/>
+      <c r="G580" s="3"/>
+      <c r="H580" s="8"/>
+    </row>
+    <row r="581" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A581" s="3"/>
+      <c r="B581" s="8"/>
+      <c r="C581" s="3"/>
+      <c r="D581" s="8"/>
+      <c r="E581" s="3"/>
+      <c r="F581" s="8"/>
+      <c r="G581" s="3"/>
+      <c r="H581" s="8"/>
+    </row>
+    <row r="582" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A582" s="3"/>
+      <c r="B582" s="8"/>
+      <c r="C582" s="3"/>
+      <c r="D582" s="8"/>
+      <c r="E582" s="3"/>
+      <c r="F582" s="8"/>
+      <c r="G582" s="3"/>
+      <c r="H582" s="8"/>
+    </row>
+    <row r="583" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A583" s="3"/>
+      <c r="B583" s="8"/>
+      <c r="C583" s="3"/>
+      <c r="D583" s="8"/>
+      <c r="E583" s="3"/>
+      <c r="F583" s="8"/>
+      <c r="G583" s="3"/>
+      <c r="H583" s="8"/>
+    </row>
+    <row r="584" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A584" s="3"/>
+      <c r="B584" s="8"/>
+      <c r="C584" s="3"/>
+      <c r="D584" s="8"/>
+      <c r="E584" s="3"/>
+      <c r="F584" s="8"/>
+      <c r="G584" s="3"/>
+      <c r="H584" s="8"/>
+    </row>
+    <row r="585" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A585" s="3"/>
+      <c r="B585" s="8"/>
+      <c r="C585" s="3"/>
+      <c r="D585" s="8"/>
+      <c r="E585" s="3"/>
+      <c r="F585" s="8"/>
+      <c r="G585" s="3"/>
+      <c r="H585" s="8"/>
+    </row>
+    <row r="586" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A586" s="3"/>
+      <c r="B586" s="8"/>
+      <c r="C586" s="3"/>
+      <c r="D586" s="8"/>
+      <c r="E586" s="3"/>
+      <c r="F586" s="8"/>
+      <c r="G586" s="3"/>
+      <c r="H586" s="8"/>
+    </row>
+    <row r="587" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A587" s="3"/>
+      <c r="B587" s="8"/>
+      <c r="C587" s="3"/>
+      <c r="D587" s="8"/>
+      <c r="E587" s="3"/>
+      <c r="F587" s="8"/>
+      <c r="G587" s="3"/>
+      <c r="H587" s="8"/>
+    </row>
+    <row r="588" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A588" s="3"/>
+      <c r="B588" s="8"/>
+      <c r="C588" s="3"/>
+      <c r="D588" s="8"/>
+      <c r="E588" s="3"/>
+      <c r="F588" s="8"/>
+      <c r="G588" s="3"/>
+      <c r="H588" s="8"/>
+    </row>
+    <row r="589" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A589" s="3"/>
+      <c r="B589" s="8"/>
+      <c r="C589" s="3"/>
+      <c r="D589" s="8"/>
+      <c r="E589" s="3"/>
+      <c r="F589" s="8"/>
+      <c r="G589" s="3"/>
+      <c r="H589" s="8"/>
+    </row>
+    <row r="590" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A590" s="3"/>
+      <c r="B590" s="8"/>
+      <c r="C590" s="3"/>
+      <c r="D590" s="8"/>
+      <c r="E590" s="3"/>
+      <c r="F590" s="8"/>
+      <c r="G590" s="3"/>
+      <c r="H590" s="8"/>
+    </row>
+    <row r="591" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A591" s="3"/>
+      <c r="B591" s="8"/>
+      <c r="C591" s="3"/>
+      <c r="D591" s="8"/>
+      <c r="E591" s="3"/>
+      <c r="F591" s="8"/>
+      <c r="G591" s="3"/>
+      <c r="H591" s="8"/>
+    </row>
+    <row r="592" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A592" s="3"/>
+      <c r="B592" s="8"/>
+      <c r="C592" s="3"/>
+      <c r="D592" s="8"/>
+      <c r="E592" s="3"/>
+      <c r="F592" s="8"/>
+      <c r="G592" s="3"/>
+      <c r="H592" s="8"/>
+    </row>
+    <row r="593" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A593" s="3"/>
+      <c r="B593" s="8"/>
+      <c r="C593" s="3"/>
+      <c r="D593" s="8"/>
+      <c r="E593" s="3"/>
+      <c r="F593" s="8"/>
+      <c r="G593" s="3"/>
+      <c r="H593" s="8"/>
+    </row>
+    <row r="594" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A594" s="3"/>
+      <c r="B594" s="8"/>
+      <c r="C594" s="3"/>
+      <c r="D594" s="8"/>
+      <c r="E594" s="3"/>
+      <c r="F594" s="8"/>
+      <c r="G594" s="3"/>
+      <c r="H594" s="8"/>
+    </row>
+    <row r="595" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A595" s="3"/>
+      <c r="B595" s="8"/>
+      <c r="C595" s="3"/>
+      <c r="D595" s="8"/>
+      <c r="E595" s="3"/>
+      <c r="F595" s="8"/>
+      <c r="G595" s="3"/>
+      <c r="H595" s="8"/>
+    </row>
+    <row r="596" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A596" s="3"/>
+      <c r="B596" s="8"/>
+      <c r="C596" s="3"/>
+      <c r="D596" s="8"/>
+      <c r="E596" s="3"/>
+      <c r="F596" s="8"/>
+      <c r="G596" s="3"/>
+      <c r="H596" s="8"/>
+    </row>
+    <row r="597" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A597" s="3"/>
+      <c r="B597" s="8"/>
+      <c r="C597" s="3"/>
+      <c r="D597" s="8"/>
+      <c r="E597" s="3"/>
+      <c r="F597" s="8"/>
+      <c r="G597" s="3"/>
+      <c r="H597" s="8"/>
+    </row>
+    <row r="598" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A598" s="3"/>
+      <c r="B598" s="8"/>
+      <c r="C598" s="3"/>
+      <c r="D598" s="8"/>
+      <c r="E598" s="3"/>
+      <c r="F598" s="8"/>
+      <c r="G598" s="3"/>
+      <c r="H598" s="8"/>
+    </row>
+    <row r="599" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A599" s="3"/>
+      <c r="B599" s="8"/>
+      <c r="C599" s="3"/>
+      <c r="D599" s="8"/>
+      <c r="E599" s="3"/>
+      <c r="F599" s="8"/>
+      <c r="G599" s="3"/>
+      <c r="H599" s="8"/>
+    </row>
+    <row r="600" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A600" s="3"/>
+      <c r="B600" s="8"/>
+      <c r="C600" s="3"/>
+      <c r="D600" s="8"/>
+      <c r="E600" s="3"/>
+      <c r="F600" s="8"/>
+      <c r="G600" s="3"/>
+      <c r="H600" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -11494,7 +12584,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A127:B127 G38:H38 C40:D45 C46:E53 C61:D61 C60:E60 A11:D20 H27:H37 F11:F20 A22:D24 G11:H26 B77:B82 D93:D183 B35:B75 A3:H10 A30:D34 A21:F21 E127 E92:F94 C62:E63 C36:F39 C83:F88 C54:E54 C55:E55 C56:E56 C57:E57 C58:E58 C59:E59 G75:H88 C70:E70 C64:E64 C65:E65 C66:E66 C67:E67 C68:E68 C75:F82 C71:E71 C72:E72 C73:E73 C74:E74 C69:E69 B83:B96 C90:F91 C89:E89 G90:H93 H89 D184:D196 A25:D29 F22:F29 H39:H42 F30:F35 H43:H47 B98:B103 B105:B106 B108 B110:B111 B113:B114 D198:D201 D203:D205 D208 D210:D219 D222:D225 D227:D283 C35:D35 B310:B315 D310:D374 B317:B320 H310:H316 H48:H51 D487:D526 H487:H503" numberStoredAsText="1"/>
+    <ignoredError sqref="A127:B127 G38:H38 C40:D45 C46:E53 C61:D61 C60:E60 A11:D20 H27:H37 F11:F20 A22:D24 G11:H26 B77:B82 D93:D183 B35:B75 A3:H10 A30:D34 A21:F21 E127 E92:F94 C62:E63 C36:F39 C83:F88 C54:E54 C55:E55 C56:E56 C57:E57 C58:E58 C59:E59 G75:H88 C70:E70 C64:E64 C65:E65 C66:E66 C67:E67 C68:E68 C75:F82 C71:E71 C72:E72 C73:E73 C74:E74 C69:E69 B83:B96 C90:F91 C89:E89 G90:H93 H89 D184:D196 A25:D29 F22:F29 H39:H42 F30:F35 H43:H47 B98:B103 B105:B106 B108 B110:B111 B113:B114 D198:D201 D203:D205 D208 D210:D219 D222:D225 D227:D283 C35:D35 B310:B315 D310:D374 B317:B320 H310:H316 H48:H51 D487:D526 H487:H498 H499:H510 H527:H536 H541 D527:D574" numberStoredAsText="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/Syriatel Cash Inventory.xlsx
+++ b/Syriatel Cash Inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Melad Ibrahim\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE6FC50-7CBD-4185-9A34-A61A71EA5D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA900F1-6157-4836-8246-94FF6F7BBBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="96" yWindow="6120" windowWidth="23040" windowHeight="6216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="520">
   <si>
     <t>التحويلات الواردة</t>
   </si>
@@ -1320,9 +1320,6 @@
     <t>8 22:35</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>8 22:40</t>
   </si>
   <si>
@@ -1549,6 +1546,90 @@
   </si>
   <si>
     <t>17 20:59</t>
+  </si>
+  <si>
+    <t>29 10:05</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>28 22:44</t>
+  </si>
+  <si>
+    <t>26 00:57</t>
+  </si>
+  <si>
+    <t>26 18:03</t>
+  </si>
+  <si>
+    <t>26 19:46</t>
+  </si>
+  <si>
+    <t>26 22:13</t>
+  </si>
+  <si>
+    <t>6704</t>
+  </si>
+  <si>
+    <t>27 02:07</t>
+  </si>
+  <si>
+    <t>27 17:15</t>
+  </si>
+  <si>
+    <t>6999</t>
+  </si>
+  <si>
+    <t>28 16:58</t>
+  </si>
+  <si>
+    <t>28 19:36</t>
+  </si>
+  <si>
+    <t>7439</t>
+  </si>
+  <si>
+    <t>28 19:46</t>
+  </si>
+  <si>
+    <t>29 13:19</t>
+  </si>
+  <si>
+    <t>29 16:04</t>
+  </si>
+  <si>
+    <t>29 22:27</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>From 26/9</t>
+  </si>
+  <si>
+    <t>From 1/9</t>
+  </si>
+  <si>
+    <t>From 7/10</t>
+  </si>
+  <si>
+    <t>7 00:06</t>
+  </si>
+  <si>
+    <t>7 00:37</t>
+  </si>
+  <si>
+    <t>7 18:26</t>
+  </si>
+  <si>
+    <t>7 21:15</t>
+  </si>
+  <si>
+    <t>3083</t>
+  </si>
+  <si>
+    <t>7 22:29</t>
   </si>
 </sst>
 </file>
@@ -2607,7 +2688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J600"/>
+  <dimension ref="A1:J693"/>
   <sheetFormatPr defaultColWidth="17.69921875" defaultRowHeight="19.2" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.69921875" style="2" customWidth="1"/>
@@ -10671,13 +10752,17 @@
         <v>1</v>
       </c>
       <c r="C485" s="3"/>
-      <c r="D485" s="8"/>
+      <c r="D485" s="8" t="s">
+        <v>512</v>
+      </c>
       <c r="E485" s="3"/>
       <c r="F485" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G485" s="3"/>
-      <c r="H485" s="8"/>
+      <c r="H485" s="8" t="s">
+        <v>512</v>
+      </c>
     </row>
     <row r="486" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="3"/>
@@ -10949,7 +11034,7 @@
       <c r="G498" s="3">
         <v>5400</v>
       </c>
-      <c r="H498" s="8" t="s">
+      <c r="H498" s="10" t="s">
         <v>177</v>
       </c>
     </row>
@@ -10966,12 +11051,12 @@
       </c>
       <c r="E499" s="3"/>
       <c r="F499" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G499" s="3">
         <v>5400</v>
       </c>
-      <c r="H499" s="8" t="s">
+      <c r="H499" s="10" t="s">
         <v>76</v>
       </c>
     </row>
@@ -10988,12 +11073,12 @@
       </c>
       <c r="E500" s="3"/>
       <c r="F500" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G500" s="3">
         <v>5378</v>
       </c>
-      <c r="H500" s="8" t="s">
+      <c r="H500" s="10" t="s">
         <v>368</v>
       </c>
     </row>
@@ -11010,13 +11095,13 @@
       </c>
       <c r="E501" s="3"/>
       <c r="F501" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G501" s="3">
         <v>22</v>
       </c>
-      <c r="H501" s="8" t="s">
-        <v>427</v>
+      <c r="H501" s="10" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="502" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -11037,8 +11122,8 @@
       <c r="G502" s="3">
         <v>400</v>
       </c>
-      <c r="H502" s="8" t="s">
-        <v>416</v>
+      <c r="H502" s="10" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="503" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -11054,12 +11139,12 @@
       </c>
       <c r="E503" s="3"/>
       <c r="F503" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G503" s="3">
         <v>600</v>
       </c>
-      <c r="H503" s="8" t="s">
+      <c r="H503" s="10" t="s">
         <v>363</v>
       </c>
     </row>
@@ -11076,12 +11161,12 @@
       </c>
       <c r="E504" s="3"/>
       <c r="F504" s="8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G504" s="3">
         <v>460</v>
       </c>
-      <c r="H504" s="8" t="s">
+      <c r="H504" s="10" t="s">
         <v>214</v>
       </c>
     </row>
@@ -11098,7 +11183,7 @@
       </c>
       <c r="E505" s="3"/>
       <c r="F505" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G505" s="3">
         <v>5298</v>
@@ -11120,7 +11205,7 @@
       </c>
       <c r="E506" s="3"/>
       <c r="F506" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G506" s="3">
         <v>5360</v>
@@ -11142,7 +11227,7 @@
       </c>
       <c r="E507" s="3"/>
       <c r="F507" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G507" s="3">
         <v>5400</v>
@@ -11164,13 +11249,13 @@
       </c>
       <c r="E508" s="3"/>
       <c r="F508" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G508" s="3">
         <v>11584</v>
       </c>
       <c r="H508" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="509" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -11186,13 +11271,13 @@
       </c>
       <c r="E509" s="3"/>
       <c r="F509" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G509" s="3">
         <v>2216</v>
       </c>
       <c r="H509" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="510" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -11443,11 +11528,13 @@
       <c r="C525" s="3">
         <v>1000</v>
       </c>
-      <c r="D525" s="8">
+      <c r="D525" s="10">
         <v>741</v>
       </c>
       <c r="E525" s="3"/>
-      <c r="F525" s="8"/>
+      <c r="F525" s="8" t="s">
+        <v>3</v>
+      </c>
       <c r="G525" s="3"/>
       <c r="H525" s="8"/>
     </row>
@@ -11459,91 +11546,95 @@
       <c r="C526" s="3">
         <v>1000</v>
       </c>
-      <c r="D526" s="8">
+      <c r="D526" s="10">
         <v>741</v>
       </c>
       <c r="E526" s="3"/>
       <c r="F526" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G526" s="3"/>
-      <c r="H526" s="8"/>
+        <v>391</v>
+      </c>
+      <c r="G526" s="3">
+        <v>84</v>
+      </c>
+      <c r="H526" s="10" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="527" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="3"/>
       <c r="B527" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C527" s="3">
         <v>250</v>
       </c>
-      <c r="D527" s="8" t="s">
+      <c r="D527" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E527" s="3"/>
       <c r="F527" s="8" t="s">
-        <v>391</v>
+        <v>431</v>
       </c>
       <c r="G527" s="3">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="H527" s="10" t="s">
-        <v>392</v>
+        <v>432</v>
       </c>
     </row>
     <row r="528" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="3"/>
       <c r="B528" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C528" s="3">
         <v>500</v>
       </c>
-      <c r="D528" s="8" t="s">
+      <c r="D528" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E528" s="3"/>
       <c r="F528" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G528" s="3">
-        <v>208</v>
-      </c>
-      <c r="H528" s="8" t="s">
-        <v>433</v>
+        <v>45</v>
+      </c>
+      <c r="H528" s="10" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="529" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="3"/>
       <c r="B529" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C529" s="3">
         <v>500</v>
       </c>
-      <c r="D529" s="8" t="s">
+      <c r="D529" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E529" s="3"/>
       <c r="F529" s="8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G529" s="3">
-        <v>45</v>
-      </c>
-      <c r="H529" s="8" t="s">
-        <v>435</v>
+        <v>312</v>
+      </c>
+      <c r="H529" s="10" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="530" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="3"/>
       <c r="B530" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C530" s="3">
         <v>500</v>
       </c>
-      <c r="D530" s="8" t="s">
+      <c r="D530" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E530" s="3"/>
@@ -11551,21 +11642,21 @@
         <v>436</v>
       </c>
       <c r="G530" s="3">
-        <v>312</v>
-      </c>
-      <c r="H530" s="8" t="s">
-        <v>174</v>
+        <v>40</v>
+      </c>
+      <c r="H530" s="10" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="531" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="3"/>
       <c r="B531" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C531" s="3">
         <v>1000</v>
       </c>
-      <c r="D531" s="8" t="s">
+      <c r="D531" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E531" s="3"/>
@@ -11573,21 +11664,21 @@
         <v>437</v>
       </c>
       <c r="G531" s="3">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="H531" s="8" t="s">
-        <v>392</v>
+        <v>174</v>
       </c>
     </row>
     <row r="532" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="3"/>
       <c r="B532" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C532" s="3">
         <v>500</v>
       </c>
-      <c r="D532" s="8" t="s">
+      <c r="D532" s="10" t="s">
         <v>42</v>
       </c>
       <c r="E532" s="3"/>
@@ -11595,10 +11686,10 @@
         <v>438</v>
       </c>
       <c r="G532" s="3">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="H532" s="8" t="s">
-        <v>174</v>
+        <v>392</v>
       </c>
     </row>
     <row r="533" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -11607,9 +11698,9 @@
         <v>277</v>
       </c>
       <c r="C533" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="D533" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="D533" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E533" s="3"/>
@@ -11626,78 +11717,72 @@
     <row r="534" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="3"/>
       <c r="B534" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C534" s="3">
         <v>500</v>
       </c>
-      <c r="D534" s="8" t="s">
+      <c r="D534" s="10" t="s">
         <v>388</v>
       </c>
       <c r="E534" s="3"/>
       <c r="F534" s="8" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="G534" s="3">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="H534" s="8" t="s">
-        <v>392</v>
+        <v>429</v>
       </c>
     </row>
     <row r="535" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="3"/>
       <c r="B535" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C535" s="3">
         <v>1000</v>
       </c>
-      <c r="D535" s="8" t="s">
+      <c r="D535" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E535" s="3"/>
       <c r="F535" s="8" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="G535" s="3">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="H535" s="8" t="s">
-        <v>430</v>
+        <v>392</v>
       </c>
     </row>
     <row r="536" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="3"/>
       <c r="B536" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C536" s="3">
         <v>1000</v>
       </c>
-      <c r="D536" s="8" t="s">
+      <c r="D536" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E536" s="3"/>
-      <c r="F536" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="G536" s="3">
-        <v>80</v>
-      </c>
-      <c r="H536" s="8" t="s">
-        <v>392</v>
-      </c>
+      <c r="F536" s="8"/>
+      <c r="G536" s="3"/>
+      <c r="H536" s="8"/>
     </row>
     <row r="537" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="3"/>
       <c r="B537" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C537" s="3">
         <v>1000</v>
       </c>
-      <c r="D537" s="8" t="s">
+      <c r="D537" s="10" t="s">
         <v>388</v>
       </c>
       <c r="E537" s="3"/>
@@ -11708,12 +11793,12 @@
     <row r="538" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="3"/>
       <c r="B538" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C538" s="3">
         <v>1000</v>
       </c>
-      <c r="D538" s="8" t="s">
+      <c r="D538" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E538" s="3"/>
@@ -11724,68 +11809,68 @@
     <row r="539" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="3"/>
       <c r="B539" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C539" s="3">
         <v>1000</v>
       </c>
-      <c r="D539" s="8" t="s">
-        <v>474</v>
+      <c r="D539" s="10" t="s">
+        <v>473</v>
       </c>
       <c r="E539" s="3"/>
-      <c r="F539" s="8"/>
+      <c r="F539" s="8" t="s">
+        <v>2</v>
+      </c>
       <c r="G539" s="3"/>
       <c r="H539" s="8"/>
     </row>
     <row r="540" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="3"/>
       <c r="B540" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C540" s="3">
         <v>1000</v>
       </c>
-      <c r="D540" s="8" t="s">
+      <c r="D540" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E540" s="3"/>
       <c r="F540" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G540" s="3"/>
-      <c r="H540" s="8"/>
+        <v>430</v>
+      </c>
+      <c r="G540" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H540" s="8" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="541" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="3"/>
       <c r="B541" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C541" s="3">
         <v>1000</v>
       </c>
-      <c r="D541" s="8" t="s">
+      <c r="D541" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E541" s="3"/>
-      <c r="F541" s="8" t="s">
-        <v>431</v>
-      </c>
-      <c r="G541" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H541" s="8" t="s">
-        <v>172</v>
-      </c>
+      <c r="F541" s="8"/>
+      <c r="G541" s="3"/>
+      <c r="H541" s="8"/>
     </row>
     <row r="542" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="3"/>
       <c r="B542" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C542" s="3">
         <v>1000</v>
       </c>
-      <c r="D542" s="8" t="s">
+      <c r="D542" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E542" s="3"/>
@@ -11796,12 +11881,12 @@
     <row r="543" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="3"/>
       <c r="B543" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C543" s="3">
         <v>1000</v>
       </c>
-      <c r="D543" s="8" t="s">
+      <c r="D543" s="10" t="s">
         <v>42</v>
       </c>
       <c r="E543" s="3"/>
@@ -11812,12 +11897,12 @@
     <row r="544" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="3"/>
       <c r="B544" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C544" s="3">
         <v>480</v>
       </c>
-      <c r="D544" s="8" t="s">
+      <c r="D544" s="10" t="s">
         <v>87</v>
       </c>
       <c r="E544" s="3"/>
@@ -11828,12 +11913,12 @@
     <row r="545" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="3"/>
       <c r="B545" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C545" s="3">
         <v>1000</v>
       </c>
-      <c r="D545" s="8" t="s">
+      <c r="D545" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E545" s="3"/>
@@ -11844,12 +11929,12 @@
     <row r="546" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="3"/>
       <c r="B546" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C546" s="3">
         <v>1000</v>
       </c>
-      <c r="D546" s="8" t="s">
+      <c r="D546" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E546" s="3"/>
@@ -11860,7 +11945,7 @@
     <row r="547" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="3"/>
       <c r="B547" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C547" s="3">
         <v>1000</v>
@@ -11876,7 +11961,7 @@
     <row r="548" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="3"/>
       <c r="B548" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C548" s="3">
         <v>1000</v>
@@ -11892,7 +11977,7 @@
     <row r="549" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="3"/>
       <c r="B549" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C549" s="3">
         <v>500</v>
@@ -11908,7 +11993,7 @@
     <row r="550" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="3"/>
       <c r="B550" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C550" s="3">
         <v>1000</v>
@@ -11924,7 +12009,7 @@
     <row r="551" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="3"/>
       <c r="B551" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C551" s="3">
         <v>2000</v>
@@ -11940,7 +12025,7 @@
     <row r="552" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="3"/>
       <c r="B552" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C552" s="3">
         <v>480</v>
@@ -11956,13 +12041,13 @@
     <row r="553" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="3"/>
       <c r="B553" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C553" s="3">
         <v>970</v>
       </c>
       <c r="D553" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E553" s="3"/>
       <c r="F553" s="8"/>
@@ -11972,7 +12057,7 @@
     <row r="554" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="3"/>
       <c r="B554" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C554" s="3">
         <v>500</v>
@@ -11988,7 +12073,7 @@
     <row r="555" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="3"/>
       <c r="B555" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C555" s="3">
         <v>1000</v>
@@ -12004,7 +12089,7 @@
     <row r="556" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="3"/>
       <c r="B556" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C556" s="3">
         <v>500</v>
@@ -12020,7 +12105,7 @@
     <row r="557" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="3"/>
       <c r="B557" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C557" s="3">
         <v>250</v>
@@ -12036,13 +12121,13 @@
     <row r="558" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="3"/>
       <c r="B558" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C558" s="3">
         <v>480</v>
       </c>
       <c r="D558" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E558" s="3"/>
       <c r="F558" s="8"/>
@@ -12052,7 +12137,7 @@
     <row r="559" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="3"/>
       <c r="B559" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C559" s="3">
         <v>200</v>
@@ -12068,7 +12153,7 @@
     <row r="560" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="3"/>
       <c r="B560" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C560" s="3">
         <v>500</v>
@@ -12084,7 +12169,7 @@
     <row r="561" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="3"/>
       <c r="B561" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C561" s="3">
         <v>1000</v>
@@ -12100,13 +12185,13 @@
     <row r="562" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="3"/>
       <c r="B562" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C562" s="3">
         <v>1000</v>
       </c>
       <c r="D562" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E562" s="3"/>
       <c r="F562" s="8"/>
@@ -12116,7 +12201,7 @@
     <row r="563" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="3"/>
       <c r="B563" s="8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C563" s="3">
         <v>500</v>
@@ -12132,7 +12217,7 @@
     <row r="564" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="3"/>
       <c r="B564" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C564" s="3">
         <v>480</v>
@@ -12148,7 +12233,7 @@
     <row r="565" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="3"/>
       <c r="B565" s="8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C565" s="3">
         <v>500</v>
@@ -12164,7 +12249,7 @@
     <row r="566" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="3"/>
       <c r="B566" s="8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C566" s="3">
         <v>700</v>
@@ -12180,13 +12265,13 @@
     <row r="567" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="3"/>
       <c r="B567" s="8" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C567" s="3">
         <v>500</v>
       </c>
       <c r="D567" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E567" s="3"/>
       <c r="F567" s="8"/>
@@ -12196,13 +12281,13 @@
     <row r="568" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="3"/>
       <c r="B568" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C568" s="3">
         <v>480</v>
       </c>
       <c r="D568" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E568" s="3"/>
       <c r="F568" s="8"/>
@@ -12212,7 +12297,7 @@
     <row r="569" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="3"/>
       <c r="B569" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C569" s="3">
         <v>480</v>
@@ -12228,7 +12313,7 @@
     <row r="570" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="3"/>
       <c r="B570" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C570" s="3">
         <v>500</v>
@@ -12244,13 +12329,13 @@
     <row r="571" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="3"/>
       <c r="B571" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C571" s="3">
         <v>450</v>
       </c>
       <c r="D571" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E571" s="3"/>
       <c r="F571" s="8"/>
@@ -12260,7 +12345,7 @@
     <row r="572" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="3"/>
       <c r="B572" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C572" s="3">
         <v>500</v>
@@ -12276,13 +12361,13 @@
     <row r="573" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="3"/>
       <c r="B573" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C573" s="3">
         <v>480</v>
       </c>
       <c r="D573" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E573" s="3"/>
       <c r="F573" s="8"/>
@@ -12292,7 +12377,7 @@
     <row r="574" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="3"/>
       <c r="B574" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C574" s="3">
         <v>500</v>
@@ -12356,14 +12441,14 @@
       <c r="H579" s="8"/>
     </row>
     <row r="580" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A580" s="3"/>
-      <c r="B580" s="8"/>
-      <c r="C580" s="3"/>
-      <c r="D580" s="8"/>
-      <c r="E580" s="3"/>
-      <c r="F580" s="8"/>
-      <c r="G580" s="3"/>
-      <c r="H580" s="8"/>
+      <c r="A580" s="37"/>
+      <c r="B580" s="37"/>
+      <c r="C580" s="37"/>
+      <c r="D580" s="37"/>
+      <c r="E580" s="37"/>
+      <c r="F580" s="37"/>
+      <c r="G580" s="37"/>
+      <c r="H580" s="37"/>
     </row>
     <row r="581" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="3"/>
@@ -12377,13 +12462,21 @@
     </row>
     <row r="582" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="3"/>
-      <c r="B582" s="8"/>
+      <c r="B582" s="8" t="s">
+        <v>1</v>
+      </c>
       <c r="C582" s="3"/>
-      <c r="D582" s="8"/>
+      <c r="D582" s="8" t="s">
+        <v>511</v>
+      </c>
       <c r="E582" s="3"/>
-      <c r="F582" s="8"/>
+      <c r="F582" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="G582" s="3"/>
-      <c r="H582" s="8"/>
+      <c r="H582" s="8" t="s">
+        <v>511</v>
+      </c>
     </row>
     <row r="583" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="3"/>
@@ -12397,19 +12490,37 @@
     </row>
     <row r="584" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="3"/>
-      <c r="B584" s="8"/>
-      <c r="C584" s="3"/>
-      <c r="D584" s="8"/>
+      <c r="B584" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C584" s="3">
+        <v>500</v>
+      </c>
+      <c r="D584" s="8" t="s">
+        <v>145</v>
+      </c>
       <c r="E584" s="3"/>
-      <c r="F584" s="8"/>
-      <c r="G584" s="3"/>
-      <c r="H584" s="8"/>
+      <c r="F584" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="G584" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H584" s="8" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="585" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="3"/>
-      <c r="B585" s="8"/>
-      <c r="C585" s="3"/>
-      <c r="D585" s="8"/>
+      <c r="B585" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C585" s="3">
+        <v>2000</v>
+      </c>
+      <c r="D585" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="E585" s="3"/>
       <c r="F585" s="8"/>
       <c r="G585" s="3"/>
@@ -12417,9 +12528,15 @@
     </row>
     <row r="586" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="3"/>
-      <c r="B586" s="8"/>
-      <c r="C586" s="3"/>
-      <c r="D586" s="8"/>
+      <c r="B586" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C586" s="3">
+        <v>1950</v>
+      </c>
+      <c r="D586" s="8" t="s">
+        <v>451</v>
+      </c>
       <c r="E586" s="3"/>
       <c r="F586" s="8"/>
       <c r="G586" s="3"/>
@@ -12427,9 +12544,15 @@
     </row>
     <row r="587" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="3"/>
-      <c r="B587" s="8"/>
-      <c r="C587" s="3"/>
-      <c r="D587" s="8"/>
+      <c r="B587" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C587" s="3">
+        <v>280</v>
+      </c>
+      <c r="D587" s="8" t="s">
+        <v>499</v>
+      </c>
       <c r="E587" s="3"/>
       <c r="F587" s="8"/>
       <c r="G587" s="3"/>
@@ -12437,19 +12560,33 @@
     </row>
     <row r="588" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="3"/>
-      <c r="B588" s="8"/>
-      <c r="C588" s="3"/>
-      <c r="D588" s="8"/>
+      <c r="B588" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="C588" s="3">
+        <v>200</v>
+      </c>
+      <c r="D588" s="8" t="s">
+        <v>331</v>
+      </c>
       <c r="E588" s="3"/>
-      <c r="F588" s="8"/>
+      <c r="F588" s="8" t="s">
+        <v>3</v>
+      </c>
       <c r="G588" s="3"/>
       <c r="H588" s="8"/>
     </row>
     <row r="589" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="3"/>
-      <c r="B589" s="8"/>
-      <c r="C589" s="3"/>
-      <c r="D589" s="8"/>
+      <c r="B589" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="C589" s="3">
+        <v>300</v>
+      </c>
+      <c r="D589" s="8" t="s">
+        <v>502</v>
+      </c>
       <c r="E589" s="3"/>
       <c r="F589" s="8"/>
       <c r="G589" s="3"/>
@@ -12457,19 +12594,37 @@
     </row>
     <row r="590" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="3"/>
-      <c r="B590" s="8"/>
-      <c r="C590" s="3"/>
-      <c r="D590" s="8"/>
+      <c r="B590" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="C590" s="3">
+        <v>970</v>
+      </c>
+      <c r="D590" s="8" t="s">
+        <v>451</v>
+      </c>
       <c r="E590" s="3"/>
-      <c r="F590" s="8"/>
-      <c r="G590" s="3"/>
-      <c r="H590" s="8"/>
+      <c r="F590" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="G590" s="3">
+        <v>312</v>
+      </c>
+      <c r="H590" s="8" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="591" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="3"/>
-      <c r="B591" s="8"/>
-      <c r="C591" s="3"/>
-      <c r="D591" s="8"/>
+      <c r="B591" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="C591" s="3">
+        <v>300</v>
+      </c>
+      <c r="D591" s="8" t="s">
+        <v>505</v>
+      </c>
       <c r="E591" s="3"/>
       <c r="F591" s="8"/>
       <c r="G591" s="3"/>
@@ -12477,9 +12632,15 @@
     </row>
     <row r="592" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="3"/>
-      <c r="B592" s="8"/>
-      <c r="C592" s="3"/>
-      <c r="D592" s="8"/>
+      <c r="B592" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="C592" s="3">
+        <v>1020</v>
+      </c>
+      <c r="D592" s="8" t="s">
+        <v>298</v>
+      </c>
       <c r="E592" s="3"/>
       <c r="F592" s="8"/>
       <c r="G592" s="3"/>
@@ -12487,9 +12648,15 @@
     </row>
     <row r="593" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="3"/>
-      <c r="B593" s="8"/>
-      <c r="C593" s="3"/>
-      <c r="D593" s="8"/>
+      <c r="B593" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C593" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D593" s="8" t="s">
+        <v>298</v>
+      </c>
       <c r="E593" s="3"/>
       <c r="F593" s="8"/>
       <c r="G593" s="3"/>
@@ -12497,9 +12664,15 @@
     </row>
     <row r="594" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="3"/>
-      <c r="B594" s="8"/>
-      <c r="C594" s="3"/>
-      <c r="D594" s="8"/>
+      <c r="B594" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="C594" s="3">
+        <v>200</v>
+      </c>
+      <c r="D594" s="8" t="s">
+        <v>505</v>
+      </c>
       <c r="E594" s="3"/>
       <c r="F594" s="8"/>
       <c r="G594" s="3"/>
@@ -12507,9 +12680,15 @@
     </row>
     <row r="595" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="3"/>
-      <c r="B595" s="8"/>
-      <c r="C595" s="3"/>
-      <c r="D595" s="8"/>
+      <c r="B595" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="C595" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D595" s="8" t="s">
+        <v>99</v>
+      </c>
       <c r="E595" s="3"/>
       <c r="F595" s="8"/>
       <c r="G595" s="3"/>
@@ -12536,14 +12715,14 @@
       <c r="H597" s="8"/>
     </row>
     <row r="598" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="3"/>
-      <c r="B598" s="8"/>
-      <c r="C598" s="3"/>
-      <c r="D598" s="8"/>
-      <c r="E598" s="3"/>
-      <c r="F598" s="8"/>
-      <c r="G598" s="3"/>
-      <c r="H598" s="8"/>
+      <c r="A598" s="37"/>
+      <c r="B598" s="37"/>
+      <c r="C598" s="37"/>
+      <c r="D598" s="37"/>
+      <c r="E598" s="37"/>
+      <c r="F598" s="37"/>
+      <c r="G598" s="37"/>
+      <c r="H598" s="37"/>
     </row>
     <row r="599" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="3"/>
@@ -12557,13 +12736,981 @@
     </row>
     <row r="600" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="3"/>
-      <c r="B600" s="8"/>
+      <c r="B600" s="8" t="s">
+        <v>1</v>
+      </c>
       <c r="C600" s="3"/>
-      <c r="D600" s="8"/>
+      <c r="D600" s="8" t="s">
+        <v>513</v>
+      </c>
       <c r="E600" s="3"/>
-      <c r="F600" s="8"/>
+      <c r="F600" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="G600" s="3"/>
-      <c r="H600" s="8"/>
+      <c r="H600" s="8" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="601" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A601" s="3"/>
+      <c r="B601" s="8"/>
+      <c r="C601" s="3"/>
+      <c r="D601" s="8"/>
+      <c r="E601" s="3"/>
+      <c r="F601" s="8"/>
+      <c r="G601" s="3"/>
+      <c r="H601" s="8"/>
+    </row>
+    <row r="602" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A602" s="3"/>
+      <c r="B602" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="C602" s="3">
+        <v>750</v>
+      </c>
+      <c r="D602" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E602" s="3"/>
+      <c r="F602" s="8"/>
+      <c r="G602" s="3"/>
+      <c r="H602" s="8"/>
+    </row>
+    <row r="603" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A603" s="3"/>
+      <c r="B603" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="C603" s="3">
+        <v>260</v>
+      </c>
+      <c r="D603" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E603" s="3"/>
+      <c r="F603" s="8"/>
+      <c r="G603" s="3"/>
+      <c r="H603" s="8"/>
+    </row>
+    <row r="604" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A604" s="3"/>
+      <c r="B604" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="C604" s="3">
+        <v>500</v>
+      </c>
+      <c r="D604" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E604" s="3"/>
+      <c r="F604" s="8"/>
+      <c r="G604" s="3"/>
+      <c r="H604" s="8"/>
+    </row>
+    <row r="605" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A605" s="3"/>
+      <c r="B605" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="C605" s="3">
+        <v>300</v>
+      </c>
+      <c r="D605" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="E605" s="3"/>
+      <c r="F605" s="8"/>
+      <c r="G605" s="3"/>
+      <c r="H605" s="8"/>
+    </row>
+    <row r="606" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A606" s="3"/>
+      <c r="B606" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="C606" s="3">
+        <v>500</v>
+      </c>
+      <c r="D606" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E606" s="3"/>
+      <c r="F606" s="8"/>
+      <c r="G606" s="3"/>
+      <c r="H606" s="8"/>
+    </row>
+    <row r="607" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A607" s="3"/>
+      <c r="B607" s="8"/>
+      <c r="C607" s="3"/>
+      <c r="D607" s="8"/>
+      <c r="E607" s="3"/>
+      <c r="F607" s="8"/>
+      <c r="G607" s="3"/>
+      <c r="H607" s="8"/>
+    </row>
+    <row r="608" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A608" s="3"/>
+      <c r="B608" s="8"/>
+      <c r="C608" s="3"/>
+      <c r="D608" s="8"/>
+      <c r="E608" s="3"/>
+      <c r="F608" s="8"/>
+      <c r="G608" s="3"/>
+      <c r="H608" s="8"/>
+    </row>
+    <row r="609" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A609" s="3"/>
+      <c r="B609" s="8"/>
+      <c r="C609" s="3"/>
+      <c r="D609" s="8"/>
+      <c r="E609" s="3"/>
+      <c r="F609" s="8"/>
+      <c r="G609" s="3"/>
+      <c r="H609" s="8"/>
+    </row>
+    <row r="610" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A610" s="3"/>
+      <c r="B610" s="8"/>
+      <c r="C610" s="3"/>
+      <c r="D610" s="8"/>
+      <c r="E610" s="3"/>
+      <c r="F610" s="8"/>
+      <c r="G610" s="3"/>
+      <c r="H610" s="8"/>
+    </row>
+    <row r="611" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A611" s="3"/>
+      <c r="B611" s="8"/>
+      <c r="C611" s="3"/>
+      <c r="D611" s="8"/>
+      <c r="E611" s="3"/>
+      <c r="F611" s="8"/>
+      <c r="G611" s="3"/>
+      <c r="H611" s="8"/>
+    </row>
+    <row r="612" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A612" s="3"/>
+      <c r="B612" s="8"/>
+      <c r="C612" s="3"/>
+      <c r="D612" s="8"/>
+      <c r="E612" s="3"/>
+      <c r="F612" s="8"/>
+      <c r="G612" s="3"/>
+      <c r="H612" s="8"/>
+    </row>
+    <row r="613" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A613" s="3"/>
+      <c r="B613" s="8"/>
+      <c r="C613" s="3"/>
+      <c r="D613" s="8"/>
+      <c r="E613" s="3"/>
+      <c r="F613" s="8"/>
+      <c r="G613" s="3"/>
+      <c r="H613" s="8"/>
+    </row>
+    <row r="614" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A614" s="3"/>
+      <c r="B614" s="8"/>
+      <c r="C614" s="3"/>
+      <c r="D614" s="8"/>
+      <c r="E614" s="3"/>
+      <c r="F614" s="8"/>
+      <c r="G614" s="3"/>
+      <c r="H614" s="8"/>
+    </row>
+    <row r="615" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A615" s="3"/>
+      <c r="B615" s="8"/>
+      <c r="C615" s="3"/>
+      <c r="D615" s="8"/>
+      <c r="E615" s="3"/>
+      <c r="F615" s="8"/>
+      <c r="G615" s="3"/>
+      <c r="H615" s="8"/>
+    </row>
+    <row r="616" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A616" s="3"/>
+      <c r="B616" s="8"/>
+      <c r="C616" s="3"/>
+      <c r="D616" s="8"/>
+      <c r="E616" s="3"/>
+      <c r="F616" s="8"/>
+      <c r="G616" s="3"/>
+      <c r="H616" s="8"/>
+    </row>
+    <row r="617" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A617" s="3"/>
+      <c r="B617" s="8"/>
+      <c r="C617" s="3"/>
+      <c r="D617" s="8"/>
+      <c r="E617" s="3"/>
+      <c r="F617" s="8"/>
+      <c r="G617" s="3"/>
+      <c r="H617" s="8"/>
+    </row>
+    <row r="618" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A618" s="3"/>
+      <c r="B618" s="8"/>
+      <c r="C618" s="3"/>
+      <c r="D618" s="8"/>
+      <c r="E618" s="3"/>
+      <c r="F618" s="8"/>
+      <c r="G618" s="3"/>
+      <c r="H618" s="8"/>
+    </row>
+    <row r="619" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A619" s="3"/>
+      <c r="B619" s="8"/>
+      <c r="C619" s="3"/>
+      <c r="D619" s="8"/>
+      <c r="E619" s="3"/>
+      <c r="F619" s="8"/>
+      <c r="G619" s="3"/>
+      <c r="H619" s="8"/>
+    </row>
+    <row r="620" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A620" s="3"/>
+      <c r="B620" s="8"/>
+      <c r="C620" s="3"/>
+      <c r="D620" s="8"/>
+      <c r="E620" s="3"/>
+      <c r="F620" s="8"/>
+      <c r="G620" s="3"/>
+      <c r="H620" s="8"/>
+    </row>
+    <row r="621" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A621" s="3"/>
+      <c r="B621" s="8"/>
+      <c r="C621" s="3"/>
+      <c r="D621" s="8"/>
+      <c r="E621" s="3"/>
+      <c r="F621" s="8"/>
+      <c r="G621" s="3"/>
+      <c r="H621" s="8"/>
+    </row>
+    <row r="622" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A622" s="3"/>
+      <c r="B622" s="8"/>
+      <c r="C622" s="3"/>
+      <c r="D622" s="8"/>
+      <c r="E622" s="3"/>
+      <c r="F622" s="8"/>
+      <c r="G622" s="3"/>
+      <c r="H622" s="8"/>
+    </row>
+    <row r="623" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A623" s="3"/>
+      <c r="B623" s="8"/>
+      <c r="C623" s="3"/>
+      <c r="D623" s="8"/>
+      <c r="E623" s="3"/>
+      <c r="F623" s="8"/>
+      <c r="G623" s="3"/>
+      <c r="H623" s="8"/>
+    </row>
+    <row r="624" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A624" s="3"/>
+      <c r="B624" s="8"/>
+      <c r="C624" s="3"/>
+      <c r="D624" s="8"/>
+      <c r="E624" s="3"/>
+      <c r="F624" s="8"/>
+      <c r="G624" s="3"/>
+      <c r="H624" s="8"/>
+    </row>
+    <row r="625" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A625" s="3"/>
+      <c r="B625" s="8"/>
+      <c r="C625" s="3"/>
+      <c r="D625" s="8"/>
+      <c r="E625" s="3"/>
+      <c r="F625" s="8"/>
+      <c r="G625" s="3"/>
+      <c r="H625" s="8"/>
+    </row>
+    <row r="626" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A626" s="3"/>
+      <c r="B626" s="8"/>
+      <c r="C626" s="3"/>
+      <c r="D626" s="8"/>
+      <c r="E626" s="3"/>
+      <c r="F626" s="8"/>
+      <c r="G626" s="3"/>
+      <c r="H626" s="8"/>
+    </row>
+    <row r="627" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A627" s="3"/>
+      <c r="B627" s="8"/>
+      <c r="C627" s="3"/>
+      <c r="D627" s="8"/>
+      <c r="E627" s="3"/>
+      <c r="F627" s="8"/>
+      <c r="G627" s="3"/>
+      <c r="H627" s="8"/>
+    </row>
+    <row r="628" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A628" s="3"/>
+      <c r="B628" s="8"/>
+      <c r="C628" s="3"/>
+      <c r="D628" s="8"/>
+      <c r="E628" s="3"/>
+      <c r="F628" s="8"/>
+      <c r="G628" s="3"/>
+      <c r="H628" s="8"/>
+    </row>
+    <row r="629" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A629" s="3"/>
+      <c r="B629" s="8"/>
+      <c r="C629" s="3"/>
+      <c r="D629" s="8"/>
+      <c r="E629" s="3"/>
+      <c r="F629" s="8"/>
+      <c r="G629" s="3"/>
+      <c r="H629" s="8"/>
+    </row>
+    <row r="630" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A630" s="3"/>
+      <c r="B630" s="8"/>
+      <c r="C630" s="3"/>
+      <c r="D630" s="8"/>
+      <c r="E630" s="3"/>
+      <c r="F630" s="8"/>
+      <c r="G630" s="3"/>
+      <c r="H630" s="8"/>
+    </row>
+    <row r="631" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A631" s="3"/>
+      <c r="B631" s="8"/>
+      <c r="C631" s="3"/>
+      <c r="D631" s="8"/>
+      <c r="E631" s="3"/>
+      <c r="F631" s="8"/>
+      <c r="G631" s="3"/>
+      <c r="H631" s="8"/>
+    </row>
+    <row r="632" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A632" s="3"/>
+      <c r="B632" s="8"/>
+      <c r="C632" s="3"/>
+      <c r="D632" s="8"/>
+      <c r="E632" s="3"/>
+      <c r="F632" s="8"/>
+      <c r="G632" s="3"/>
+      <c r="H632" s="8"/>
+    </row>
+    <row r="633" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A633" s="3"/>
+      <c r="B633" s="8"/>
+      <c r="C633" s="3"/>
+      <c r="D633" s="8"/>
+      <c r="E633" s="3"/>
+      <c r="F633" s="8"/>
+      <c r="G633" s="3"/>
+      <c r="H633" s="8"/>
+    </row>
+    <row r="634" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A634" s="3"/>
+      <c r="B634" s="8"/>
+      <c r="C634" s="3"/>
+      <c r="D634" s="8"/>
+      <c r="E634" s="3"/>
+      <c r="F634" s="8"/>
+      <c r="G634" s="3"/>
+      <c r="H634" s="8"/>
+    </row>
+    <row r="635" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A635" s="3"/>
+      <c r="B635" s="8"/>
+      <c r="C635" s="3"/>
+      <c r="D635" s="8"/>
+      <c r="E635" s="3"/>
+      <c r="F635" s="8"/>
+      <c r="G635" s="3"/>
+      <c r="H635" s="8"/>
+    </row>
+    <row r="636" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A636" s="3"/>
+      <c r="B636" s="8"/>
+      <c r="C636" s="3"/>
+      <c r="D636" s="8"/>
+      <c r="E636" s="3"/>
+      <c r="F636" s="8"/>
+      <c r="G636" s="3"/>
+      <c r="H636" s="8"/>
+    </row>
+    <row r="637" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A637" s="3"/>
+      <c r="B637" s="8"/>
+      <c r="C637" s="3"/>
+      <c r="D637" s="8"/>
+      <c r="E637" s="3"/>
+      <c r="F637" s="8"/>
+      <c r="G637" s="3"/>
+      <c r="H637" s="8"/>
+    </row>
+    <row r="638" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A638" s="3"/>
+      <c r="B638" s="8"/>
+      <c r="C638" s="3"/>
+      <c r="D638" s="8"/>
+      <c r="E638" s="3"/>
+      <c r="F638" s="8"/>
+      <c r="G638" s="3"/>
+      <c r="H638" s="8"/>
+    </row>
+    <row r="639" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A639" s="3"/>
+      <c r="B639" s="8"/>
+      <c r="C639" s="3"/>
+      <c r="D639" s="8"/>
+      <c r="E639" s="3"/>
+      <c r="F639" s="8"/>
+      <c r="G639" s="3"/>
+      <c r="H639" s="8"/>
+    </row>
+    <row r="640" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A640" s="3"/>
+      <c r="B640" s="8"/>
+      <c r="C640" s="3"/>
+      <c r="D640" s="8"/>
+      <c r="E640" s="3"/>
+      <c r="F640" s="8"/>
+      <c r="G640" s="3"/>
+      <c r="H640" s="8"/>
+    </row>
+    <row r="641" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A641" s="3"/>
+      <c r="B641" s="8"/>
+      <c r="C641" s="3"/>
+      <c r="D641" s="8"/>
+      <c r="E641" s="3"/>
+      <c r="F641" s="8"/>
+      <c r="G641" s="3"/>
+      <c r="H641" s="8"/>
+    </row>
+    <row r="642" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A642" s="3"/>
+      <c r="B642" s="8"/>
+      <c r="C642" s="3"/>
+      <c r="D642" s="8"/>
+      <c r="E642" s="3"/>
+      <c r="F642" s="8"/>
+      <c r="G642" s="3"/>
+      <c r="H642" s="8"/>
+    </row>
+    <row r="643" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A643" s="3"/>
+      <c r="B643" s="8"/>
+      <c r="C643" s="3"/>
+      <c r="D643" s="8"/>
+      <c r="E643" s="3"/>
+      <c r="F643" s="8"/>
+      <c r="G643" s="3"/>
+      <c r="H643" s="8"/>
+    </row>
+    <row r="644" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A644" s="3"/>
+      <c r="B644" s="8"/>
+      <c r="C644" s="3"/>
+      <c r="D644" s="8"/>
+      <c r="E644" s="3"/>
+      <c r="F644" s="8"/>
+      <c r="G644" s="3"/>
+      <c r="H644" s="8"/>
+    </row>
+    <row r="645" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A645" s="3"/>
+      <c r="B645" s="8"/>
+      <c r="C645" s="3"/>
+      <c r="D645" s="8"/>
+      <c r="E645" s="3"/>
+      <c r="F645" s="8"/>
+      <c r="G645" s="3"/>
+      <c r="H645" s="8"/>
+    </row>
+    <row r="646" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A646" s="3"/>
+      <c r="B646" s="8"/>
+      <c r="C646" s="3"/>
+      <c r="D646" s="8"/>
+      <c r="E646" s="3"/>
+      <c r="F646" s="8"/>
+      <c r="G646" s="3"/>
+      <c r="H646" s="8"/>
+    </row>
+    <row r="647" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A647" s="3"/>
+      <c r="B647" s="8"/>
+      <c r="C647" s="3"/>
+      <c r="D647" s="8"/>
+      <c r="E647" s="3"/>
+      <c r="F647" s="8"/>
+      <c r="G647" s="3"/>
+      <c r="H647" s="8"/>
+    </row>
+    <row r="648" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A648" s="3"/>
+      <c r="B648" s="8"/>
+      <c r="C648" s="3"/>
+      <c r="D648" s="8"/>
+      <c r="E648" s="3"/>
+      <c r="F648" s="8"/>
+      <c r="G648" s="3"/>
+      <c r="H648" s="8"/>
+    </row>
+    <row r="649" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A649" s="3"/>
+      <c r="B649" s="8"/>
+      <c r="C649" s="3"/>
+      <c r="D649" s="8"/>
+      <c r="E649" s="3"/>
+      <c r="F649" s="8"/>
+      <c r="G649" s="3"/>
+      <c r="H649" s="8"/>
+    </row>
+    <row r="650" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A650" s="3"/>
+      <c r="B650" s="8"/>
+      <c r="C650" s="3"/>
+      <c r="D650" s="8"/>
+      <c r="E650" s="3"/>
+      <c r="F650" s="8"/>
+      <c r="G650" s="3"/>
+      <c r="H650" s="8"/>
+    </row>
+    <row r="651" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A651" s="3"/>
+      <c r="B651" s="8"/>
+      <c r="C651" s="3"/>
+      <c r="D651" s="8"/>
+      <c r="E651" s="3"/>
+      <c r="F651" s="8"/>
+      <c r="G651" s="3"/>
+      <c r="H651" s="8"/>
+    </row>
+    <row r="652" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A652" s="3"/>
+      <c r="B652" s="8"/>
+      <c r="C652" s="3"/>
+      <c r="D652" s="8"/>
+      <c r="E652" s="3"/>
+      <c r="F652" s="8"/>
+      <c r="G652" s="3"/>
+      <c r="H652" s="8"/>
+    </row>
+    <row r="653" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A653" s="3"/>
+      <c r="B653" s="8"/>
+      <c r="C653" s="3"/>
+      <c r="D653" s="8"/>
+      <c r="E653" s="3"/>
+      <c r="F653" s="8"/>
+      <c r="G653" s="3"/>
+      <c r="H653" s="8"/>
+    </row>
+    <row r="654" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A654" s="3"/>
+      <c r="B654" s="8"/>
+      <c r="C654" s="3"/>
+      <c r="D654" s="8"/>
+      <c r="E654" s="3"/>
+      <c r="F654" s="8"/>
+      <c r="G654" s="3"/>
+      <c r="H654" s="8"/>
+    </row>
+    <row r="655" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A655" s="3"/>
+      <c r="B655" s="8"/>
+      <c r="C655" s="3"/>
+      <c r="D655" s="8"/>
+      <c r="E655" s="3"/>
+      <c r="F655" s="8"/>
+      <c r="G655" s="3"/>
+      <c r="H655" s="8"/>
+    </row>
+    <row r="656" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A656" s="3"/>
+      <c r="B656" s="8"/>
+      <c r="C656" s="3"/>
+      <c r="D656" s="8"/>
+      <c r="E656" s="3"/>
+      <c r="F656" s="8"/>
+      <c r="G656" s="3"/>
+      <c r="H656" s="8"/>
+    </row>
+    <row r="657" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A657" s="3"/>
+      <c r="B657" s="8"/>
+      <c r="C657" s="3"/>
+      <c r="D657" s="8"/>
+      <c r="E657" s="3"/>
+      <c r="F657" s="8"/>
+      <c r="G657" s="3"/>
+      <c r="H657" s="8"/>
+    </row>
+    <row r="658" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A658" s="3"/>
+      <c r="B658" s="8"/>
+      <c r="C658" s="3"/>
+      <c r="D658" s="8"/>
+      <c r="E658" s="3"/>
+      <c r="F658" s="8"/>
+      <c r="G658" s="3"/>
+      <c r="H658" s="8"/>
+    </row>
+    <row r="659" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A659" s="3"/>
+      <c r="B659" s="8"/>
+      <c r="C659" s="3"/>
+      <c r="D659" s="8"/>
+      <c r="E659" s="3"/>
+      <c r="F659" s="8"/>
+      <c r="G659" s="3"/>
+      <c r="H659" s="8"/>
+    </row>
+    <row r="660" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A660" s="3"/>
+      <c r="B660" s="8"/>
+      <c r="C660" s="3"/>
+      <c r="D660" s="8"/>
+      <c r="E660" s="3"/>
+      <c r="F660" s="8"/>
+      <c r="G660" s="3"/>
+      <c r="H660" s="8"/>
+    </row>
+    <row r="661" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A661" s="3"/>
+      <c r="B661" s="8"/>
+      <c r="C661" s="3"/>
+      <c r="D661" s="8"/>
+      <c r="E661" s="3"/>
+      <c r="F661" s="8"/>
+      <c r="G661" s="3"/>
+      <c r="H661" s="8"/>
+    </row>
+    <row r="662" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A662" s="3"/>
+      <c r="B662" s="8"/>
+      <c r="C662" s="3"/>
+      <c r="D662" s="8"/>
+      <c r="E662" s="3"/>
+      <c r="F662" s="8"/>
+      <c r="G662" s="3"/>
+      <c r="H662" s="8"/>
+    </row>
+    <row r="663" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A663" s="3"/>
+      <c r="B663" s="8"/>
+      <c r="C663" s="3"/>
+      <c r="D663" s="8"/>
+      <c r="E663" s="3"/>
+      <c r="F663" s="8"/>
+      <c r="G663" s="3"/>
+      <c r="H663" s="8"/>
+    </row>
+    <row r="664" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A664" s="3"/>
+      <c r="B664" s="8"/>
+      <c r="C664" s="3"/>
+      <c r="D664" s="8"/>
+      <c r="E664" s="3"/>
+      <c r="F664" s="8"/>
+      <c r="G664" s="3"/>
+      <c r="H664" s="8"/>
+    </row>
+    <row r="665" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A665" s="3"/>
+      <c r="B665" s="8"/>
+      <c r="C665" s="3"/>
+      <c r="D665" s="8"/>
+      <c r="E665" s="3"/>
+      <c r="F665" s="8"/>
+      <c r="G665" s="3"/>
+      <c r="H665" s="8"/>
+    </row>
+    <row r="666" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A666" s="3"/>
+      <c r="B666" s="8"/>
+      <c r="C666" s="3"/>
+      <c r="D666" s="8"/>
+      <c r="E666" s="3"/>
+      <c r="F666" s="8"/>
+      <c r="G666" s="3"/>
+      <c r="H666" s="8"/>
+    </row>
+    <row r="667" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A667" s="3"/>
+      <c r="B667" s="8"/>
+      <c r="C667" s="3"/>
+      <c r="D667" s="8"/>
+      <c r="E667" s="3"/>
+      <c r="F667" s="8"/>
+      <c r="G667" s="3"/>
+      <c r="H667" s="8"/>
+    </row>
+    <row r="668" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A668" s="3"/>
+      <c r="B668" s="8"/>
+      <c r="C668" s="3"/>
+      <c r="D668" s="8"/>
+      <c r="E668" s="3"/>
+      <c r="F668" s="8"/>
+      <c r="G668" s="3"/>
+      <c r="H668" s="8"/>
+    </row>
+    <row r="669" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A669" s="3"/>
+      <c r="B669" s="8"/>
+      <c r="C669" s="3"/>
+      <c r="D669" s="8"/>
+      <c r="E669" s="3"/>
+      <c r="F669" s="8"/>
+      <c r="G669" s="3"/>
+      <c r="H669" s="8"/>
+    </row>
+    <row r="670" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A670" s="3"/>
+      <c r="B670" s="8"/>
+      <c r="C670" s="3"/>
+      <c r="D670" s="8"/>
+      <c r="E670" s="3"/>
+      <c r="F670" s="8"/>
+      <c r="G670" s="3"/>
+      <c r="H670" s="8"/>
+    </row>
+    <row r="671" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A671" s="3"/>
+      <c r="B671" s="8"/>
+      <c r="C671" s="3"/>
+      <c r="D671" s="8"/>
+      <c r="E671" s="3"/>
+      <c r="F671" s="8"/>
+      <c r="G671" s="3"/>
+      <c r="H671" s="8"/>
+    </row>
+    <row r="672" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A672" s="3"/>
+      <c r="B672" s="8"/>
+      <c r="C672" s="3"/>
+      <c r="D672" s="8"/>
+      <c r="E672" s="3"/>
+      <c r="F672" s="8"/>
+      <c r="G672" s="3"/>
+      <c r="H672" s="8"/>
+    </row>
+    <row r="673" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A673" s="3"/>
+      <c r="B673" s="8"/>
+      <c r="C673" s="3"/>
+      <c r="D673" s="8"/>
+      <c r="E673" s="3"/>
+      <c r="F673" s="8"/>
+      <c r="G673" s="3"/>
+      <c r="H673" s="8"/>
+    </row>
+    <row r="674" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A674" s="3"/>
+      <c r="B674" s="8"/>
+      <c r="C674" s="3"/>
+      <c r="D674" s="8"/>
+      <c r="E674" s="3"/>
+      <c r="F674" s="8"/>
+      <c r="G674" s="3"/>
+      <c r="H674" s="8"/>
+    </row>
+    <row r="675" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A675" s="3"/>
+      <c r="B675" s="8"/>
+      <c r="C675" s="3"/>
+      <c r="D675" s="8"/>
+      <c r="E675" s="3"/>
+      <c r="F675" s="8"/>
+      <c r="G675" s="3"/>
+      <c r="H675" s="8"/>
+    </row>
+    <row r="676" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A676" s="3"/>
+      <c r="B676" s="8"/>
+      <c r="C676" s="3"/>
+      <c r="D676" s="8"/>
+      <c r="E676" s="3"/>
+      <c r="F676" s="8"/>
+      <c r="G676" s="3"/>
+      <c r="H676" s="8"/>
+    </row>
+    <row r="677" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A677" s="3"/>
+      <c r="B677" s="8"/>
+      <c r="C677" s="3"/>
+      <c r="D677" s="8"/>
+      <c r="E677" s="3"/>
+      <c r="F677" s="8"/>
+      <c r="G677" s="3"/>
+      <c r="H677" s="8"/>
+    </row>
+    <row r="678" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A678" s="3"/>
+      <c r="B678" s="8"/>
+      <c r="C678" s="3"/>
+      <c r="D678" s="8"/>
+      <c r="E678" s="3"/>
+      <c r="F678" s="8"/>
+      <c r="G678" s="3"/>
+      <c r="H678" s="8"/>
+    </row>
+    <row r="679" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A679" s="3"/>
+      <c r="B679" s="8"/>
+      <c r="C679" s="3"/>
+      <c r="D679" s="8"/>
+      <c r="E679" s="3"/>
+      <c r="F679" s="8"/>
+      <c r="G679" s="3"/>
+      <c r="H679" s="8"/>
+    </row>
+    <row r="680" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A680" s="3"/>
+      <c r="B680" s="8"/>
+      <c r="C680" s="3"/>
+      <c r="D680" s="8"/>
+      <c r="E680" s="3"/>
+      <c r="F680" s="8"/>
+      <c r="G680" s="3"/>
+      <c r="H680" s="8"/>
+    </row>
+    <row r="681" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A681" s="3"/>
+      <c r="B681" s="8"/>
+      <c r="C681" s="3"/>
+      <c r="D681" s="8"/>
+      <c r="E681" s="3"/>
+      <c r="F681" s="8"/>
+      <c r="G681" s="3"/>
+      <c r="H681" s="8"/>
+    </row>
+    <row r="682" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A682" s="3"/>
+      <c r="B682" s="8"/>
+      <c r="C682" s="3"/>
+      <c r="D682" s="8"/>
+      <c r="E682" s="3"/>
+      <c r="F682" s="8"/>
+      <c r="G682" s="3"/>
+      <c r="H682" s="8"/>
+    </row>
+    <row r="683" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A683" s="3"/>
+      <c r="B683" s="8"/>
+      <c r="C683" s="3"/>
+      <c r="D683" s="8"/>
+      <c r="E683" s="3"/>
+      <c r="F683" s="8"/>
+      <c r="G683" s="3"/>
+      <c r="H683" s="8"/>
+    </row>
+    <row r="684" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A684" s="3"/>
+      <c r="B684" s="8"/>
+      <c r="C684" s="3"/>
+      <c r="D684" s="8"/>
+      <c r="E684" s="3"/>
+      <c r="F684" s="8"/>
+      <c r="G684" s="3"/>
+      <c r="H684" s="8"/>
+    </row>
+    <row r="685" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A685" s="3"/>
+      <c r="B685" s="8"/>
+      <c r="C685" s="3"/>
+      <c r="D685" s="8"/>
+      <c r="E685" s="3"/>
+      <c r="F685" s="8"/>
+      <c r="G685" s="3"/>
+      <c r="H685" s="8"/>
+    </row>
+    <row r="686" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A686" s="3"/>
+      <c r="B686" s="8"/>
+      <c r="C686" s="3"/>
+      <c r="D686" s="8"/>
+      <c r="E686" s="3"/>
+      <c r="F686" s="8"/>
+      <c r="G686" s="3"/>
+      <c r="H686" s="8"/>
+    </row>
+    <row r="687" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A687" s="3"/>
+      <c r="B687" s="8"/>
+      <c r="C687" s="3"/>
+      <c r="D687" s="8"/>
+      <c r="E687" s="3"/>
+      <c r="F687" s="8"/>
+      <c r="G687" s="3"/>
+      <c r="H687" s="8"/>
+    </row>
+    <row r="688" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A688" s="3"/>
+      <c r="B688" s="8"/>
+      <c r="C688" s="3"/>
+      <c r="D688" s="8"/>
+      <c r="E688" s="3"/>
+      <c r="F688" s="8"/>
+      <c r="G688" s="3"/>
+      <c r="H688" s="8"/>
+    </row>
+    <row r="689" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A689" s="3"/>
+      <c r="B689" s="8"/>
+      <c r="C689" s="3"/>
+      <c r="D689" s="8"/>
+      <c r="E689" s="3"/>
+      <c r="F689" s="8"/>
+      <c r="G689" s="3"/>
+      <c r="H689" s="8"/>
+    </row>
+    <row r="690" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A690" s="3"/>
+      <c r="B690" s="8"/>
+      <c r="C690" s="3"/>
+      <c r="D690" s="8"/>
+      <c r="E690" s="3"/>
+      <c r="F690" s="8"/>
+      <c r="G690" s="3"/>
+      <c r="H690" s="8"/>
+    </row>
+    <row r="691" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A691" s="3"/>
+      <c r="B691" s="8"/>
+      <c r="C691" s="3"/>
+      <c r="D691" s="8"/>
+      <c r="E691" s="3"/>
+      <c r="F691" s="8"/>
+      <c r="G691" s="3"/>
+      <c r="H691" s="8"/>
+    </row>
+    <row r="692" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A692" s="3"/>
+      <c r="B692" s="8"/>
+      <c r="C692" s="3"/>
+      <c r="D692" s="8"/>
+      <c r="E692" s="3"/>
+      <c r="F692" s="8"/>
+      <c r="G692" s="3"/>
+      <c r="H692" s="8"/>
+    </row>
+    <row r="693" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A693" s="3"/>
+      <c r="B693" s="8"/>
+      <c r="C693" s="3"/>
+      <c r="D693" s="8"/>
+      <c r="E693" s="3"/>
+      <c r="F693" s="8"/>
+      <c r="G693" s="3"/>
+      <c r="H693" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -12584,7 +13731,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A127:B127 G38:H38 C40:D45 C46:E53 C61:D61 C60:E60 A11:D20 H27:H37 F11:F20 A22:D24 G11:H26 B77:B82 D93:D183 B35:B75 A3:H10 A30:D34 A21:F21 E127 E92:F94 C62:E63 C36:F39 C83:F88 C54:E54 C55:E55 C56:E56 C57:E57 C58:E58 C59:E59 G75:H88 C70:E70 C64:E64 C65:E65 C66:E66 C67:E67 C68:E68 C75:F82 C71:E71 C72:E72 C73:E73 C74:E74 C69:E69 B83:B96 C90:F91 C89:E89 G90:H93 H89 D184:D196 A25:D29 F22:F29 H39:H42 F30:F35 H43:H47 B98:B103 B105:B106 B108 B110:B111 B113:B114 D198:D201 D203:D205 D208 D210:D219 D222:D225 D227:D283 C35:D35 B310:B315 D310:D374 B317:B320 H310:H316 H48:H51 D487:D526 H487:H498 H499:H510 H527:H536 H541 D527:D574" numberStoredAsText="1"/>
+    <ignoredError sqref="A127:B127 G38:H38 C40:D45 C46:E53 C61:D61 C60:E60 A11:D20 H27:H37 F11:F20 A22:D24 G11:H26 B77:B82 D93:D183 B35:B75 A3:H10 A30:D34 A21:F21 E127 E92:F94 C62:E63 C36:F39 C83:F88 C54:E54 C55:E55 C56:E56 C57:E57 C58:E58 C59:E59 G75:H88 C70:E70 C64:E64 C65:E65 C66:E66 C67:E67 C68:E68 C75:F82 C71:E71 C72:E72 C73:E73 C74:E74 C69:E69 B83:B96 C90:F91 C89:E89 G90:H93 H89 D184:D196 A25:D29 F22:F29 H39:H42 F30:F35 H43:H47 B98:B103 B105:B106 B108 B110:B111 B113:B114 D198:D201 D203:D205 D208 D210:D219 D222:D225 D227:D283 C35:D35 B310:B315 D310:D374 B317:B320 H310:H316 H48:H51 D487:D526 H487:H497 H510 D527:D574 D584:D595 H584:H590" numberStoredAsText="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/Syriatel Cash Inventory.xlsx
+++ b/Syriatel Cash Inventory.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Melad Ibrahim\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jafar\Desktop\Temp\ibrahem-melad1411-patch-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA900F1-6157-4836-8246-94FF6F7BBBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="96" yWindow="6120" windowWidth="23040" windowHeight="6216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8556"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="521">
   <si>
     <t>التحويلات الواردة</t>
   </si>
@@ -202,7 +201,7 @@
         <u/>
         <sz val="14"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -212,7 +211,7 @@
       <rPr>
         <sz val="14"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -223,7 +222,7 @@
         <u/>
         <sz val="14"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -1631,23 +1630,26 @@
   <si>
     <t>7 22:29</t>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1655,20 +1657,20 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1676,7 +1678,7 @@
       <u/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2257,24 +2259,6 @@
     <xf numFmtId="38" fontId="1" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2302,9 +2286,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="عادي" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2420,8 +2422,8 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1229 24575,'5'4'0,"1"1"0,0-1 0,0-1 0,0 1 0,1-1 0,-1 0 0,1 0 0,0-1 0,0 0 0,0 0 0,0 0 0,8 0 0,14 1 0,47-1 0,-61-3 0,0 1 0,0 1 0,0 0 0,0 0 0,0 2 0,0 0 0,25 8 0,-21-5 0,1-1 0,0-1 0,0 0 0,33 1 0,86-6 0,-65-1 0,586 2 0,-642-2 0,0 0 0,0-1 0,-1 0 0,1-2 0,-1 0 0,1-1 0,-2-1 0,29-15 0,-15 8 0,47-16 0,5 5 0,-1-3 0,-1-4 0,90-51 0,-142 64 0,-1-1 0,-1-1 0,-1-2 0,-1 0 0,41-53 0,-33 37 0,63-57 0,-36 47 0,3 2 0,1 3 0,91-47 0,-117 69 0,37-27 0,14-9 0,-59 42 0,1 0 0,1 2 0,0 2 0,1 0 0,52-11 0,5 3 0,-31 6 0,1 2 0,68-5 0,129 15 0,-131 4 0,-83 0 0,0 2 0,54 13 0,11 1 0,163 5 0,20-2 0,-13 0 0,251-22-1365,-504 1-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2163.85">5420 1 24575,'0'2'0,"0"1"0,1 0 0,-1 0 0,1-1 0,0 1 0,0-1 0,0 1 0,0 0 0,0-1 0,0 0 0,1 1 0,-1-1 0,1 0 0,2 3 0,33 29 0,-30-28 0,0 0 0,0 0 0,-1 0 0,6 7 0,6 11 0,0-2 0,2 0 0,32 27 0,-43-42 0,0-1 0,0 0 0,1-1 0,17 8 0,23 13 0,-14-3 0,-26-17 0,0-1 0,-1 2 0,1-1 0,-1 1 0,-1 1 0,1 0 0,-1 0 0,0 0 0,11 17 0,-19-23 0,1-1 0,0 1 0,-1 0 0,1-1 0,-1 1 0,0 0 0,1 0 0,-1-1 0,0 1 0,0 0 0,0 0 0,0-1 0,0 1 0,-1 0 0,1 0 0,0-1 0,-1 1 0,0 0 0,1 0 0,-1-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 0 0,0 1 0,-3 1 0,-3 4 0,-2-1 0,1 0 0,-19 10 0,13-7 0,-37 21 0,-2-3 0,-1-1 0,-1-3 0,-96 27 0,37-12-1365,84-27-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1230 24575,'4'4'0,"2"1"0,-1-1 0,0-1 0,0 1 0,1-1 0,0 0 0,0 0 0,0-1 0,0 0 0,0 0 0,0 0 0,7 0 0,12 1 0,41-1 0,-53-3 0,0 1 0,0 1 0,0 0 0,1 0 0,-1 2 0,0 0 0,21 8 0,-17-5 0,0-1 0,1-1 0,-1 0 0,29 1 0,75-6 0,-57-1 0,510 2 0,-558-2 0,0 0 0,-1-1 0,0 0 0,1-2 0,-1 0 0,0-1 0,-1-1 0,25-15 0,-13 8 0,41-16 0,5 5 0,-2-3 0,0-4 0,77-51 0,-122 64 0,-2-1 0,0-1 0,-1-2 0,-1 0 0,35-53 0,-28 37 0,54-57 0,-30 47 0,2 1 0,0 4 0,80-47 0,-101 69 0,31-27 0,12-9 0,-50 42 0,0 0 0,1 2 0,0 2 0,1 0 0,45-11 0,4 3 0,-27 6 0,2 2 0,58-5 0,113 15 0,-115 4 0,-71 0 0,0 2 0,46 13 0,10 1 0,142 5 0,17-2 0,-11 0 0,218-22-1365,-438 1-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2163.85">4713 1 24575,'0'2'0,"0"1"0,1 0 0,-1 0 0,1-1 0,0 1 0,0-1 0,0 1 0,0 0 0,0-1 0,-1 0 0,2 1 0,-1-1 0,1 0 0,1 3 0,29 29 0,-25-28 0,-1 0 0,0 0 0,-1 0 0,5 7 0,6 11 0,0-2 0,1 0 0,28 27 0,-37-42 0,0-1 0,0 0 0,0-1 0,16 8 0,19 13 0,-11-3 0,-24-17 0,1-1 0,-1 2 0,1-1 0,-2 1 0,0 1 0,1 0 0,-1 0 0,0 0 0,10 17 0,-17-23 0,1-1 0,-1 1 0,0 0 0,1-1 0,-1 1 0,0 0 0,1 0 0,-1-1 0,0 1 0,0 0 0,0 0 0,0-1 0,0 1 0,-1 0 0,1 0 0,0-1 0,-1 1 0,1 0 0,0 0 0,-1-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,1 0 0,-1 1 0,-3 1 0,-2 4 0,-2-1 0,1 0 0,-16 10 0,11-7 0,-33 21 0,-1-3 0,-1-1 0,-1-3 0,-83 27 0,32-11-1365,73-28-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -2687,33 +2689,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J693"/>
-  <sheetFormatPr defaultColWidth="17.69921875" defaultRowHeight="19.2" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="17.6640625" defaultRowHeight="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.69921875" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="17.69921875" style="2"/>
+    <col min="1" max="1" width="17.6640625" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="17.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42" t="s">
+      <c r="D1" s="51"/>
+      <c r="E1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42" t="s">
+      <c r="F1" s="51"/>
+      <c r="G1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="43"/>
-    </row>
-    <row r="2" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H1" s="52"/>
+    </row>
+    <row r="2" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
@@ -2738,11 +2740,11 @@
       <c r="H2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="53" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>56</v>
       </c>
@@ -2762,9 +2764,9 @@
       <c r="I3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J3" s="45"/>
-    </row>
-    <row r="4" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J3" s="54"/>
+    </row>
+    <row r="4" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>240000</v>
       </c>
@@ -2792,11 +2794,11 @@
       <c r="I4" s="2">
         <v>111</v>
       </c>
-      <c r="J4" s="40" t="s">
+      <c r="J4" s="49" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>100000</v>
       </c>
@@ -2824,9 +2826,9 @@
       <c r="I5" s="2">
         <v>111</v>
       </c>
-      <c r="J5" s="40"/>
-    </row>
-    <row r="6" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J5" s="49"/>
+    </row>
+    <row r="6" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>276000</v>
       </c>
@@ -2854,9 +2856,9 @@
       <c r="I6" s="2">
         <v>111</v>
       </c>
-      <c r="J6" s="40"/>
-    </row>
-    <row r="7" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J6" s="49"/>
+    </row>
+    <row r="7" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>200000</v>
       </c>
@@ -2885,7 +2887,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>200000</v>
       </c>
@@ -2914,7 +2916,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>100000</v>
       </c>
@@ -2946,7 +2948,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>40000</v>
       </c>
@@ -2970,11 +2972,11 @@
       <c r="I10" s="2">
         <v>111</v>
       </c>
-      <c r="J10" s="40" t="s">
+      <c r="J10" s="49" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>330000</v>
       </c>
@@ -3002,9 +3004,9 @@
       <c r="I11" s="2">
         <v>111</v>
       </c>
-      <c r="J11" s="40"/>
-    </row>
-    <row r="12" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J11" s="49"/>
+    </row>
+    <row r="12" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>200000</v>
       </c>
@@ -3032,9 +3034,9 @@
       <c r="I12" s="2">
         <v>111</v>
       </c>
-      <c r="J12" s="40"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J12" s="49"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>219000</v>
       </c>
@@ -3063,7 +3065,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>189000</v>
       </c>
@@ -3095,7 +3097,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>164000</v>
       </c>
@@ -3124,7 +3126,7 @@
         <v>1111111111</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>250000</v>
       </c>
@@ -3153,7 +3155,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>300000</v>
       </c>
@@ -3182,7 +3184,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>48000</v>
       </c>
@@ -3211,7 +3213,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>35000</v>
       </c>
@@ -3240,7 +3242,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>467000</v>
       </c>
@@ -3269,7 +3271,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>10000</v>
       </c>
@@ -3294,7 +3296,7 @@
         <v>1111111111</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>100000</v>
       </c>
@@ -3323,7 +3325,7 @@
         <v>1111111111</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>100000</v>
       </c>
@@ -3352,7 +3354,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>54000</v>
       </c>
@@ -3381,7 +3383,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>100000</v>
       </c>
@@ -3410,7 +3412,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>41000</v>
       </c>
@@ -3432,7 +3434,7 @@
       <c r="G26" s="16"/>
       <c r="H26" s="17"/>
     </row>
-    <row r="27" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>200000</v>
       </c>
@@ -3461,7 +3463,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>400000</v>
       </c>
@@ -3486,11 +3488,11 @@
       <c r="H28" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="54" t="s">
+      <c r="J28" s="48" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>500000</v>
       </c>
@@ -3515,9 +3517,9 @@
       <c r="H29" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J29" s="54"/>
-    </row>
-    <row r="30" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J29" s="48"/>
+    </row>
+    <row r="30" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>150000</v>
       </c>
@@ -3542,9 +3544,9 @@
       <c r="H30" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J30" s="54"/>
-    </row>
-    <row r="31" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J30" s="48"/>
+    </row>
+    <row r="31" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>200000</v>
       </c>
@@ -3570,7 +3572,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>205000</v>
       </c>
@@ -3596,7 +3598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>200000</v>
       </c>
@@ -3622,7 +3624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="16"/>
       <c r="B34" s="17"/>
       <c r="C34" s="3">
@@ -3644,7 +3646,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>7000</v>
       </c>
@@ -3670,7 +3672,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>81000</v>
       </c>
@@ -3692,7 +3694,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>200000</v>
       </c>
@@ -3714,7 +3716,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>100000</v>
       </c>
@@ -3732,7 +3734,7 @@
       <c r="G38" s="22"/>
       <c r="H38" s="22"/>
     </row>
-    <row r="39" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>250000</v>
       </c>
@@ -3757,7 +3759,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>150000</v>
       </c>
@@ -3778,11 +3780,11 @@
       <c r="H40" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J40" s="53" t="s">
+      <c r="J40" s="47" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>300000</v>
       </c>
@@ -3803,9 +3805,9 @@
       <c r="H41" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="J41" s="53"/>
-    </row>
-    <row r="42" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J41" s="47"/>
+    </row>
+    <row r="42" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>200000</v>
       </c>
@@ -3826,9 +3828,9 @@
       <c r="H42" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="J42" s="53"/>
-    </row>
-    <row r="43" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J42" s="47"/>
+    </row>
+    <row r="43" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>200000</v>
       </c>
@@ -3850,7 +3852,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>150000</v>
       </c>
@@ -3872,7 +3874,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>200000</v>
       </c>
@@ -3894,7 +3896,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>150000</v>
       </c>
@@ -3916,7 +3918,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>250000</v>
       </c>
@@ -3938,7 +3940,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>45000</v>
       </c>
@@ -3960,7 +3962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>150000</v>
       </c>
@@ -3982,7 +3984,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>200000</v>
       </c>
@@ -4004,7 +4006,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>45000</v>
       </c>
@@ -4026,7 +4028,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>250000</v>
       </c>
@@ -4044,7 +4046,7 @@
       <c r="G52" s="39"/>
       <c r="H52" s="25"/>
     </row>
-    <row r="53" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>100000</v>
       </c>
@@ -4062,7 +4064,7 @@
       <c r="G53" s="3"/>
       <c r="H53" s="8"/>
     </row>
-    <row r="54" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>50000</v>
       </c>
@@ -4080,7 +4082,7 @@
       <c r="G54" s="3"/>
       <c r="H54" s="8"/>
     </row>
-    <row r="55" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>400000</v>
       </c>
@@ -4098,7 +4100,7 @@
       <c r="G55" s="3"/>
       <c r="H55" s="8"/>
     </row>
-    <row r="56" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>50000</v>
       </c>
@@ -4116,7 +4118,7 @@
       <c r="G56" s="3"/>
       <c r="H56" s="8"/>
     </row>
-    <row r="57" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>230000</v>
       </c>
@@ -4134,7 +4136,7 @@
       <c r="G57" s="3"/>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
         <v>360000</v>
       </c>
@@ -4155,7 +4157,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <v>500000</v>
       </c>
@@ -4172,11 +4174,11 @@
       <c r="F59" s="8"/>
       <c r="G59" s="3"/>
       <c r="H59" s="8"/>
-      <c r="J59" s="49" t="s">
+      <c r="J59" s="43" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <v>500000</v>
       </c>
@@ -4193,9 +4195,9 @@
       <c r="F60" s="8"/>
       <c r="G60" s="3"/>
       <c r="H60" s="8"/>
-      <c r="J60" s="49"/>
-    </row>
-    <row r="61" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J60" s="43"/>
+    </row>
+    <row r="61" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <v>42600</v>
       </c>
@@ -4212,9 +4214,9 @@
       <c r="F61" s="8"/>
       <c r="G61" s="3"/>
       <c r="H61" s="8"/>
-      <c r="J61" s="49"/>
-    </row>
-    <row r="62" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J61" s="43"/>
+    </row>
+    <row r="62" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>37600</v>
       </c>
@@ -4232,7 +4234,7 @@
       <c r="G62" s="3"/>
       <c r="H62" s="8"/>
     </row>
-    <row r="63" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>109800</v>
       </c>
@@ -4250,7 +4252,7 @@
       <c r="G63" s="3"/>
       <c r="H63" s="8"/>
     </row>
-    <row r="64" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>50000</v>
       </c>
@@ -4268,7 +4270,7 @@
       <c r="G64" s="3"/>
       <c r="H64" s="8"/>
     </row>
-    <row r="65" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>300000</v>
       </c>
@@ -4286,7 +4288,7 @@
       <c r="G65" s="3"/>
       <c r="H65" s="8"/>
     </row>
-    <row r="66" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>200000</v>
       </c>
@@ -4304,7 +4306,7 @@
       <c r="G66" s="3"/>
       <c r="H66" s="8"/>
     </row>
-    <row r="67" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>100000</v>
       </c>
@@ -4322,7 +4324,7 @@
       <c r="G67" s="3"/>
       <c r="H67" s="8"/>
     </row>
-    <row r="68" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>140000</v>
       </c>
@@ -4340,7 +4342,7 @@
       <c r="G68" s="3"/>
       <c r="H68" s="8"/>
     </row>
-    <row r="69" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>114000</v>
       </c>
@@ -4358,7 +4360,7 @@
       <c r="G69" s="3"/>
       <c r="H69" s="8"/>
     </row>
-    <row r="70" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>186000</v>
       </c>
@@ -4376,7 +4378,7 @@
       <c r="G70" s="3"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>500000</v>
       </c>
@@ -4394,7 +4396,7 @@
       <c r="G71" s="3"/>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>200000</v>
       </c>
@@ -4412,7 +4414,7 @@
       <c r="G72" s="3"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>8000</v>
       </c>
@@ -4430,7 +4432,7 @@
       <c r="G73" s="3"/>
       <c r="H73" s="8"/>
     </row>
-    <row r="74" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>350000</v>
       </c>
@@ -4448,7 +4450,7 @@
       <c r="G74" s="3"/>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>250000</v>
       </c>
@@ -4466,7 +4468,7 @@
       <c r="G75" s="3"/>
       <c r="H75" s="8"/>
     </row>
-    <row r="76" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="21"/>
       <c r="B76" s="22"/>
       <c r="C76" s="3">
@@ -4480,7 +4482,7 @@
       <c r="G76" s="3"/>
       <c r="H76" s="8"/>
     </row>
-    <row r="77" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>500000</v>
       </c>
@@ -4498,7 +4500,7 @@
       <c r="G77" s="3"/>
       <c r="H77" s="8"/>
     </row>
-    <row r="78" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>200000</v>
       </c>
@@ -4516,7 +4518,7 @@
       <c r="G78" s="3"/>
       <c r="H78" s="8"/>
     </row>
-    <row r="79" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>85000</v>
       </c>
@@ -4534,7 +4536,7 @@
       <c r="G79" s="3"/>
       <c r="H79" s="8"/>
     </row>
-    <row r="80" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>15000</v>
       </c>
@@ -4552,7 +4554,7 @@
       <c r="G80" s="3"/>
       <c r="H80" s="8"/>
     </row>
-    <row r="81" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>100000</v>
       </c>
@@ -4570,7 +4572,7 @@
       <c r="G81" s="3"/>
       <c r="H81" s="8"/>
     </row>
-    <row r="82" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>150000</v>
       </c>
@@ -4588,7 +4590,7 @@
       <c r="G82" s="3"/>
       <c r="H82" s="8"/>
     </row>
-    <row r="83" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>200000</v>
       </c>
@@ -4606,7 +4608,7 @@
       <c r="G83" s="3"/>
       <c r="H83" s="8"/>
     </row>
-    <row r="84" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>200000</v>
       </c>
@@ -4624,7 +4626,7 @@
       <c r="G84" s="3"/>
       <c r="H84" s="8"/>
     </row>
-    <row r="85" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>450000</v>
       </c>
@@ -4642,7 +4644,7 @@
       <c r="G85" s="3"/>
       <c r="H85" s="8"/>
     </row>
-    <row r="86" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>200000</v>
       </c>
@@ -4660,7 +4662,7 @@
       <c r="G86" s="3"/>
       <c r="H86" s="8"/>
     </row>
-    <row r="87" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>500000</v>
       </c>
@@ -4678,7 +4680,7 @@
       <c r="G87" s="3"/>
       <c r="H87" s="8"/>
     </row>
-    <row r="88" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>440000</v>
       </c>
@@ -4696,7 +4698,7 @@
       <c r="G88" s="3"/>
       <c r="H88" s="8"/>
     </row>
-    <row r="89" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>60000</v>
       </c>
@@ -4714,7 +4716,7 @@
       <c r="G89" s="3"/>
       <c r="H89" s="8"/>
     </row>
-    <row r="90" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>230000</v>
       </c>
@@ -4732,7 +4734,7 @@
       <c r="G90" s="3"/>
       <c r="H90" s="8"/>
     </row>
-    <row r="91" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>315000</v>
       </c>
@@ -4750,7 +4752,7 @@
       <c r="G91" s="3"/>
       <c r="H91" s="8"/>
     </row>
-    <row r="92" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>256000</v>
       </c>
@@ -4764,7 +4766,7 @@
       <c r="G92" s="3"/>
       <c r="H92" s="8"/>
     </row>
-    <row r="93" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>300000</v>
       </c>
@@ -4782,7 +4784,7 @@
       <c r="G93" s="3"/>
       <c r="H93" s="8"/>
     </row>
-    <row r="94" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>140000</v>
       </c>
@@ -4800,7 +4802,7 @@
       <c r="G94" s="3"/>
       <c r="H94" s="8"/>
     </row>
-    <row r="95" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>68000</v>
       </c>
@@ -4818,7 +4820,7 @@
       <c r="G95" s="3"/>
       <c r="H95" s="8"/>
     </row>
-    <row r="96" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>63000</v>
       </c>
@@ -4836,7 +4838,7 @@
       <c r="G96" s="3"/>
       <c r="H96" s="8"/>
     </row>
-    <row r="97" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>150000</v>
       </c>
@@ -4854,7 +4856,7 @@
       <c r="G97" s="3"/>
       <c r="H97" s="8"/>
     </row>
-    <row r="98" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>150000</v>
       </c>
@@ -4872,7 +4874,7 @@
       <c r="G98" s="3"/>
       <c r="H98" s="8"/>
     </row>
-    <row r="99" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>150000</v>
       </c>
@@ -4890,7 +4892,7 @@
       <c r="G99" s="3"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>300000</v>
       </c>
@@ -4908,7 +4910,7 @@
       <c r="G100" s="3"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>200000</v>
       </c>
@@ -4926,7 +4928,7 @@
       <c r="G101" s="3"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>485000</v>
       </c>
@@ -4944,7 +4946,7 @@
       <c r="G102" s="3"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>200000</v>
       </c>
@@ -4962,7 +4964,7 @@
       <c r="G103" s="3"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>500000</v>
       </c>
@@ -4980,7 +4982,7 @@
       <c r="G104" s="3"/>
       <c r="H104" s="8"/>
     </row>
-    <row r="105" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>200000</v>
       </c>
@@ -4998,7 +5000,7 @@
       <c r="G105" s="3"/>
       <c r="H105" s="8"/>
     </row>
-    <row r="106" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>100000</v>
       </c>
@@ -5016,7 +5018,7 @@
       <c r="G106" s="3"/>
       <c r="H106" s="8"/>
     </row>
-    <row r="107" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>100000</v>
       </c>
@@ -5034,7 +5036,7 @@
       <c r="G107" s="3"/>
       <c r="H107" s="8"/>
     </row>
-    <row r="108" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>500000</v>
       </c>
@@ -5052,7 +5054,7 @@
       <c r="G108" s="3"/>
       <c r="H108" s="8"/>
     </row>
-    <row r="109" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>150000</v>
       </c>
@@ -5070,7 +5072,7 @@
       <c r="G109" s="3"/>
       <c r="H109" s="8"/>
     </row>
-    <row r="110" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>200000</v>
       </c>
@@ -5088,7 +5090,7 @@
       <c r="G110" s="3"/>
       <c r="H110" s="8"/>
     </row>
-    <row r="111" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>200000</v>
       </c>
@@ -5106,7 +5108,7 @@
       <c r="G111" s="3"/>
       <c r="H111" s="8"/>
     </row>
-    <row r="112" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>100000</v>
       </c>
@@ -5124,7 +5126,7 @@
       <c r="G112" s="3"/>
       <c r="H112" s="8"/>
     </row>
-    <row r="113" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>130000</v>
       </c>
@@ -5142,7 +5144,7 @@
       <c r="G113" s="3"/>
       <c r="H113" s="8"/>
     </row>
-    <row r="114" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>300000</v>
       </c>
@@ -5160,7 +5162,7 @@
       <c r="G114" s="3"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>100000</v>
       </c>
@@ -5178,7 +5180,7 @@
       <c r="G115" s="3"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>300000</v>
       </c>
@@ -5196,7 +5198,7 @@
       <c r="G116" s="3"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>120000</v>
       </c>
@@ -5214,7 +5216,7 @@
       <c r="G117" s="3"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>80000</v>
       </c>
@@ -5232,7 +5234,7 @@
       <c r="G118" s="3"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="39"/>
       <c r="B119" s="25"/>
       <c r="C119" s="3">
@@ -5246,7 +5248,7 @@
       <c r="G119" s="3"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="8"/>
       <c r="C120" s="3">
@@ -5260,7 +5262,7 @@
       <c r="G120" s="3"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="8"/>
       <c r="C121" s="3">
@@ -5274,7 +5276,7 @@
       <c r="G121" s="3"/>
       <c r="H121" s="8"/>
     </row>
-    <row r="122" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="8"/>
       <c r="C122" s="3">
@@ -5288,7 +5290,7 @@
       <c r="G122" s="3"/>
       <c r="H122" s="8"/>
     </row>
-    <row r="123" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="8"/>
       <c r="C123" s="3">
@@ -5302,7 +5304,7 @@
       <c r="G123" s="3"/>
       <c r="H123" s="8"/>
     </row>
-    <row r="124" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="8"/>
       <c r="C124" s="3">
@@ -5316,7 +5318,7 @@
       <c r="G124" s="3"/>
       <c r="H124" s="8"/>
     </row>
-    <row r="125" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="8"/>
       <c r="C125" s="3">
@@ -5330,7 +5332,7 @@
       <c r="G125" s="3"/>
       <c r="H125" s="8"/>
     </row>
-    <row r="126" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="8"/>
       <c r="C126" s="3">
@@ -5344,7 +5346,7 @@
       <c r="G126" s="3"/>
       <c r="H126" s="8"/>
     </row>
-    <row r="127" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="8"/>
       <c r="C127" s="3">
@@ -5358,7 +5360,7 @@
       <c r="G127" s="3"/>
       <c r="H127" s="8"/>
     </row>
-    <row r="128" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="8"/>
       <c r="C128" s="3">
@@ -5372,7 +5374,7 @@
       <c r="G128" s="3"/>
       <c r="H128" s="8"/>
     </row>
-    <row r="129" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="8"/>
       <c r="C129" s="3">
@@ -5386,7 +5388,7 @@
       <c r="G129" s="3"/>
       <c r="H129" s="8"/>
     </row>
-    <row r="130" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="8"/>
       <c r="C130" s="3">
@@ -5400,7 +5402,7 @@
       <c r="G130" s="3"/>
       <c r="H130" s="8"/>
     </row>
-    <row r="131" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="8"/>
       <c r="C131" s="3">
@@ -5414,7 +5416,7 @@
       <c r="G131" s="3"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="8"/>
       <c r="C132" s="3">
@@ -5428,7 +5430,7 @@
       <c r="G132" s="3"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="8"/>
       <c r="C133" s="3">
@@ -5442,7 +5444,7 @@
       <c r="G133" s="3"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="8"/>
       <c r="C134" s="3">
@@ -5456,7 +5458,7 @@
       <c r="G134" s="3"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="8"/>
       <c r="C135" s="3">
@@ -5470,7 +5472,7 @@
       <c r="G135" s="3"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="8"/>
       <c r="C136" s="3">
@@ -5484,7 +5486,7 @@
       <c r="G136" s="3"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="8"/>
       <c r="C137" s="3">
@@ -5498,7 +5500,7 @@
       <c r="G137" s="3"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="8"/>
       <c r="C138" s="3">
@@ -5512,7 +5514,7 @@
       <c r="G138" s="3"/>
       <c r="H138" s="8"/>
     </row>
-    <row r="139" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="8"/>
       <c r="C139" s="3">
@@ -5526,7 +5528,7 @@
       <c r="G139" s="3"/>
       <c r="H139" s="8"/>
     </row>
-    <row r="140" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="8"/>
       <c r="C140" s="3">
@@ -5540,7 +5542,7 @@
       <c r="G140" s="3"/>
       <c r="H140" s="8"/>
     </row>
-    <row r="141" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="8"/>
       <c r="C141" s="3">
@@ -5554,7 +5556,7 @@
       <c r="G141" s="3"/>
       <c r="H141" s="8"/>
     </row>
-    <row r="142" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="8"/>
       <c r="C142" s="3">
@@ -5568,7 +5570,7 @@
       <c r="G142" s="3"/>
       <c r="H142" s="8"/>
     </row>
-    <row r="143" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="8"/>
       <c r="C143" s="3">
@@ -5582,7 +5584,7 @@
       <c r="G143" s="3"/>
       <c r="H143" s="8"/>
     </row>
-    <row r="144" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="8"/>
       <c r="C144" s="3">
@@ -5596,7 +5598,7 @@
       <c r="G144" s="3"/>
       <c r="H144" s="8"/>
     </row>
-    <row r="145" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="8"/>
       <c r="C145" s="3">
@@ -5610,7 +5612,7 @@
       <c r="G145" s="3"/>
       <c r="H145" s="8"/>
     </row>
-    <row r="146" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="8"/>
       <c r="C146" s="3">
@@ -5624,7 +5626,7 @@
       <c r="G146" s="3"/>
       <c r="H146" s="8"/>
     </row>
-    <row r="147" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="8"/>
       <c r="C147" s="3">
@@ -5638,7 +5640,7 @@
       <c r="G147" s="3"/>
       <c r="H147" s="8"/>
     </row>
-    <row r="148" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
       <c r="B148" s="8"/>
       <c r="C148" s="3">
@@ -5652,7 +5654,7 @@
       <c r="G148" s="3"/>
       <c r="H148" s="8"/>
     </row>
-    <row r="149" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="8"/>
       <c r="C149" s="3">
@@ -5666,7 +5668,7 @@
       <c r="G149" s="3"/>
       <c r="H149" s="8"/>
     </row>
-    <row r="150" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
       <c r="B150" s="8"/>
       <c r="C150" s="3">
@@ -5680,7 +5682,7 @@
       <c r="G150" s="3"/>
       <c r="H150" s="8"/>
     </row>
-    <row r="151" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
       <c r="B151" s="8"/>
       <c r="C151" s="3">
@@ -5694,7 +5696,7 @@
       <c r="G151" s="3"/>
       <c r="H151" s="8"/>
     </row>
-    <row r="152" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
       <c r="B152" s="8"/>
       <c r="C152" s="3">
@@ -5708,7 +5710,7 @@
       <c r="G152" s="3"/>
       <c r="H152" s="8"/>
     </row>
-    <row r="153" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3"/>
       <c r="B153" s="8"/>
       <c r="C153" s="3">
@@ -5722,7 +5724,7 @@
       <c r="G153" s="3"/>
       <c r="H153" s="8"/>
     </row>
-    <row r="154" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3"/>
       <c r="B154" s="8"/>
       <c r="C154" s="3">
@@ -5736,7 +5738,7 @@
       <c r="G154" s="3"/>
       <c r="H154" s="8"/>
     </row>
-    <row r="155" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
       <c r="B155" s="8"/>
       <c r="C155" s="3">
@@ -5750,7 +5752,7 @@
       <c r="G155" s="3"/>
       <c r="H155" s="8"/>
     </row>
-    <row r="156" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
       <c r="B156" s="8"/>
       <c r="C156" s="3">
@@ -5764,7 +5766,7 @@
       <c r="G156" s="3"/>
       <c r="H156" s="8"/>
     </row>
-    <row r="157" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3"/>
       <c r="B157" s="8"/>
       <c r="C157" s="3">
@@ -5778,7 +5780,7 @@
       <c r="G157" s="3"/>
       <c r="H157" s="8"/>
     </row>
-    <row r="158" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3"/>
       <c r="B158" s="8"/>
       <c r="C158" s="3">
@@ -5792,7 +5794,7 @@
       <c r="G158" s="3"/>
       <c r="H158" s="8"/>
     </row>
-    <row r="159" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
       <c r="B159" s="8"/>
       <c r="C159" s="3">
@@ -5806,7 +5808,7 @@
       <c r="G159" s="3"/>
       <c r="H159" s="8"/>
     </row>
-    <row r="160" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
       <c r="B160" s="8"/>
       <c r="C160" s="3">
@@ -5820,7 +5822,7 @@
       <c r="G160" s="3"/>
       <c r="H160" s="8"/>
     </row>
-    <row r="161" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3"/>
       <c r="B161" s="8"/>
       <c r="C161" s="3">
@@ -5834,7 +5836,7 @@
       <c r="G161" s="3"/>
       <c r="H161" s="8"/>
     </row>
-    <row r="162" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3"/>
       <c r="B162" s="8"/>
       <c r="C162" s="3">
@@ -5848,7 +5850,7 @@
       <c r="G162" s="3"/>
       <c r="H162" s="8"/>
     </row>
-    <row r="163" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
       <c r="B163" s="8"/>
       <c r="C163" s="3">
@@ -5862,7 +5864,7 @@
       <c r="G163" s="3"/>
       <c r="H163" s="8"/>
     </row>
-    <row r="164" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3"/>
       <c r="B164" s="8"/>
       <c r="C164" s="3">
@@ -5876,7 +5878,7 @@
       <c r="G164" s="3"/>
       <c r="H164" s="8"/>
     </row>
-    <row r="165" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3"/>
       <c r="B165" s="8"/>
       <c r="C165" s="3">
@@ -5890,7 +5892,7 @@
       <c r="G165" s="3"/>
       <c r="H165" s="8"/>
     </row>
-    <row r="166" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3"/>
       <c r="B166" s="8"/>
       <c r="C166" s="3">
@@ -5904,7 +5906,7 @@
       <c r="G166" s="3"/>
       <c r="H166" s="8"/>
     </row>
-    <row r="167" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
       <c r="B167" s="8"/>
       <c r="C167" s="3">
@@ -5918,7 +5920,7 @@
       <c r="G167" s="3"/>
       <c r="H167" s="8"/>
     </row>
-    <row r="168" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3"/>
       <c r="B168" s="8"/>
       <c r="C168" s="3">
@@ -5932,7 +5934,7 @@
       <c r="G168" s="3"/>
       <c r="H168" s="8"/>
     </row>
-    <row r="169" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3"/>
       <c r="B169" s="8"/>
       <c r="C169" s="3">
@@ -5946,7 +5948,7 @@
       <c r="G169" s="3"/>
       <c r="H169" s="8"/>
     </row>
-    <row r="170" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3"/>
       <c r="B170" s="8"/>
       <c r="C170" s="3">
@@ -5960,7 +5962,7 @@
       <c r="G170" s="3"/>
       <c r="H170" s="8"/>
     </row>
-    <row r="171" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
       <c r="B171" s="8"/>
       <c r="C171" s="3">
@@ -5974,7 +5976,7 @@
       <c r="G171" s="3"/>
       <c r="H171" s="8"/>
     </row>
-    <row r="172" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
       <c r="B172" s="8"/>
       <c r="C172" s="3">
@@ -5988,7 +5990,7 @@
       <c r="G172" s="3"/>
       <c r="H172" s="8"/>
     </row>
-    <row r="173" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3"/>
       <c r="B173" s="8"/>
       <c r="C173" s="3">
@@ -6002,7 +6004,7 @@
       <c r="G173" s="3"/>
       <c r="H173" s="8"/>
     </row>
-    <row r="174" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3"/>
       <c r="B174" s="8"/>
       <c r="C174" s="3">
@@ -6016,7 +6018,7 @@
       <c r="G174" s="3"/>
       <c r="H174" s="8"/>
     </row>
-    <row r="175" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
       <c r="B175" s="8"/>
       <c r="C175" s="3">
@@ -6030,7 +6032,7 @@
       <c r="G175" s="3"/>
       <c r="H175" s="8"/>
     </row>
-    <row r="176" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
       <c r="B176" s="8"/>
       <c r="C176" s="3">
@@ -6044,7 +6046,7 @@
       <c r="G176" s="3"/>
       <c r="H176" s="8"/>
     </row>
-    <row r="177" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3"/>
       <c r="B177" s="8"/>
       <c r="C177" s="3">
@@ -6058,7 +6060,7 @@
       <c r="G177" s="3"/>
       <c r="H177" s="8"/>
     </row>
-    <row r="178" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3"/>
       <c r="B178" s="8"/>
       <c r="C178" s="3">
@@ -6072,7 +6074,7 @@
       <c r="G178" s="3"/>
       <c r="H178" s="8"/>
     </row>
-    <row r="179" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
       <c r="B179" s="8"/>
       <c r="C179" s="3">
@@ -6086,7 +6088,7 @@
       <c r="G179" s="3"/>
       <c r="H179" s="8"/>
     </row>
-    <row r="180" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
       <c r="B180" s="8"/>
       <c r="C180" s="3">
@@ -6100,7 +6102,7 @@
       <c r="G180" s="3"/>
       <c r="H180" s="8"/>
     </row>
-    <row r="181" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3"/>
       <c r="B181" s="8"/>
       <c r="C181" s="3">
@@ -6114,7 +6116,7 @@
       <c r="G181" s="3"/>
       <c r="H181" s="8"/>
     </row>
-    <row r="182" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3"/>
       <c r="B182" s="8"/>
       <c r="C182" s="3">
@@ -6128,7 +6130,7 @@
       <c r="G182" s="3"/>
       <c r="H182" s="8"/>
     </row>
-    <row r="183" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
       <c r="B183" s="8"/>
       <c r="C183" s="21"/>
@@ -6138,7 +6140,7 @@
       <c r="G183" s="3"/>
       <c r="H183" s="8"/>
     </row>
-    <row r="184" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
       <c r="B184" s="8"/>
       <c r="C184" s="3">
@@ -6152,7 +6154,7 @@
       <c r="G184" s="3"/>
       <c r="H184" s="8"/>
     </row>
-    <row r="185" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3"/>
       <c r="B185" s="8"/>
       <c r="C185" s="3">
@@ -6166,7 +6168,7 @@
       <c r="G185" s="3"/>
       <c r="H185" s="8"/>
     </row>
-    <row r="186" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3"/>
       <c r="B186" s="8"/>
       <c r="C186" s="3">
@@ -6180,7 +6182,7 @@
       <c r="G186" s="3"/>
       <c r="H186" s="8"/>
     </row>
-    <row r="187" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
       <c r="B187" s="8"/>
       <c r="C187" s="3">
@@ -6194,7 +6196,7 @@
       <c r="G187" s="3"/>
       <c r="H187" s="8"/>
     </row>
-    <row r="188" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3"/>
       <c r="B188" s="8"/>
       <c r="C188" s="3">
@@ -6208,7 +6210,7 @@
       <c r="G188" s="3"/>
       <c r="H188" s="8"/>
     </row>
-    <row r="189" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3"/>
       <c r="B189" s="8"/>
       <c r="C189" s="3">
@@ -6222,7 +6224,7 @@
       <c r="G189" s="3"/>
       <c r="H189" s="8"/>
     </row>
-    <row r="190" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3"/>
       <c r="B190" s="8"/>
       <c r="C190" s="3">
@@ -6236,7 +6238,7 @@
       <c r="G190" s="3"/>
       <c r="H190" s="8"/>
     </row>
-    <row r="191" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3"/>
       <c r="B191" s="8"/>
       <c r="C191" s="3">
@@ -6250,7 +6252,7 @@
       <c r="G191" s="3"/>
       <c r="H191" s="8"/>
     </row>
-    <row r="192" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3"/>
       <c r="B192" s="8"/>
       <c r="C192" s="3">
@@ -6264,7 +6266,7 @@
       <c r="G192" s="3"/>
       <c r="H192" s="8"/>
     </row>
-    <row r="193" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3"/>
       <c r="B193" s="8"/>
       <c r="C193" s="3">
@@ -6278,7 +6280,7 @@
       <c r="G193" s="3"/>
       <c r="H193" s="8"/>
     </row>
-    <row r="194" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3"/>
       <c r="B194" s="8"/>
       <c r="C194" s="3">
@@ -6292,7 +6294,7 @@
       <c r="G194" s="3"/>
       <c r="H194" s="8"/>
     </row>
-    <row r="195" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3"/>
       <c r="B195" s="8"/>
       <c r="C195" s="3">
@@ -6306,7 +6308,7 @@
       <c r="G195" s="3"/>
       <c r="H195" s="8"/>
     </row>
-    <row r="196" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3"/>
       <c r="B196" s="8"/>
       <c r="C196" s="3">
@@ -6320,7 +6322,7 @@
       <c r="G196" s="3"/>
       <c r="H196" s="8"/>
     </row>
-    <row r="197" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3"/>
       <c r="B197" s="8"/>
       <c r="C197" s="3">
@@ -6334,7 +6336,7 @@
       <c r="G197" s="3"/>
       <c r="H197" s="8"/>
     </row>
-    <row r="198" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3"/>
       <c r="B198" s="8"/>
       <c r="C198" s="3">
@@ -6348,7 +6350,7 @@
       <c r="G198" s="3"/>
       <c r="H198" s="8"/>
     </row>
-    <row r="199" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3"/>
       <c r="B199" s="8"/>
       <c r="C199" s="3">
@@ -6362,7 +6364,7 @@
       <c r="G199" s="3"/>
       <c r="H199" s="8"/>
     </row>
-    <row r="200" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3"/>
       <c r="B200" s="8"/>
       <c r="C200" s="3">
@@ -6376,7 +6378,7 @@
       <c r="G200" s="3"/>
       <c r="H200" s="8"/>
     </row>
-    <row r="201" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3"/>
       <c r="B201" s="8"/>
       <c r="C201" s="3">
@@ -6390,7 +6392,7 @@
       <c r="G201" s="3"/>
       <c r="H201" s="8"/>
     </row>
-    <row r="202" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3"/>
       <c r="B202" s="8"/>
       <c r="C202" s="3">
@@ -6404,7 +6406,7 @@
       <c r="G202" s="3"/>
       <c r="H202" s="8"/>
     </row>
-    <row r="203" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3"/>
       <c r="B203" s="8"/>
       <c r="C203" s="3">
@@ -6418,7 +6420,7 @@
       <c r="G203" s="3"/>
       <c r="H203" s="8"/>
     </row>
-    <row r="204" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3"/>
       <c r="B204" s="8"/>
       <c r="C204" s="3">
@@ -6432,7 +6434,7 @@
       <c r="G204" s="3"/>
       <c r="H204" s="8"/>
     </row>
-    <row r="205" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3"/>
       <c r="B205" s="8"/>
       <c r="C205" s="3">
@@ -6446,7 +6448,7 @@
       <c r="G205" s="3"/>
       <c r="H205" s="8"/>
     </row>
-    <row r="206" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3"/>
       <c r="B206" s="8"/>
       <c r="C206" s="3">
@@ -6460,7 +6462,7 @@
       <c r="G206" s="3"/>
       <c r="H206" s="8"/>
     </row>
-    <row r="207" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3"/>
       <c r="B207" s="8"/>
       <c r="C207" s="3">
@@ -6474,7 +6476,7 @@
       <c r="G207" s="3"/>
       <c r="H207" s="8"/>
     </row>
-    <row r="208" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3"/>
       <c r="B208" s="8"/>
       <c r="C208" s="3">
@@ -6488,7 +6490,7 @@
       <c r="G208" s="3"/>
       <c r="H208" s="8"/>
     </row>
-    <row r="209" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3"/>
       <c r="B209" s="8"/>
       <c r="C209" s="3">
@@ -6502,7 +6504,7 @@
       <c r="G209" s="3"/>
       <c r="H209" s="8"/>
     </row>
-    <row r="210" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3"/>
       <c r="B210" s="8"/>
       <c r="C210" s="3">
@@ -6516,7 +6518,7 @@
       <c r="G210" s="3"/>
       <c r="H210" s="8"/>
     </row>
-    <row r="211" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3"/>
       <c r="B211" s="8"/>
       <c r="C211" s="3">
@@ -6530,7 +6532,7 @@
       <c r="G211" s="3"/>
       <c r="H211" s="8"/>
     </row>
-    <row r="212" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3"/>
       <c r="B212" s="8"/>
       <c r="C212" s="3">
@@ -6544,7 +6546,7 @@
       <c r="G212" s="3"/>
       <c r="H212" s="8"/>
     </row>
-    <row r="213" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3"/>
       <c r="B213" s="8"/>
       <c r="C213" s="3">
@@ -6558,7 +6560,7 @@
       <c r="G213" s="3"/>
       <c r="H213" s="8"/>
     </row>
-    <row r="214" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3"/>
       <c r="B214" s="8"/>
       <c r="C214" s="3">
@@ -6572,7 +6574,7 @@
       <c r="G214" s="3"/>
       <c r="H214" s="8"/>
     </row>
-    <row r="215" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3"/>
       <c r="B215" s="8"/>
       <c r="C215" s="3">
@@ -6586,7 +6588,7 @@
       <c r="G215" s="3"/>
       <c r="H215" s="8"/>
     </row>
-    <row r="216" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3"/>
       <c r="B216" s="8"/>
       <c r="C216" s="3">
@@ -6600,7 +6602,7 @@
       <c r="G216" s="3"/>
       <c r="H216" s="8"/>
     </row>
-    <row r="217" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3"/>
       <c r="B217" s="8"/>
       <c r="C217" s="3">
@@ -6614,7 +6616,7 @@
       <c r="G217" s="3"/>
       <c r="H217" s="8"/>
     </row>
-    <row r="218" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3"/>
       <c r="B218" s="8"/>
       <c r="C218" s="3">
@@ -6628,7 +6630,7 @@
       <c r="G218" s="3"/>
       <c r="H218" s="8"/>
     </row>
-    <row r="219" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3"/>
       <c r="B219" s="8"/>
       <c r="C219" s="3">
@@ -6642,7 +6644,7 @@
       <c r="G219" s="3"/>
       <c r="H219" s="8"/>
     </row>
-    <row r="220" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3"/>
       <c r="B220" s="8"/>
       <c r="C220" s="3">
@@ -6656,7 +6658,7 @@
       <c r="G220" s="3"/>
       <c r="H220" s="8"/>
     </row>
-    <row r="221" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3"/>
       <c r="B221" s="8"/>
       <c r="C221" s="3">
@@ -6670,7 +6672,7 @@
       <c r="G221" s="3"/>
       <c r="H221" s="8"/>
     </row>
-    <row r="222" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3"/>
       <c r="B222" s="8"/>
       <c r="C222" s="3">
@@ -6684,7 +6686,7 @@
       <c r="G222" s="3"/>
       <c r="H222" s="8"/>
     </row>
-    <row r="223" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3"/>
       <c r="B223" s="8"/>
       <c r="C223" s="3">
@@ -6698,7 +6700,7 @@
       <c r="G223" s="3"/>
       <c r="H223" s="8"/>
     </row>
-    <row r="224" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3"/>
       <c r="B224" s="8"/>
       <c r="C224" s="3">
@@ -6712,7 +6714,7 @@
       <c r="G224" s="3"/>
       <c r="H224" s="8"/>
     </row>
-    <row r="225" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3"/>
       <c r="B225" s="8"/>
       <c r="C225" s="3">
@@ -6726,7 +6728,7 @@
       <c r="G225" s="3"/>
       <c r="H225" s="8"/>
     </row>
-    <row r="226" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3"/>
       <c r="B226" s="8"/>
       <c r="C226" s="3">
@@ -6740,7 +6742,7 @@
       <c r="G226" s="3"/>
       <c r="H226" s="8"/>
     </row>
-    <row r="227" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3"/>
       <c r="B227" s="8"/>
       <c r="C227" s="3">
@@ -6754,7 +6756,7 @@
       <c r="G227" s="3"/>
       <c r="H227" s="8"/>
     </row>
-    <row r="228" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3"/>
       <c r="B228" s="8"/>
       <c r="C228" s="3">
@@ -6768,7 +6770,7 @@
       <c r="G228" s="3"/>
       <c r="H228" s="8"/>
     </row>
-    <row r="229" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3"/>
       <c r="B229" s="8"/>
       <c r="C229" s="3">
@@ -6782,7 +6784,7 @@
       <c r="G229" s="3"/>
       <c r="H229" s="8"/>
     </row>
-    <row r="230" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3"/>
       <c r="B230" s="8"/>
       <c r="C230" s="3">
@@ -6796,7 +6798,7 @@
       <c r="G230" s="3"/>
       <c r="H230" s="8"/>
     </row>
-    <row r="231" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3"/>
       <c r="B231" s="8"/>
       <c r="C231" s="3">
@@ -6810,7 +6812,7 @@
       <c r="G231" s="3"/>
       <c r="H231" s="8"/>
     </row>
-    <row r="232" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3"/>
       <c r="B232" s="8"/>
       <c r="C232" s="3">
@@ -6824,7 +6826,7 @@
       <c r="G232" s="3"/>
       <c r="H232" s="8"/>
     </row>
-    <row r="233" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3"/>
       <c r="B233" s="8"/>
       <c r="C233" s="3">
@@ -6838,7 +6840,7 @@
       <c r="G233" s="3"/>
       <c r="H233" s="8"/>
     </row>
-    <row r="234" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3"/>
       <c r="B234" s="8"/>
       <c r="C234" s="3">
@@ -6852,7 +6854,7 @@
       <c r="G234" s="3"/>
       <c r="H234" s="8"/>
     </row>
-    <row r="235" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3"/>
       <c r="B235" s="8"/>
       <c r="C235" s="3">
@@ -6866,7 +6868,7 @@
       <c r="G235" s="3"/>
       <c r="H235" s="8"/>
     </row>
-    <row r="236" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3"/>
       <c r="B236" s="8"/>
       <c r="C236" s="3">
@@ -6880,7 +6882,7 @@
       <c r="G236" s="3"/>
       <c r="H236" s="8"/>
     </row>
-    <row r="237" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3"/>
       <c r="B237" s="8"/>
       <c r="C237" s="3">
@@ -6894,7 +6896,7 @@
       <c r="G237" s="3"/>
       <c r="H237" s="8"/>
     </row>
-    <row r="238" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3"/>
       <c r="B238" s="8"/>
       <c r="C238" s="3">
@@ -6908,7 +6910,7 @@
       <c r="G238" s="3"/>
       <c r="H238" s="8"/>
     </row>
-    <row r="239" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3"/>
       <c r="B239" s="8"/>
       <c r="C239" s="3">
@@ -6922,7 +6924,7 @@
       <c r="G239" s="3"/>
       <c r="H239" s="8"/>
     </row>
-    <row r="240" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3"/>
       <c r="B240" s="8"/>
       <c r="C240" s="3">
@@ -6936,7 +6938,7 @@
       <c r="G240" s="3"/>
       <c r="H240" s="8"/>
     </row>
-    <row r="241" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3"/>
       <c r="B241" s="8"/>
       <c r="C241" s="3">
@@ -6950,7 +6952,7 @@
       <c r="G241" s="3"/>
       <c r="H241" s="8"/>
     </row>
-    <row r="242" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3"/>
       <c r="B242" s="8"/>
       <c r="C242" s="3">
@@ -6964,7 +6966,7 @@
       <c r="G242" s="3"/>
       <c r="H242" s="8"/>
     </row>
-    <row r="243" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3"/>
       <c r="B243" s="8"/>
       <c r="C243" s="3">
@@ -6978,7 +6980,7 @@
       <c r="G243" s="3"/>
       <c r="H243" s="8"/>
     </row>
-    <row r="244" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3"/>
       <c r="B244" s="8"/>
       <c r="C244" s="3">
@@ -6992,7 +6994,7 @@
       <c r="G244" s="3"/>
       <c r="H244" s="8"/>
     </row>
-    <row r="245" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3"/>
       <c r="B245" s="8"/>
       <c r="C245" s="3">
@@ -7006,7 +7008,7 @@
       <c r="G245" s="3"/>
       <c r="H245" s="8"/>
     </row>
-    <row r="246" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3"/>
       <c r="B246" s="8"/>
       <c r="C246" s="3">
@@ -7020,7 +7022,7 @@
       <c r="G246" s="3"/>
       <c r="H246" s="8"/>
     </row>
-    <row r="247" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3"/>
       <c r="B247" s="8"/>
       <c r="C247" s="3">
@@ -7034,7 +7036,7 @@
       <c r="G247" s="3"/>
       <c r="H247" s="8"/>
     </row>
-    <row r="248" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3"/>
       <c r="B248" s="8"/>
       <c r="C248" s="3">
@@ -7048,7 +7050,7 @@
       <c r="G248" s="3"/>
       <c r="H248" s="8"/>
     </row>
-    <row r="249" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3"/>
       <c r="B249" s="8"/>
       <c r="C249" s="3">
@@ -7062,7 +7064,7 @@
       <c r="G249" s="3"/>
       <c r="H249" s="8"/>
     </row>
-    <row r="250" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3"/>
       <c r="B250" s="8"/>
       <c r="C250" s="3">
@@ -7076,7 +7078,7 @@
       <c r="G250" s="3"/>
       <c r="H250" s="8"/>
     </row>
-    <row r="251" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3"/>
       <c r="B251" s="8"/>
       <c r="C251" s="3">
@@ -7090,7 +7092,7 @@
       <c r="G251" s="3"/>
       <c r="H251" s="8"/>
     </row>
-    <row r="252" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3"/>
       <c r="B252" s="8"/>
       <c r="C252" s="3">
@@ -7104,7 +7106,7 @@
       <c r="G252" s="3"/>
       <c r="H252" s="8"/>
     </row>
-    <row r="253" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3"/>
       <c r="B253" s="8"/>
       <c r="C253" s="3">
@@ -7118,7 +7120,7 @@
       <c r="G253" s="3"/>
       <c r="H253" s="8"/>
     </row>
-    <row r="254" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3"/>
       <c r="B254" s="8"/>
       <c r="C254" s="3">
@@ -7132,7 +7134,7 @@
       <c r="G254" s="3"/>
       <c r="H254" s="8"/>
     </row>
-    <row r="255" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3"/>
       <c r="B255" s="8"/>
       <c r="C255" s="3">
@@ -7146,7 +7148,7 @@
       <c r="G255" s="3"/>
       <c r="H255" s="8"/>
     </row>
-    <row r="256" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3"/>
       <c r="B256" s="8"/>
       <c r="C256" s="3">
@@ -7160,7 +7162,7 @@
       <c r="G256" s="3"/>
       <c r="H256" s="8"/>
     </row>
-    <row r="257" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="3"/>
       <c r="B257" s="8"/>
       <c r="C257" s="3">
@@ -7174,7 +7176,7 @@
       <c r="G257" s="3"/>
       <c r="H257" s="8"/>
     </row>
-    <row r="258" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="3"/>
       <c r="B258" s="8"/>
       <c r="C258" s="3">
@@ -7188,7 +7190,7 @@
       <c r="G258" s="3"/>
       <c r="H258" s="8"/>
     </row>
-    <row r="259" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="3"/>
       <c r="B259" s="8"/>
       <c r="C259" s="3">
@@ -7202,7 +7204,7 @@
       <c r="G259" s="3"/>
       <c r="H259" s="8"/>
     </row>
-    <row r="260" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3"/>
       <c r="B260" s="8"/>
       <c r="C260" s="3">
@@ -7216,7 +7218,7 @@
       <c r="G260" s="3"/>
       <c r="H260" s="8"/>
     </row>
-    <row r="261" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="3"/>
       <c r="B261" s="8"/>
       <c r="C261" s="3">
@@ -7230,7 +7232,7 @@
       <c r="G261" s="3"/>
       <c r="H261" s="8"/>
     </row>
-    <row r="262" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3"/>
       <c r="B262" s="8"/>
       <c r="C262" s="3">
@@ -7244,7 +7246,7 @@
       <c r="G262" s="3"/>
       <c r="H262" s="8"/>
     </row>
-    <row r="263" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3"/>
       <c r="B263" s="8"/>
       <c r="C263" s="3">
@@ -7258,7 +7260,7 @@
       <c r="G263" s="3"/>
       <c r="H263" s="8"/>
     </row>
-    <row r="264" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3"/>
       <c r="B264" s="8"/>
       <c r="C264" s="3">
@@ -7272,7 +7274,7 @@
       <c r="G264" s="3"/>
       <c r="H264" s="8"/>
     </row>
-    <row r="265" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3"/>
       <c r="B265" s="8"/>
       <c r="C265" s="3">
@@ -7286,7 +7288,7 @@
       <c r="G265" s="3"/>
       <c r="H265" s="8"/>
     </row>
-    <row r="266" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3"/>
       <c r="B266" s="8"/>
       <c r="C266" s="3">
@@ -7300,7 +7302,7 @@
       <c r="G266" s="3"/>
       <c r="H266" s="8"/>
     </row>
-    <row r="267" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="3"/>
       <c r="B267" s="8"/>
       <c r="C267" s="3">
@@ -7314,7 +7316,7 @@
       <c r="G267" s="3"/>
       <c r="H267" s="8"/>
     </row>
-    <row r="268" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="3"/>
       <c r="B268" s="8"/>
       <c r="C268" s="3">
@@ -7328,7 +7330,7 @@
       <c r="G268" s="3"/>
       <c r="H268" s="8"/>
     </row>
-    <row r="269" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="3"/>
       <c r="B269" s="8"/>
       <c r="C269" s="3">
@@ -7342,7 +7344,7 @@
       <c r="G269" s="3"/>
       <c r="H269" s="8"/>
     </row>
-    <row r="270" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="3"/>
       <c r="B270" s="8"/>
       <c r="C270" s="3">
@@ -7356,7 +7358,7 @@
       <c r="G270" s="3"/>
       <c r="H270" s="8"/>
     </row>
-    <row r="271" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="3"/>
       <c r="B271" s="8"/>
       <c r="C271" s="3">
@@ -7370,7 +7372,7 @@
       <c r="G271" s="3"/>
       <c r="H271" s="8"/>
     </row>
-    <row r="272" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="3"/>
       <c r="B272" s="8"/>
       <c r="C272" s="3">
@@ -7384,7 +7386,7 @@
       <c r="G272" s="3"/>
       <c r="H272" s="8"/>
     </row>
-    <row r="273" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="3"/>
       <c r="B273" s="8"/>
       <c r="C273" s="3">
@@ -7398,7 +7400,7 @@
       <c r="G273" s="3"/>
       <c r="H273" s="8"/>
     </row>
-    <row r="274" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="3"/>
       <c r="B274" s="8"/>
       <c r="C274" s="3">
@@ -7412,7 +7414,7 @@
       <c r="G274" s="3"/>
       <c r="H274" s="8"/>
     </row>
-    <row r="275" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="3"/>
       <c r="B275" s="8"/>
       <c r="C275" s="3">
@@ -7426,7 +7428,7 @@
       <c r="G275" s="3"/>
       <c r="H275" s="8"/>
     </row>
-    <row r="276" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="3"/>
       <c r="B276" s="8"/>
       <c r="C276" s="3">
@@ -7440,7 +7442,7 @@
       <c r="G276" s="3"/>
       <c r="H276" s="8"/>
     </row>
-    <row r="277" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="3"/>
       <c r="B277" s="8"/>
       <c r="C277" s="3">
@@ -7454,7 +7456,7 @@
       <c r="G277" s="3"/>
       <c r="H277" s="8"/>
     </row>
-    <row r="278" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="3"/>
       <c r="B278" s="8"/>
       <c r="C278" s="3">
@@ -7468,7 +7470,7 @@
       <c r="G278" s="3"/>
       <c r="H278" s="8"/>
     </row>
-    <row r="279" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="3"/>
       <c r="B279" s="8"/>
       <c r="C279" s="3">
@@ -7482,7 +7484,7 @@
       <c r="G279" s="3"/>
       <c r="H279" s="8"/>
     </row>
-    <row r="280" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="3"/>
       <c r="B280" s="8"/>
       <c r="C280" s="3">
@@ -7496,7 +7498,7 @@
       <c r="G280" s="3"/>
       <c r="H280" s="8"/>
     </row>
-    <row r="281" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="3"/>
       <c r="B281" s="8"/>
       <c r="C281" s="3">
@@ -7510,7 +7512,7 @@
       <c r="G281" s="3"/>
       <c r="H281" s="8"/>
     </row>
-    <row r="282" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="3"/>
       <c r="B282" s="8"/>
       <c r="C282" s="3">
@@ -7524,7 +7526,7 @@
       <c r="G282" s="3"/>
       <c r="H282" s="8"/>
     </row>
-    <row r="283" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="3"/>
       <c r="B283" s="8"/>
       <c r="C283" s="3">
@@ -7538,7 +7540,7 @@
       <c r="G283" s="3"/>
       <c r="H283" s="8"/>
     </row>
-    <row r="284" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="3"/>
       <c r="B284" s="8"/>
       <c r="C284" s="3">
@@ -7552,7 +7554,7 @@
       <c r="G284" s="3"/>
       <c r="H284" s="8"/>
     </row>
-    <row r="285" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="3"/>
       <c r="B285" s="8"/>
       <c r="C285" s="3">
@@ -7566,7 +7568,7 @@
       <c r="G285" s="3"/>
       <c r="H285" s="8"/>
     </row>
-    <row r="286" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="3"/>
       <c r="B286" s="8"/>
       <c r="C286" s="3">
@@ -7580,7 +7582,7 @@
       <c r="G286" s="3"/>
       <c r="H286" s="8"/>
     </row>
-    <row r="287" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="3"/>
       <c r="B287" s="8"/>
       <c r="C287" s="3">
@@ -7594,7 +7596,7 @@
       <c r="G287" s="3"/>
       <c r="H287" s="8"/>
     </row>
-    <row r="288" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="3"/>
       <c r="B288" s="8"/>
       <c r="C288" s="3">
@@ -7608,7 +7610,7 @@
       <c r="G288" s="3"/>
       <c r="H288" s="8"/>
     </row>
-    <row r="289" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="3"/>
       <c r="B289" s="8"/>
       <c r="C289" s="3">
@@ -7622,7 +7624,7 @@
       <c r="G289" s="3"/>
       <c r="H289" s="8"/>
     </row>
-    <row r="290" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="3"/>
       <c r="B290" s="8"/>
       <c r="C290" s="3">
@@ -7636,7 +7638,7 @@
       <c r="G290" s="3"/>
       <c r="H290" s="8"/>
     </row>
-    <row r="291" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="3"/>
       <c r="B291" s="8"/>
       <c r="C291" s="3">
@@ -7650,7 +7652,7 @@
       <c r="G291" s="3"/>
       <c r="H291" s="8"/>
     </row>
-    <row r="292" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="3"/>
       <c r="B292" s="8"/>
       <c r="C292" s="3">
@@ -7664,7 +7666,7 @@
       <c r="G292" s="3"/>
       <c r="H292" s="8"/>
     </row>
-    <row r="293" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="3"/>
       <c r="B293" s="8"/>
       <c r="C293" s="3">
@@ -7678,7 +7680,7 @@
       <c r="G293" s="3"/>
       <c r="H293" s="8"/>
     </row>
-    <row r="294" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="3"/>
       <c r="B294" s="8"/>
       <c r="C294" s="3">
@@ -7692,7 +7694,7 @@
       <c r="G294" s="3"/>
       <c r="H294" s="8"/>
     </row>
-    <row r="295" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="3"/>
       <c r="B295" s="8"/>
       <c r="C295" s="3">
@@ -7706,7 +7708,7 @@
       <c r="G295" s="3"/>
       <c r="H295" s="8"/>
     </row>
-    <row r="296" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="3"/>
       <c r="B296" s="8"/>
       <c r="C296" s="3">
@@ -7720,7 +7722,7 @@
       <c r="G296" s="3"/>
       <c r="H296" s="8"/>
     </row>
-    <row r="297" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="3"/>
       <c r="B297" s="8"/>
       <c r="C297" s="3">
@@ -7734,7 +7736,7 @@
       <c r="G297" s="3"/>
       <c r="H297" s="8"/>
     </row>
-    <row r="298" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="3"/>
       <c r="B298" s="8"/>
       <c r="C298" s="3">
@@ -7748,7 +7750,7 @@
       <c r="G298" s="3"/>
       <c r="H298" s="8"/>
     </row>
-    <row r="299" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="3"/>
       <c r="B299" s="8"/>
       <c r="C299" s="3">
@@ -7762,7 +7764,7 @@
       <c r="G299" s="3"/>
       <c r="H299" s="8"/>
     </row>
-    <row r="300" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="3"/>
       <c r="B300" s="8"/>
       <c r="C300" s="3">
@@ -7776,7 +7778,7 @@
       <c r="G300" s="3"/>
       <c r="H300" s="8"/>
     </row>
-    <row r="301" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="3"/>
       <c r="B301" s="8"/>
       <c r="C301" s="3">
@@ -7790,7 +7792,7 @@
       <c r="G301" s="3"/>
       <c r="H301" s="8"/>
     </row>
-    <row r="302" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="3"/>
       <c r="B302" s="8"/>
       <c r="C302" s="3">
@@ -7804,7 +7806,7 @@
       <c r="G302" s="3"/>
       <c r="H302" s="8"/>
     </row>
-    <row r="303" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="3"/>
       <c r="B303" s="8"/>
       <c r="C303" s="3">
@@ -7818,7 +7820,7 @@
       <c r="G303" s="3"/>
       <c r="H303" s="8"/>
     </row>
-    <row r="304" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="3"/>
       <c r="B304" s="8"/>
       <c r="C304" s="39"/>
@@ -7828,7 +7830,7 @@
       <c r="G304" s="3"/>
       <c r="H304" s="8"/>
     </row>
-    <row r="305" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="3"/>
       <c r="B305" s="8"/>
       <c r="C305" s="3"/>
@@ -7838,7 +7840,7 @@
       <c r="G305" s="3"/>
       <c r="H305" s="8"/>
     </row>
-    <row r="306" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="3"/>
       <c r="B306" s="8"/>
       <c r="C306" s="3"/>
@@ -7848,7 +7850,7 @@
       <c r="G306" s="3"/>
       <c r="H306" s="8"/>
     </row>
-    <row r="307" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="3"/>
       <c r="B307" s="8"/>
       <c r="C307" s="3"/>
@@ -7858,7 +7860,7 @@
       <c r="G307" s="3"/>
       <c r="H307" s="8"/>
     </row>
-    <row r="308" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A308" s="3"/>
       <c r="B308" s="8"/>
       <c r="C308" s="3"/>
@@ -7868,7 +7870,7 @@
       <c r="G308" s="3"/>
       <c r="H308" s="8"/>
     </row>
-    <row r="309" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A309" s="29"/>
       <c r="B309" s="30"/>
       <c r="C309" s="29"/>
@@ -7881,7 +7883,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="310" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
         <v>200000</v>
       </c>
@@ -7906,11 +7908,11 @@
       <c r="H310" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="J310" s="46" t="s">
+      <c r="J310" s="40" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="311" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="3">
         <v>490000</v>
       </c>
@@ -7927,9 +7929,9 @@
       <c r="F311" s="19"/>
       <c r="G311" s="19"/>
       <c r="H311" s="33"/>
-      <c r="J311" s="47"/>
-    </row>
-    <row r="312" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J311" s="41"/>
+    </row>
+    <row r="312" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A312" s="3">
         <v>410000</v>
       </c>
@@ -7954,9 +7956,9 @@
       <c r="H312" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="J312" s="48"/>
-    </row>
-    <row r="313" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J312" s="42"/>
+    </row>
+    <row r="313" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A313" s="33"/>
       <c r="B313" s="19"/>
       <c r="C313" s="3">
@@ -7976,7 +7978,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="314" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A314" s="3">
         <v>2000</v>
       </c>
@@ -7998,7 +8000,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="315" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:10" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A315" s="3">
         <v>3500</v>
       </c>
@@ -8023,7 +8025,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="316" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3">
         <v>4850</v>
       </c>
@@ -8044,11 +8046,11 @@
       <c r="H316" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="J316" s="50" t="s">
+      <c r="J316" s="44" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="317" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="3">
         <v>3000</v>
       </c>
@@ -8067,9 +8069,9 @@
       <c r="H317" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="J317" s="51"/>
-    </row>
-    <row r="318" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J317" s="45"/>
+    </row>
+    <row r="318" spans="1:10" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A318" s="3">
         <v>3000</v>
       </c>
@@ -8086,9 +8088,9 @@
       <c r="F318" s="8"/>
       <c r="G318" s="3"/>
       <c r="H318" s="8"/>
-      <c r="J318" s="52"/>
-    </row>
-    <row r="319" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J318" s="46"/>
+    </row>
+    <row r="319" spans="1:10" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A319" s="3">
         <v>2000</v>
       </c>
@@ -8106,7 +8108,7 @@
       <c r="G319" s="3"/>
       <c r="H319" s="8"/>
     </row>
-    <row r="320" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="3">
         <v>1500</v>
       </c>
@@ -8124,7 +8126,7 @@
       <c r="G320" s="3"/>
       <c r="H320" s="8"/>
     </row>
-    <row r="321" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="3"/>
       <c r="B321" s="17" t="s">
         <v>198</v>
@@ -8140,7 +8142,7 @@
       <c r="G321" s="3"/>
       <c r="H321" s="8"/>
     </row>
-    <row r="322" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="3"/>
       <c r="B322" s="8"/>
       <c r="C322" s="3">
@@ -8154,7 +8156,7 @@
       <c r="G322" s="3"/>
       <c r="H322" s="8"/>
     </row>
-    <row r="323" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="3"/>
       <c r="B323" s="8"/>
       <c r="C323" s="3">
@@ -8168,7 +8170,7 @@
       <c r="G323" s="3"/>
       <c r="H323" s="8"/>
     </row>
-    <row r="324" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="3"/>
       <c r="B324" s="8"/>
       <c r="C324" s="33"/>
@@ -8178,7 +8180,7 @@
       <c r="G324" s="3"/>
       <c r="H324" s="8"/>
     </row>
-    <row r="325" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="3"/>
       <c r="B325" s="8"/>
       <c r="C325" s="3">
@@ -8192,7 +8194,7 @@
       <c r="G325" s="3"/>
       <c r="H325" s="8"/>
     </row>
-    <row r="326" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="3"/>
       <c r="B326" s="8"/>
       <c r="C326" s="3">
@@ -8206,7 +8208,7 @@
       <c r="G326" s="3"/>
       <c r="H326" s="8"/>
     </row>
-    <row r="327" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="3"/>
       <c r="B327" s="8"/>
       <c r="C327" s="3">
@@ -8220,7 +8222,7 @@
       <c r="G327" s="3"/>
       <c r="H327" s="8"/>
     </row>
-    <row r="328" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="3"/>
       <c r="B328" s="8"/>
       <c r="C328" s="3">
@@ -8234,7 +8236,7 @@
       <c r="G328" s="3"/>
       <c r="H328" s="8"/>
     </row>
-    <row r="329" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="3"/>
       <c r="B329" s="8"/>
       <c r="C329" s="3">
@@ -8248,7 +8250,7 @@
       <c r="G329" s="3"/>
       <c r="H329" s="8"/>
     </row>
-    <row r="330" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="3"/>
       <c r="B330" s="8"/>
       <c r="C330" s="3">
@@ -8262,7 +8264,7 @@
       <c r="G330" s="3"/>
       <c r="H330" s="8"/>
     </row>
-    <row r="331" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="3"/>
       <c r="B331" s="8"/>
       <c r="C331" s="3">
@@ -8276,7 +8278,7 @@
       <c r="G331" s="3"/>
       <c r="H331" s="8"/>
     </row>
-    <row r="332" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="3"/>
       <c r="B332" s="8"/>
       <c r="C332" s="3">
@@ -8290,7 +8292,7 @@
       <c r="G332" s="3"/>
       <c r="H332" s="8"/>
     </row>
-    <row r="333" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="3"/>
       <c r="B333" s="8"/>
       <c r="C333" s="3">
@@ -8304,7 +8306,7 @@
       <c r="G333" s="3"/>
       <c r="H333" s="8"/>
     </row>
-    <row r="334" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="3"/>
       <c r="B334" s="8"/>
       <c r="C334" s="3">
@@ -8318,7 +8320,7 @@
       <c r="G334" s="3"/>
       <c r="H334" s="8"/>
     </row>
-    <row r="335" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="3"/>
       <c r="B335" s="8"/>
       <c r="C335" s="3">
@@ -8332,7 +8334,7 @@
       <c r="G335" s="3"/>
       <c r="H335" s="8"/>
     </row>
-    <row r="336" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3"/>
       <c r="B336" s="8"/>
       <c r="C336" s="3">
@@ -8346,7 +8348,7 @@
       <c r="G336" s="3"/>
       <c r="H336" s="8"/>
     </row>
-    <row r="337" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="3"/>
       <c r="B337" s="8"/>
       <c r="C337" s="3">
@@ -8360,7 +8362,7 @@
       <c r="G337" s="3"/>
       <c r="H337" s="8"/>
     </row>
-    <row r="338" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="3"/>
       <c r="B338" s="8"/>
       <c r="C338" s="3">
@@ -8374,7 +8376,7 @@
       <c r="G338" s="3"/>
       <c r="H338" s="8"/>
     </row>
-    <row r="339" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="3"/>
       <c r="B339" s="8"/>
       <c r="C339" s="3">
@@ -8388,7 +8390,7 @@
       <c r="G339" s="3"/>
       <c r="H339" s="8"/>
     </row>
-    <row r="340" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="3"/>
       <c r="B340" s="8"/>
       <c r="C340" s="3">
@@ -8402,7 +8404,7 @@
       <c r="G340" s="3"/>
       <c r="H340" s="8"/>
     </row>
-    <row r="341" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="3"/>
       <c r="B341" s="8"/>
       <c r="C341" s="3">
@@ -8416,7 +8418,7 @@
       <c r="G341" s="3"/>
       <c r="H341" s="8"/>
     </row>
-    <row r="342" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="3"/>
       <c r="B342" s="8"/>
       <c r="C342" s="3">
@@ -8430,7 +8432,7 @@
       <c r="G342" s="3"/>
       <c r="H342" s="8"/>
     </row>
-    <row r="343" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3"/>
       <c r="B343" s="8"/>
       <c r="C343" s="3">
@@ -8444,7 +8446,7 @@
       <c r="G343" s="3"/>
       <c r="H343" s="8"/>
     </row>
-    <row r="344" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="3"/>
       <c r="B344" s="8"/>
       <c r="C344" s="3">
@@ -8458,7 +8460,7 @@
       <c r="G344" s="3"/>
       <c r="H344" s="8"/>
     </row>
-    <row r="345" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="3"/>
       <c r="B345" s="8"/>
       <c r="C345" s="3">
@@ -8472,7 +8474,7 @@
       <c r="G345" s="3"/>
       <c r="H345" s="8"/>
     </row>
-    <row r="346" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3"/>
       <c r="B346" s="8"/>
       <c r="C346" s="3">
@@ -8486,7 +8488,7 @@
       <c r="G346" s="3"/>
       <c r="H346" s="8"/>
     </row>
-    <row r="347" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="3"/>
       <c r="B347" s="8"/>
       <c r="C347" s="3">
@@ -8500,7 +8502,7 @@
       <c r="G347" s="3"/>
       <c r="H347" s="8"/>
     </row>
-    <row r="348" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3"/>
       <c r="B348" s="8"/>
       <c r="C348" s="3">
@@ -8514,7 +8516,7 @@
       <c r="G348" s="3"/>
       <c r="H348" s="8"/>
     </row>
-    <row r="349" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="3"/>
       <c r="B349" s="8"/>
       <c r="C349" s="3">
@@ -8528,7 +8530,7 @@
       <c r="G349" s="3"/>
       <c r="H349" s="8"/>
     </row>
-    <row r="350" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3"/>
       <c r="B350" s="8"/>
       <c r="C350" s="3">
@@ -8542,7 +8544,7 @@
       <c r="G350" s="3"/>
       <c r="H350" s="8"/>
     </row>
-    <row r="351" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="3"/>
       <c r="B351" s="8"/>
       <c r="C351" s="3">
@@ -8556,7 +8558,7 @@
       <c r="G351" s="3"/>
       <c r="H351" s="8"/>
     </row>
-    <row r="352" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="3"/>
       <c r="B352" s="8"/>
       <c r="C352" s="3">
@@ -8570,7 +8572,7 @@
       <c r="G352" s="3"/>
       <c r="H352" s="8"/>
     </row>
-    <row r="353" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3"/>
       <c r="B353" s="8"/>
       <c r="C353" s="3">
@@ -8584,7 +8586,7 @@
       <c r="G353" s="3"/>
       <c r="H353" s="8"/>
     </row>
-    <row r="354" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3"/>
       <c r="B354" s="8"/>
       <c r="C354" s="3">
@@ -8598,7 +8600,7 @@
       <c r="G354" s="3"/>
       <c r="H354" s="8"/>
     </row>
-    <row r="355" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="3"/>
       <c r="B355" s="8"/>
       <c r="C355" s="3">
@@ -8612,7 +8614,7 @@
       <c r="G355" s="3"/>
       <c r="H355" s="8"/>
     </row>
-    <row r="356" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3"/>
       <c r="B356" s="8"/>
       <c r="C356" s="3">
@@ -8626,7 +8628,7 @@
       <c r="G356" s="3"/>
       <c r="H356" s="8"/>
     </row>
-    <row r="357" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="3"/>
       <c r="B357" s="8"/>
       <c r="C357" s="3">
@@ -8640,7 +8642,7 @@
       <c r="G357" s="3"/>
       <c r="H357" s="8"/>
     </row>
-    <row r="358" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="3"/>
       <c r="B358" s="8"/>
       <c r="C358" s="3">
@@ -8654,7 +8656,7 @@
       <c r="G358" s="3"/>
       <c r="H358" s="8"/>
     </row>
-    <row r="359" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3"/>
       <c r="B359" s="8"/>
       <c r="C359" s="3">
@@ -8668,7 +8670,7 @@
       <c r="G359" s="3"/>
       <c r="H359" s="8"/>
     </row>
-    <row r="360" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="3"/>
       <c r="B360" s="8"/>
       <c r="C360" s="3">
@@ -8682,7 +8684,7 @@
       <c r="G360" s="3"/>
       <c r="H360" s="8"/>
     </row>
-    <row r="361" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="3"/>
       <c r="B361" s="8"/>
       <c r="C361" s="3">
@@ -8696,7 +8698,7 @@
       <c r="G361" s="3"/>
       <c r="H361" s="8"/>
     </row>
-    <row r="362" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3"/>
       <c r="B362" s="8"/>
       <c r="C362" s="3">
@@ -8710,7 +8712,7 @@
       <c r="G362" s="3"/>
       <c r="H362" s="8"/>
     </row>
-    <row r="363" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="3"/>
       <c r="B363" s="8"/>
       <c r="C363" s="3">
@@ -8724,7 +8726,7 @@
       <c r="G363" s="3"/>
       <c r="H363" s="8"/>
     </row>
-    <row r="364" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3"/>
       <c r="B364" s="8"/>
       <c r="C364" s="3">
@@ -8738,7 +8740,7 @@
       <c r="G364" s="3"/>
       <c r="H364" s="8"/>
     </row>
-    <row r="365" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="3"/>
       <c r="B365" s="8"/>
       <c r="C365" s="3">
@@ -8752,7 +8754,7 @@
       <c r="G365" s="3"/>
       <c r="H365" s="8"/>
     </row>
-    <row r="366" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3"/>
       <c r="B366" s="8"/>
       <c r="C366" s="3">
@@ -8766,7 +8768,7 @@
       <c r="G366" s="3"/>
       <c r="H366" s="8"/>
     </row>
-    <row r="367" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3"/>
       <c r="B367" s="8"/>
       <c r="C367" s="3">
@@ -8780,7 +8782,7 @@
       <c r="G367" s="3"/>
       <c r="H367" s="8"/>
     </row>
-    <row r="368" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="3"/>
       <c r="B368" s="8"/>
       <c r="C368" s="3">
@@ -8794,7 +8796,7 @@
       <c r="G368" s="3"/>
       <c r="H368" s="8"/>
     </row>
-    <row r="369" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="3"/>
       <c r="B369" s="8"/>
       <c r="C369" s="3">
@@ -8808,7 +8810,7 @@
       <c r="G369" s="3"/>
       <c r="H369" s="8"/>
     </row>
-    <row r="370" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="3"/>
       <c r="B370" s="8"/>
       <c r="C370" s="3">
@@ -8822,7 +8824,7 @@
       <c r="G370" s="3"/>
       <c r="H370" s="8"/>
     </row>
-    <row r="371" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="3"/>
       <c r="B371" s="8"/>
       <c r="C371" s="3">
@@ -8836,7 +8838,7 @@
       <c r="G371" s="3"/>
       <c r="H371" s="8"/>
     </row>
-    <row r="372" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="3"/>
       <c r="B372" s="8"/>
       <c r="C372" s="3">
@@ -8850,7 +8852,7 @@
       <c r="G372" s="3"/>
       <c r="H372" s="8"/>
     </row>
-    <row r="373" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3"/>
       <c r="B373" s="8"/>
       <c r="C373" s="3">
@@ -8864,7 +8866,7 @@
       <c r="G373" s="3"/>
       <c r="H373" s="8"/>
     </row>
-    <row r="374" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3"/>
       <c r="B374" s="8"/>
       <c r="C374" s="3">
@@ -8878,7 +8880,7 @@
       <c r="G374" s="3"/>
       <c r="H374" s="8"/>
     </row>
-    <row r="375" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="3"/>
       <c r="B375" s="8"/>
       <c r="C375" s="3"/>
@@ -8890,7 +8892,7 @@
       <c r="G375" s="3"/>
       <c r="H375" s="8"/>
     </row>
-    <row r="376" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3"/>
       <c r="B376" s="8"/>
       <c r="C376" s="3"/>
@@ -8900,7 +8902,7 @@
       <c r="G376" s="3"/>
       <c r="H376" s="8"/>
     </row>
-    <row r="377" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="3"/>
       <c r="B377" s="8"/>
       <c r="C377" s="3"/>
@@ -8912,7 +8914,7 @@
       <c r="G377" s="3"/>
       <c r="H377" s="8"/>
     </row>
-    <row r="378" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="3"/>
       <c r="B378" s="8"/>
       <c r="C378" s="3"/>
@@ -8928,7 +8930,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="379" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="3"/>
       <c r="B379" s="8"/>
       <c r="C379" s="3"/>
@@ -8944,7 +8946,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="380" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="3"/>
       <c r="B380" s="8"/>
       <c r="C380" s="3"/>
@@ -8960,7 +8962,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="381" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="3"/>
       <c r="B381" s="8"/>
       <c r="C381" s="3"/>
@@ -8970,7 +8972,7 @@
       <c r="G381" s="3"/>
       <c r="H381" s="8"/>
     </row>
-    <row r="382" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="3"/>
       <c r="B382" s="8" t="s">
         <v>1</v>
@@ -8984,7 +8986,7 @@
       <c r="G382" s="3"/>
       <c r="H382" s="8"/>
     </row>
-    <row r="383" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="3"/>
       <c r="B383" s="8" t="s">
         <v>215</v>
@@ -9004,7 +9006,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="384" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="3"/>
       <c r="B384" s="8" t="s">
         <v>217</v>
@@ -9024,7 +9026,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="385" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="3"/>
       <c r="B385" s="8" t="s">
         <v>218</v>
@@ -9046,7 +9048,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="386" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="3"/>
       <c r="B386" s="8" t="s">
         <v>219</v>
@@ -9068,7 +9070,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="387" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="3"/>
       <c r="B387" s="8" t="s">
         <v>220</v>
@@ -9088,7 +9090,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="388" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="3"/>
       <c r="B388" s="8" t="s">
         <v>221</v>
@@ -9108,7 +9110,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="389" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="3"/>
       <c r="B389" s="8" t="s">
         <v>223</v>
@@ -9128,7 +9130,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="390" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="3"/>
       <c r="B390" s="8" t="s">
         <v>224</v>
@@ -9150,7 +9152,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="391" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="3"/>
       <c r="B391" s="8" t="s">
         <v>225</v>
@@ -9174,7 +9176,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="392" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="3"/>
       <c r="B392" s="8" t="s">
         <v>226</v>
@@ -9194,7 +9196,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="393" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="3"/>
       <c r="B393" s="8" t="s">
         <v>227</v>
@@ -9214,7 +9216,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="394" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="3"/>
       <c r="B394" s="8" t="s">
         <v>228</v>
@@ -9234,7 +9236,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="395" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="3"/>
       <c r="B395" s="8" t="s">
         <v>229</v>
@@ -9254,7 +9256,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="396" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="3"/>
       <c r="B396" s="8" t="s">
         <v>230</v>
@@ -9274,7 +9276,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="397" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="3"/>
       <c r="B397" s="8" t="s">
         <v>231</v>
@@ -9296,7 +9298,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="398" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="3"/>
       <c r="B398" s="8" t="s">
         <v>233</v>
@@ -9316,7 +9318,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="399" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="3"/>
       <c r="B399" s="8" t="s">
         <v>235</v>
@@ -9336,7 +9338,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="400" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="3"/>
       <c r="B400" s="8" t="s">
         <v>236</v>
@@ -9352,7 +9354,7 @@
       <c r="G400" s="3"/>
       <c r="H400" s="8"/>
     </row>
-    <row r="401" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="3"/>
       <c r="B401" s="8" t="s">
         <v>238</v>
@@ -9368,7 +9370,7 @@
       <c r="G401" s="37"/>
       <c r="H401" s="38"/>
     </row>
-    <row r="402" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="3"/>
       <c r="B402" s="8" t="s">
         <v>239</v>
@@ -9384,7 +9386,7 @@
       <c r="G402" s="3"/>
       <c r="H402" s="8"/>
     </row>
-    <row r="403" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="3"/>
       <c r="B403" s="8" t="s">
         <v>240</v>
@@ -9402,7 +9404,7 @@
       <c r="G403" s="3"/>
       <c r="H403" s="8"/>
     </row>
-    <row r="404" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="3"/>
       <c r="B404" s="8" t="s">
         <v>241</v>
@@ -9424,7 +9426,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="405" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="3"/>
       <c r="B405" s="8" t="s">
         <v>242</v>
@@ -9446,7 +9448,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="406" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3"/>
       <c r="B406" s="8" t="s">
         <v>243</v>
@@ -9468,7 +9470,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="407" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="3"/>
       <c r="B407" s="8" t="s">
         <v>244</v>
@@ -9490,7 +9492,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="408" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="3"/>
       <c r="B408" s="8" t="s">
         <v>245</v>
@@ -9512,7 +9514,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="409" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="3"/>
       <c r="B409" s="8" t="s">
         <v>254</v>
@@ -9534,7 +9536,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="410" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="3"/>
       <c r="B410" s="8"/>
       <c r="C410" s="3"/>
@@ -9550,7 +9552,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="411" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="37"/>
       <c r="B411" s="38"/>
       <c r="C411" s="37"/>
@@ -9566,7 +9568,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="412" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="3"/>
       <c r="B412" s="8"/>
       <c r="C412" s="3"/>
@@ -9582,7 +9584,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="413" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="3"/>
       <c r="B413" s="8" t="s">
         <v>1</v>
@@ -9600,7 +9602,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="414" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="3"/>
       <c r="B414" s="8" t="s">
         <v>269</v>
@@ -9622,7 +9624,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="415" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="3"/>
       <c r="B415" s="8" t="s">
         <v>270</v>
@@ -9638,7 +9640,7 @@
       <c r="G415" s="3"/>
       <c r="H415" s="8"/>
     </row>
-    <row r="416" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="3"/>
       <c r="B416" s="8" t="s">
         <v>289</v>
@@ -9656,7 +9658,7 @@
       <c r="G416" s="3"/>
       <c r="H416" s="8"/>
     </row>
-    <row r="417" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="3"/>
       <c r="B417" s="8" t="s">
         <v>290</v>
@@ -9678,7 +9680,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="418" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="3"/>
       <c r="B418" s="8" t="s">
         <v>291</v>
@@ -9694,7 +9696,7 @@
       <c r="G418" s="3"/>
       <c r="H418" s="8"/>
     </row>
-    <row r="419" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="3"/>
       <c r="B419" s="8" t="s">
         <v>292</v>
@@ -9712,7 +9714,7 @@
       <c r="G419" s="3"/>
       <c r="H419" s="8"/>
     </row>
-    <row r="420" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="3"/>
       <c r="B420" s="8" t="s">
         <v>271</v>
@@ -9734,7 +9736,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="421" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="3"/>
       <c r="B421" s="8" t="s">
         <v>293</v>
@@ -9756,7 +9758,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="422" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="3"/>
       <c r="B422" s="8" t="s">
         <v>294</v>
@@ -9778,7 +9780,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="423" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="3"/>
       <c r="B423" s="8" t="s">
         <v>295</v>
@@ -9800,7 +9802,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="424" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="3"/>
       <c r="B424" s="8" t="s">
         <v>296</v>
@@ -9822,7 +9824,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="425" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="3"/>
       <c r="B425" s="8" t="s">
         <v>310</v>
@@ -9844,7 +9846,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="426" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="3"/>
       <c r="B426" s="8" t="s">
         <v>297</v>
@@ -9860,7 +9862,7 @@
       <c r="G426" s="3"/>
       <c r="H426" s="8"/>
     </row>
-    <row r="427" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="3"/>
       <c r="B427" s="8" t="s">
         <v>299</v>
@@ -9876,7 +9878,7 @@
       <c r="G427" s="3"/>
       <c r="H427" s="8"/>
     </row>
-    <row r="428" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="3"/>
       <c r="B428" s="8" t="s">
         <v>272</v>
@@ -9892,7 +9894,7 @@
       <c r="G428" s="3"/>
       <c r="H428" s="8"/>
     </row>
-    <row r="429" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="3"/>
       <c r="B429" s="8" t="s">
         <v>274</v>
@@ -9908,7 +9910,7 @@
       <c r="G429" s="3"/>
       <c r="H429" s="8"/>
     </row>
-    <row r="430" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="3"/>
       <c r="B430" s="8" t="s">
         <v>275</v>
@@ -9924,7 +9926,7 @@
       <c r="G430" s="3"/>
       <c r="H430" s="8"/>
     </row>
-    <row r="431" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="3"/>
       <c r="B431" s="8" t="s">
         <v>276</v>
@@ -9940,7 +9942,7 @@
       <c r="G431" s="3"/>
       <c r="H431" s="8"/>
     </row>
-    <row r="432" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="3"/>
       <c r="B432" s="8" t="s">
         <v>277</v>
@@ -9956,7 +9958,7 @@
       <c r="G432" s="3"/>
       <c r="H432" s="8"/>
     </row>
-    <row r="433" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="3"/>
       <c r="B433" s="8" t="s">
         <v>300</v>
@@ -9972,7 +9974,7 @@
       <c r="G433" s="3"/>
       <c r="H433" s="8"/>
     </row>
-    <row r="434" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="3"/>
       <c r="B434" s="8" t="s">
         <v>301</v>
@@ -9988,7 +9990,7 @@
       <c r="G434" s="3"/>
       <c r="H434" s="8"/>
     </row>
-    <row r="435" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="3"/>
       <c r="B435" s="8" t="s">
         <v>303</v>
@@ -10004,7 +10006,7 @@
       <c r="G435" s="3"/>
       <c r="H435" s="8"/>
     </row>
-    <row r="436" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="3"/>
       <c r="B436" s="8" t="s">
         <v>304</v>
@@ -10020,7 +10022,7 @@
       <c r="G436" s="3"/>
       <c r="H436" s="8"/>
     </row>
-    <row r="437" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="3"/>
       <c r="B437" s="8" t="s">
         <v>278</v>
@@ -10036,7 +10038,7 @@
       <c r="G437" s="3"/>
       <c r="H437" s="8"/>
     </row>
-    <row r="438" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="3"/>
       <c r="B438" s="8" t="s">
         <v>279</v>
@@ -10052,7 +10054,7 @@
       <c r="G438" s="3"/>
       <c r="H438" s="8"/>
     </row>
-    <row r="439" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="3"/>
       <c r="B439" s="8" t="s">
         <v>280</v>
@@ -10068,7 +10070,7 @@
       <c r="G439" s="3"/>
       <c r="H439" s="8"/>
     </row>
-    <row r="440" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="3"/>
       <c r="B440" s="8" t="s">
         <v>281</v>
@@ -10084,7 +10086,7 @@
       <c r="G440" s="3"/>
       <c r="H440" s="8"/>
     </row>
-    <row r="441" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="3"/>
       <c r="B441" s="8" t="s">
         <v>282</v>
@@ -10100,7 +10102,7 @@
       <c r="G441" s="3"/>
       <c r="H441" s="8"/>
     </row>
-    <row r="442" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="3"/>
       <c r="B442" s="8" t="s">
         <v>311</v>
@@ -10116,7 +10118,7 @@
       <c r="G442" s="3"/>
       <c r="H442" s="8"/>
     </row>
-    <row r="443" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="3"/>
       <c r="B443" s="8" t="s">
         <v>312</v>
@@ -10132,7 +10134,7 @@
       <c r="G443" s="3"/>
       <c r="H443" s="8"/>
     </row>
-    <row r="444" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="3"/>
       <c r="B444" s="8" t="s">
         <v>283</v>
@@ -10148,7 +10150,7 @@
       <c r="G444" s="3"/>
       <c r="H444" s="8"/>
     </row>
-    <row r="445" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="3"/>
       <c r="B445" s="8" t="s">
         <v>313</v>
@@ -10164,7 +10166,7 @@
       <c r="G445" s="3"/>
       <c r="H445" s="8"/>
     </row>
-    <row r="446" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="3"/>
       <c r="B446" s="8" t="s">
         <v>314</v>
@@ -10180,7 +10182,7 @@
       <c r="G446" s="3"/>
       <c r="H446" s="8"/>
     </row>
-    <row r="447" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3"/>
       <c r="B447" s="8" t="s">
         <v>315</v>
@@ -10196,7 +10198,7 @@
       <c r="G447" s="3"/>
       <c r="H447" s="8"/>
     </row>
-    <row r="448" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3"/>
       <c r="B448" s="8" t="s">
         <v>316</v>
@@ -10212,7 +10214,7 @@
       <c r="G448" s="3"/>
       <c r="H448" s="8"/>
     </row>
-    <row r="449" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3"/>
       <c r="B449" s="8" t="s">
         <v>317</v>
@@ -10228,7 +10230,7 @@
       <c r="G449" s="3"/>
       <c r="H449" s="8"/>
     </row>
-    <row r="450" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3"/>
       <c r="B450" s="8" t="s">
         <v>318</v>
@@ -10244,7 +10246,7 @@
       <c r="G450" s="3"/>
       <c r="H450" s="8"/>
     </row>
-    <row r="451" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3"/>
       <c r="B451" s="8" t="s">
         <v>319</v>
@@ -10260,7 +10262,7 @@
       <c r="G451" s="3"/>
       <c r="H451" s="8"/>
     </row>
-    <row r="452" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3"/>
       <c r="B452" s="8" t="s">
         <v>284</v>
@@ -10276,7 +10278,7 @@
       <c r="G452" s="3"/>
       <c r="H452" s="8"/>
     </row>
-    <row r="453" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="3"/>
       <c r="B453" s="8" t="s">
         <v>285</v>
@@ -10292,7 +10294,7 @@
       <c r="G453" s="37"/>
       <c r="H453" s="38"/>
     </row>
-    <row r="454" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3"/>
       <c r="B454" s="8" t="s">
         <v>286</v>
@@ -10308,7 +10310,7 @@
       <c r="G454" s="3"/>
       <c r="H454" s="8"/>
     </row>
-    <row r="455" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3"/>
       <c r="B455" s="8" t="s">
         <v>305</v>
@@ -10326,7 +10328,7 @@
       <c r="G455" s="3"/>
       <c r="H455" s="8"/>
     </row>
-    <row r="456" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="3"/>
       <c r="B456" s="8" t="s">
         <v>287</v>
@@ -10348,7 +10350,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="457" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="3"/>
       <c r="B457" s="8" t="s">
         <v>288</v>
@@ -10370,7 +10372,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="458" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3"/>
       <c r="B458" s="8" t="s">
         <v>306</v>
@@ -10392,7 +10394,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="459" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="3"/>
       <c r="B459" s="8" t="s">
         <v>307</v>
@@ -10408,7 +10410,7 @@
       <c r="G459" s="3"/>
       <c r="H459" s="8"/>
     </row>
-    <row r="460" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="3"/>
       <c r="B460" s="8" t="s">
         <v>308</v>
@@ -10424,7 +10426,7 @@
       <c r="G460" s="3"/>
       <c r="H460" s="8"/>
     </row>
-    <row r="461" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3"/>
       <c r="B461" s="8" t="s">
         <v>309</v>
@@ -10442,7 +10444,7 @@
       <c r="G461" s="3"/>
       <c r="H461" s="8"/>
     </row>
-    <row r="462" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="3"/>
       <c r="B462" s="8" t="s">
         <v>320</v>
@@ -10464,7 +10466,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="463" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="3"/>
       <c r="B463" s="8"/>
       <c r="C463" s="3"/>
@@ -10480,7 +10482,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="464" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="3"/>
       <c r="B464" s="8"/>
       <c r="C464" s="3"/>
@@ -10490,7 +10492,7 @@
       <c r="G464" s="3"/>
       <c r="H464" s="8"/>
     </row>
-    <row r="465" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="3"/>
       <c r="B465" s="8"/>
       <c r="C465" s="3"/>
@@ -10500,7 +10502,7 @@
       <c r="G465" s="3"/>
       <c r="H465" s="8"/>
     </row>
-    <row r="466" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="37"/>
       <c r="B466" s="38"/>
       <c r="C466" s="37"/>
@@ -10510,7 +10512,7 @@
       <c r="G466" s="3"/>
       <c r="H466" s="8"/>
     </row>
-    <row r="467" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3"/>
       <c r="B467" s="8"/>
       <c r="C467" s="3"/>
@@ -10520,7 +10522,7 @@
       <c r="G467" s="3"/>
       <c r="H467" s="8"/>
     </row>
-    <row r="468" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="3"/>
       <c r="B468" s="8" t="s">
         <v>1</v>
@@ -10532,7 +10534,7 @@
       <c r="G468" s="3"/>
       <c r="H468" s="8"/>
     </row>
-    <row r="469" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="3"/>
       <c r="B469" s="8" t="s">
         <v>342</v>
@@ -10548,7 +10550,7 @@
       <c r="G469" s="3"/>
       <c r="H469" s="8"/>
     </row>
-    <row r="470" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="3"/>
       <c r="B470" s="8" t="s">
         <v>345</v>
@@ -10564,7 +10566,7 @@
       <c r="G470" s="3"/>
       <c r="H470" s="8"/>
     </row>
-    <row r="471" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3"/>
       <c r="B471" s="8" t="s">
         <v>346</v>
@@ -10580,7 +10582,7 @@
       <c r="G471" s="3"/>
       <c r="H471" s="8"/>
     </row>
-    <row r="472" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3"/>
       <c r="B472" s="8" t="s">
         <v>348</v>
@@ -10596,7 +10598,7 @@
       <c r="G472" s="3"/>
       <c r="H472" s="8"/>
     </row>
-    <row r="473" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="3"/>
       <c r="B473" s="8" t="s">
         <v>349</v>
@@ -10612,7 +10614,7 @@
       <c r="G473" s="3"/>
       <c r="H473" s="8"/>
     </row>
-    <row r="474" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="3"/>
       <c r="B474" s="8" t="s">
         <v>350</v>
@@ -10628,7 +10630,7 @@
       <c r="G474" s="3"/>
       <c r="H474" s="8"/>
     </row>
-    <row r="475" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="3"/>
       <c r="B475" s="8" t="s">
         <v>351</v>
@@ -10644,7 +10646,7 @@
       <c r="G475" s="3"/>
       <c r="H475" s="8"/>
     </row>
-    <row r="476" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="3"/>
       <c r="B476" s="8" t="s">
         <v>343</v>
@@ -10660,7 +10662,7 @@
       <c r="G476" s="3"/>
       <c r="H476" s="8"/>
     </row>
-    <row r="477" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="3"/>
       <c r="B477" s="8" t="s">
         <v>344</v>
@@ -10676,7 +10678,7 @@
       <c r="G477" s="3"/>
       <c r="H477" s="8"/>
     </row>
-    <row r="478" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="3"/>
       <c r="B478" s="8"/>
       <c r="C478" s="3"/>
@@ -10686,7 +10688,7 @@
       <c r="G478" s="3"/>
       <c r="H478" s="8"/>
     </row>
-    <row r="479" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="3"/>
       <c r="B479" s="8"/>
       <c r="C479" s="3"/>
@@ -10696,7 +10698,7 @@
       <c r="G479" s="3"/>
       <c r="H479" s="8"/>
     </row>
-    <row r="480" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="3"/>
       <c r="B480" s="8"/>
       <c r="C480" s="3"/>
@@ -10706,7 +10708,7 @@
       <c r="G480" s="3"/>
       <c r="H480" s="8"/>
     </row>
-    <row r="481" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="3"/>
       <c r="B481" s="8"/>
       <c r="C481" s="3"/>
@@ -10716,7 +10718,7 @@
       <c r="G481" s="3"/>
       <c r="H481" s="8"/>
     </row>
-    <row r="482" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="37"/>
       <c r="B482" s="37"/>
       <c r="C482" s="37"/>
@@ -10726,7 +10728,7 @@
       <c r="G482" s="37"/>
       <c r="H482" s="37"/>
     </row>
-    <row r="483" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="3"/>
       <c r="B483" s="8"/>
       <c r="C483" s="3"/>
@@ -10736,7 +10738,7 @@
       <c r="G483" s="3"/>
       <c r="H483" s="8"/>
     </row>
-    <row r="484" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="3"/>
       <c r="B484" s="8"/>
       <c r="C484" s="3"/>
@@ -10746,7 +10748,7 @@
       <c r="G484" s="3"/>
       <c r="H484" s="8"/>
     </row>
-    <row r="485" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="3"/>
       <c r="B485" s="8" t="s">
         <v>1</v>
@@ -10764,7 +10766,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="486" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="3"/>
       <c r="B486" s="8"/>
       <c r="C486" s="3"/>
@@ -10774,7 +10776,7 @@
       <c r="G486" s="3"/>
       <c r="H486" s="8"/>
     </row>
-    <row r="487" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="3"/>
       <c r="B487" s="8" t="s">
         <v>387</v>
@@ -10796,7 +10798,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="488" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="3"/>
       <c r="B488" s="8" t="s">
         <v>376</v>
@@ -10818,7 +10820,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="489" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="3"/>
       <c r="B489" s="8" t="s">
         <v>377</v>
@@ -10840,7 +10842,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="490" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="3"/>
       <c r="B490" s="8" t="s">
         <v>378</v>
@@ -10862,7 +10864,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="491" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="3"/>
       <c r="B491" s="8" t="s">
         <v>379</v>
@@ -10884,7 +10886,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="492" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="3"/>
       <c r="B492" s="8" t="s">
         <v>389</v>
@@ -10906,7 +10908,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="493" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="3"/>
       <c r="B493" s="8" t="s">
         <v>390</v>
@@ -10928,7 +10930,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="494" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="3"/>
       <c r="B494" s="8" t="s">
         <v>393</v>
@@ -10950,7 +10952,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="495" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="3"/>
       <c r="B495" s="8" t="s">
         <v>395</v>
@@ -10972,7 +10974,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="496" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="3"/>
       <c r="B496" s="8" t="s">
         <v>397</v>
@@ -10994,7 +10996,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="497" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="3"/>
       <c r="B497" s="8" t="s">
         <v>399</v>
@@ -11016,7 +11018,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="498" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="3"/>
       <c r="B498" s="8" t="s">
         <v>400</v>
@@ -11038,7 +11040,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="499" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="3"/>
       <c r="B499" s="8" t="s">
         <v>401</v>
@@ -11060,7 +11062,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="500" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="3"/>
       <c r="B500" s="8" t="s">
         <v>402</v>
@@ -11082,7 +11084,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="501" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="3"/>
       <c r="B501" s="8" t="s">
         <v>369</v>
@@ -11104,7 +11106,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="502" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="3"/>
       <c r="B502" s="8" t="s">
         <v>370</v>
@@ -11126,7 +11128,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="503" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="3"/>
       <c r="B503" s="8" t="s">
         <v>403</v>
@@ -11148,7 +11150,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="504" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="3"/>
       <c r="B504" s="8" t="s">
         <v>372</v>
@@ -11170,7 +11172,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="505" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="3"/>
       <c r="B505" s="8" t="s">
         <v>373</v>
@@ -11188,11 +11190,11 @@
       <c r="G505" s="3">
         <v>5298</v>
       </c>
-      <c r="H505" s="8" t="s">
+      <c r="H505" s="10" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="506" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="3"/>
       <c r="B506" s="8" t="s">
         <v>374</v>
@@ -11214,7 +11216,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="507" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="3"/>
       <c r="B507" s="8" t="s">
         <v>375</v>
@@ -11236,7 +11238,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="508" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="3"/>
       <c r="B508" s="8" t="s">
         <v>404</v>
@@ -11258,7 +11260,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="509" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="3"/>
       <c r="B509" s="8" t="s">
         <v>380</v>
@@ -11280,7 +11282,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="510" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="3"/>
       <c r="B510" s="8" t="s">
         <v>381</v>
@@ -11296,7 +11298,7 @@
       <c r="G510" s="3"/>
       <c r="H510" s="8"/>
     </row>
-    <row r="511" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="3"/>
       <c r="B511" s="8" t="s">
         <v>382</v>
@@ -11312,7 +11314,7 @@
       <c r="G511" s="3"/>
       <c r="H511" s="8"/>
     </row>
-    <row r="512" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="3"/>
       <c r="B512" s="8" t="s">
         <v>383</v>
@@ -11328,7 +11330,7 @@
       <c r="G512" s="3"/>
       <c r="H512" s="8"/>
     </row>
-    <row r="513" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="3"/>
       <c r="B513" s="8" t="s">
         <v>384</v>
@@ -11344,7 +11346,7 @@
       <c r="G513" s="3"/>
       <c r="H513" s="8"/>
     </row>
-    <row r="514" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="3"/>
       <c r="B514" s="8" t="s">
         <v>385</v>
@@ -11360,7 +11362,7 @@
       <c r="G514" s="3"/>
       <c r="H514" s="8"/>
     </row>
-    <row r="515" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="3"/>
       <c r="B515" s="8" t="s">
         <v>386</v>
@@ -11376,7 +11378,7 @@
       <c r="G515" s="3"/>
       <c r="H515" s="8"/>
     </row>
-    <row r="516" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="3"/>
       <c r="B516" s="8" t="s">
         <v>358</v>
@@ -11392,7 +11394,7 @@
       <c r="G516" s="3"/>
       <c r="H516" s="8"/>
     </row>
-    <row r="517" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="3"/>
       <c r="B517" s="8" t="s">
         <v>405</v>
@@ -11408,7 +11410,7 @@
       <c r="G517" s="3"/>
       <c r="H517" s="8"/>
     </row>
-    <row r="518" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="3"/>
       <c r="B518" s="8" t="s">
         <v>406</v>
@@ -11424,7 +11426,7 @@
       <c r="G518" s="3"/>
       <c r="H518" s="8"/>
     </row>
-    <row r="519" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="3"/>
       <c r="B519" s="8" t="s">
         <v>407</v>
@@ -11440,7 +11442,7 @@
       <c r="G519" s="3"/>
       <c r="H519" s="8"/>
     </row>
-    <row r="520" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="3"/>
       <c r="B520" s="8" t="s">
         <v>408</v>
@@ -11456,7 +11458,7 @@
       <c r="G520" s="3"/>
       <c r="H520" s="8"/>
     </row>
-    <row r="521" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="3"/>
       <c r="B521" s="8" t="s">
         <v>409</v>
@@ -11472,7 +11474,7 @@
       <c r="G521" s="3"/>
       <c r="H521" s="8"/>
     </row>
-    <row r="522" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="3"/>
       <c r="B522" s="8" t="s">
         <v>410</v>
@@ -11488,7 +11490,7 @@
       <c r="G522" s="3"/>
       <c r="H522" s="8"/>
     </row>
-    <row r="523" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="3"/>
       <c r="B523" s="8" t="s">
         <v>411</v>
@@ -11504,7 +11506,7 @@
       <c r="G523" s="3"/>
       <c r="H523" s="8"/>
     </row>
-    <row r="524" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="3"/>
       <c r="B524" s="8" t="s">
         <v>412</v>
@@ -11520,7 +11522,7 @@
       <c r="G524" s="3"/>
       <c r="H524" s="8"/>
     </row>
-    <row r="525" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="3"/>
       <c r="B525" s="8" t="s">
         <v>413</v>
@@ -11538,7 +11540,7 @@
       <c r="G525" s="3"/>
       <c r="H525" s="8"/>
     </row>
-    <row r="526" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="3"/>
       <c r="B526" s="8" t="s">
         <v>414</v>
@@ -11560,7 +11562,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="527" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="3"/>
       <c r="B527" s="8" t="s">
         <v>441</v>
@@ -11582,7 +11584,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="528" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="3"/>
       <c r="B528" s="8" t="s">
         <v>442</v>
@@ -11604,7 +11606,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="529" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="3"/>
       <c r="B529" s="8" t="s">
         <v>443</v>
@@ -11626,7 +11628,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="530" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="3"/>
       <c r="B530" s="8" t="s">
         <v>444</v>
@@ -11648,7 +11650,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="531" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="3"/>
       <c r="B531" s="8" t="s">
         <v>464</v>
@@ -11670,7 +11672,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="532" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="3"/>
       <c r="B532" s="8" t="s">
         <v>465</v>
@@ -11692,7 +11694,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="533" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="3"/>
       <c r="B533" s="8" t="s">
         <v>277</v>
@@ -11714,7 +11716,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="534" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="3"/>
       <c r="B534" s="8" t="s">
         <v>467</v>
@@ -11736,7 +11738,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="535" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="3"/>
       <c r="B535" s="8" t="s">
         <v>468</v>
@@ -11758,7 +11760,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="536" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="3"/>
       <c r="B536" s="8" t="s">
         <v>469</v>
@@ -11774,7 +11776,7 @@
       <c r="G536" s="3"/>
       <c r="H536" s="8"/>
     </row>
-    <row r="537" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="3"/>
       <c r="B537" s="8" t="s">
         <v>470</v>
@@ -11790,7 +11792,7 @@
       <c r="G537" s="3"/>
       <c r="H537" s="8"/>
     </row>
-    <row r="538" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="3"/>
       <c r="B538" s="8" t="s">
         <v>471</v>
@@ -11806,7 +11808,7 @@
       <c r="G538" s="3"/>
       <c r="H538" s="8"/>
     </row>
-    <row r="539" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="3"/>
       <c r="B539" s="8" t="s">
         <v>472</v>
@@ -11824,7 +11826,7 @@
       <c r="G539" s="3"/>
       <c r="H539" s="8"/>
     </row>
-    <row r="540" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="3"/>
       <c r="B540" s="8" t="s">
         <v>474</v>
@@ -11842,11 +11844,11 @@
       <c r="G540" s="3">
         <v>1000</v>
       </c>
-      <c r="H540" s="8" t="s">
+      <c r="H540" s="10" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="541" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="3"/>
       <c r="B541" s="8" t="s">
         <v>475</v>
@@ -11862,7 +11864,7 @@
       <c r="G541" s="3"/>
       <c r="H541" s="8"/>
     </row>
-    <row r="542" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="3"/>
       <c r="B542" s="8" t="s">
         <v>476</v>
@@ -11878,7 +11880,7 @@
       <c r="G542" s="3"/>
       <c r="H542" s="8"/>
     </row>
-    <row r="543" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A543" s="3"/>
       <c r="B543" s="8" t="s">
         <v>477</v>
@@ -11894,7 +11896,7 @@
       <c r="G543" s="3"/>
       <c r="H543" s="8"/>
     </row>
-    <row r="544" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A544" s="3"/>
       <c r="B544" s="8" t="s">
         <v>445</v>
@@ -11910,7 +11912,7 @@
       <c r="G544" s="3"/>
       <c r="H544" s="8"/>
     </row>
-    <row r="545" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="3"/>
       <c r="B545" s="8" t="s">
         <v>478</v>
@@ -11926,7 +11928,7 @@
       <c r="G545" s="3"/>
       <c r="H545" s="8"/>
     </row>
-    <row r="546" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A546" s="3"/>
       <c r="B546" s="8" t="s">
         <v>479</v>
@@ -11942,15 +11944,17 @@
       <c r="G546" s="3"/>
       <c r="H546" s="8"/>
     </row>
-    <row r="547" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A547" s="3"/>
+    <row r="547" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A547" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="B547" s="8" t="s">
         <v>480</v>
       </c>
       <c r="C547" s="3">
         <v>1000</v>
       </c>
-      <c r="D547" s="8" t="s">
+      <c r="D547" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E547" s="3"/>
@@ -11958,7 +11962,7 @@
       <c r="G547" s="3"/>
       <c r="H547" s="8"/>
     </row>
-    <row r="548" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A548" s="3"/>
       <c r="B548" s="8" t="s">
         <v>481</v>
@@ -11966,7 +11970,7 @@
       <c r="C548" s="3">
         <v>1000</v>
       </c>
-      <c r="D548" s="8" t="s">
+      <c r="D548" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E548" s="3"/>
@@ -11974,7 +11978,7 @@
       <c r="G548" s="3"/>
       <c r="H548" s="8"/>
     </row>
-    <row r="549" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A549" s="3"/>
       <c r="B549" s="8" t="s">
         <v>446</v>
@@ -11990,7 +11994,7 @@
       <c r="G549" s="3"/>
       <c r="H549" s="8"/>
     </row>
-    <row r="550" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A550" s="3"/>
       <c r="B550" s="8" t="s">
         <v>447</v>
@@ -12006,7 +12010,7 @@
       <c r="G550" s="3"/>
       <c r="H550" s="8"/>
     </row>
-    <row r="551" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="3"/>
       <c r="B551" s="8" t="s">
         <v>448</v>
@@ -12022,7 +12026,7 @@
       <c r="G551" s="3"/>
       <c r="H551" s="8"/>
     </row>
-    <row r="552" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A552" s="3"/>
       <c r="B552" s="8" t="s">
         <v>449</v>
@@ -12038,7 +12042,7 @@
       <c r="G552" s="3"/>
       <c r="H552" s="8"/>
     </row>
-    <row r="553" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A553" s="3"/>
       <c r="B553" s="8" t="s">
         <v>450</v>
@@ -12054,7 +12058,7 @@
       <c r="G553" s="3"/>
       <c r="H553" s="8"/>
     </row>
-    <row r="554" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A554" s="3"/>
       <c r="B554" s="8" t="s">
         <v>452</v>
@@ -12070,7 +12074,7 @@
       <c r="G554" s="3"/>
       <c r="H554" s="8"/>
     </row>
-    <row r="555" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A555" s="3"/>
       <c r="B555" s="8" t="s">
         <v>453</v>
@@ -12086,7 +12090,7 @@
       <c r="G555" s="3"/>
       <c r="H555" s="8"/>
     </row>
-    <row r="556" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="3"/>
       <c r="B556" s="8" t="s">
         <v>454</v>
@@ -12102,7 +12106,7 @@
       <c r="G556" s="3"/>
       <c r="H556" s="8"/>
     </row>
-    <row r="557" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A557" s="3"/>
       <c r="B557" s="8" t="s">
         <v>455</v>
@@ -12118,7 +12122,7 @@
       <c r="G557" s="3"/>
       <c r="H557" s="8"/>
     </row>
-    <row r="558" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A558" s="3"/>
       <c r="B558" s="8" t="s">
         <v>456</v>
@@ -12134,7 +12138,7 @@
       <c r="G558" s="3"/>
       <c r="H558" s="8"/>
     </row>
-    <row r="559" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A559" s="3"/>
       <c r="B559" s="8" t="s">
         <v>457</v>
@@ -12150,7 +12154,7 @@
       <c r="G559" s="3"/>
       <c r="H559" s="8"/>
     </row>
-    <row r="560" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="3"/>
       <c r="B560" s="8" t="s">
         <v>458</v>
@@ -12166,7 +12170,7 @@
       <c r="G560" s="3"/>
       <c r="H560" s="8"/>
     </row>
-    <row r="561" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A561" s="3"/>
       <c r="B561" s="8" t="s">
         <v>459</v>
@@ -12182,7 +12186,7 @@
       <c r="G561" s="3"/>
       <c r="H561" s="8"/>
     </row>
-    <row r="562" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A562" s="3"/>
       <c r="B562" s="8" t="s">
         <v>482</v>
@@ -12198,7 +12202,7 @@
       <c r="G562" s="3"/>
       <c r="H562" s="8"/>
     </row>
-    <row r="563" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A563" s="3"/>
       <c r="B563" s="8" t="s">
         <v>483</v>
@@ -12214,7 +12218,7 @@
       <c r="G563" s="3"/>
       <c r="H563" s="8"/>
     </row>
-    <row r="564" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564" s="3"/>
       <c r="B564" s="8" t="s">
         <v>484</v>
@@ -12230,7 +12234,7 @@
       <c r="G564" s="3"/>
       <c r="H564" s="8"/>
     </row>
-    <row r="565" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565" s="3"/>
       <c r="B565" s="8" t="s">
         <v>485</v>
@@ -12246,7 +12250,7 @@
       <c r="G565" s="3"/>
       <c r="H565" s="8"/>
     </row>
-    <row r="566" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566" s="3"/>
       <c r="B566" s="8" t="s">
         <v>486</v>
@@ -12262,7 +12266,7 @@
       <c r="G566" s="3"/>
       <c r="H566" s="8"/>
     </row>
-    <row r="567" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567" s="3"/>
       <c r="B567" s="8" t="s">
         <v>487</v>
@@ -12278,7 +12282,7 @@
       <c r="G567" s="3"/>
       <c r="H567" s="8"/>
     </row>
-    <row r="568" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568" s="3"/>
       <c r="B568" s="8" t="s">
         <v>489</v>
@@ -12294,7 +12298,7 @@
       <c r="G568" s="3"/>
       <c r="H568" s="8"/>
     </row>
-    <row r="569" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="3"/>
       <c r="B569" s="8" t="s">
         <v>490</v>
@@ -12310,7 +12314,7 @@
       <c r="G569" s="3"/>
       <c r="H569" s="8"/>
     </row>
-    <row r="570" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="3"/>
       <c r="B570" s="8" t="s">
         <v>491</v>
@@ -12326,7 +12330,7 @@
       <c r="G570" s="3"/>
       <c r="H570" s="8"/>
     </row>
-    <row r="571" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="3"/>
       <c r="B571" s="8" t="s">
         <v>460</v>
@@ -12342,7 +12346,7 @@
       <c r="G571" s="3"/>
       <c r="H571" s="8"/>
     </row>
-    <row r="572" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="3"/>
       <c r="B572" s="8" t="s">
         <v>461</v>
@@ -12358,7 +12362,7 @@
       <c r="G572" s="3"/>
       <c r="H572" s="8"/>
     </row>
-    <row r="573" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="3"/>
       <c r="B573" s="8" t="s">
         <v>462</v>
@@ -12374,7 +12378,7 @@
       <c r="G573" s="3"/>
       <c r="H573" s="8"/>
     </row>
-    <row r="574" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="3"/>
       <c r="B574" s="8" t="s">
         <v>463</v>
@@ -12390,7 +12394,7 @@
       <c r="G574" s="3"/>
       <c r="H574" s="8"/>
     </row>
-    <row r="575" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="3"/>
       <c r="B575" s="8"/>
       <c r="C575" s="3"/>
@@ -12400,7 +12404,7 @@
       <c r="G575" s="3"/>
       <c r="H575" s="8"/>
     </row>
-    <row r="576" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="3"/>
       <c r="B576" s="8"/>
       <c r="C576" s="3"/>
@@ -12410,7 +12414,7 @@
       <c r="G576" s="3"/>
       <c r="H576" s="8"/>
     </row>
-    <row r="577" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="3"/>
       <c r="B577" s="8"/>
       <c r="C577" s="3"/>
@@ -12420,7 +12424,7 @@
       <c r="G577" s="3"/>
       <c r="H577" s="8"/>
     </row>
-    <row r="578" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="3"/>
       <c r="B578" s="8"/>
       <c r="C578" s="3"/>
@@ -12430,7 +12434,7 @@
       <c r="G578" s="3"/>
       <c r="H578" s="8"/>
     </row>
-    <row r="579" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="3"/>
       <c r="B579" s="8"/>
       <c r="C579" s="3"/>
@@ -12440,7 +12444,7 @@
       <c r="G579" s="3"/>
       <c r="H579" s="8"/>
     </row>
-    <row r="580" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="37"/>
       <c r="B580" s="37"/>
       <c r="C580" s="37"/>
@@ -12450,7 +12454,7 @@
       <c r="G580" s="37"/>
       <c r="H580" s="37"/>
     </row>
-    <row r="581" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A581" s="3"/>
       <c r="B581" s="8"/>
       <c r="C581" s="3"/>
@@ -12460,7 +12464,7 @@
       <c r="G581" s="3"/>
       <c r="H581" s="8"/>
     </row>
-    <row r="582" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A582" s="3"/>
       <c r="B582" s="8" t="s">
         <v>1</v>
@@ -12478,7 +12482,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="583" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A583" s="3"/>
       <c r="B583" s="8"/>
       <c r="C583" s="3"/>
@@ -12488,7 +12492,7 @@
       <c r="G583" s="3"/>
       <c r="H583" s="8"/>
     </row>
-    <row r="584" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A584" s="3"/>
       <c r="B584" s="8" t="s">
         <v>495</v>
@@ -12510,7 +12514,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="585" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A585" s="3"/>
       <c r="B585" s="8" t="s">
         <v>496</v>
@@ -12526,7 +12530,7 @@
       <c r="G585" s="3"/>
       <c r="H585" s="8"/>
     </row>
-    <row r="586" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A586" s="3"/>
       <c r="B586" s="8" t="s">
         <v>497</v>
@@ -12542,7 +12546,7 @@
       <c r="G586" s="3"/>
       <c r="H586" s="8"/>
     </row>
-    <row r="587" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A587" s="3"/>
       <c r="B587" s="8" t="s">
         <v>498</v>
@@ -12558,7 +12562,7 @@
       <c r="G587" s="3"/>
       <c r="H587" s="8"/>
     </row>
-    <row r="588" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A588" s="3"/>
       <c r="B588" s="8" t="s">
         <v>500</v>
@@ -12576,7 +12580,7 @@
       <c r="G588" s="3"/>
       <c r="H588" s="8"/>
     </row>
-    <row r="589" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A589" s="3"/>
       <c r="B589" s="8" t="s">
         <v>501</v>
@@ -12592,7 +12596,7 @@
       <c r="G589" s="3"/>
       <c r="H589" s="8"/>
     </row>
-    <row r="590" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A590" s="3"/>
       <c r="B590" s="8" t="s">
         <v>503</v>
@@ -12614,7 +12618,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="591" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A591" s="3"/>
       <c r="B591" s="8" t="s">
         <v>504</v>
@@ -12630,7 +12634,7 @@
       <c r="G591" s="3"/>
       <c r="H591" s="8"/>
     </row>
-    <row r="592" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A592" s="3"/>
       <c r="B592" s="8" t="s">
         <v>506</v>
@@ -12646,7 +12650,7 @@
       <c r="G592" s="3"/>
       <c r="H592" s="8"/>
     </row>
-    <row r="593" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A593" s="3"/>
       <c r="B593" s="8" t="s">
         <v>507</v>
@@ -12662,7 +12666,7 @@
       <c r="G593" s="3"/>
       <c r="H593" s="8"/>
     </row>
-    <row r="594" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A594" s="3"/>
       <c r="B594" s="8" t="s">
         <v>508</v>
@@ -12678,7 +12682,7 @@
       <c r="G594" s="3"/>
       <c r="H594" s="8"/>
     </row>
-    <row r="595" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A595" s="3"/>
       <c r="B595" s="8" t="s">
         <v>509</v>
@@ -12694,7 +12698,7 @@
       <c r="G595" s="3"/>
       <c r="H595" s="8"/>
     </row>
-    <row r="596" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A596" s="3"/>
       <c r="B596" s="8"/>
       <c r="C596" s="3"/>
@@ -12704,7 +12708,7 @@
       <c r="G596" s="3"/>
       <c r="H596" s="8"/>
     </row>
-    <row r="597" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A597" s="3"/>
       <c r="B597" s="8"/>
       <c r="C597" s="3"/>
@@ -12714,7 +12718,7 @@
       <c r="G597" s="3"/>
       <c r="H597" s="8"/>
     </row>
-    <row r="598" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A598" s="37"/>
       <c r="B598" s="37"/>
       <c r="C598" s="37"/>
@@ -12724,7 +12728,7 @@
       <c r="G598" s="37"/>
       <c r="H598" s="37"/>
     </row>
-    <row r="599" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A599" s="3"/>
       <c r="B599" s="8"/>
       <c r="C599" s="3"/>
@@ -12734,7 +12738,7 @@
       <c r="G599" s="3"/>
       <c r="H599" s="8"/>
     </row>
-    <row r="600" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A600" s="3"/>
       <c r="B600" s="8" t="s">
         <v>1</v>
@@ -12752,7 +12756,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="601" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A601" s="3"/>
       <c r="B601" s="8"/>
       <c r="C601" s="3"/>
@@ -12762,7 +12766,7 @@
       <c r="G601" s="3"/>
       <c r="H601" s="8"/>
     </row>
-    <row r="602" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A602" s="3"/>
       <c r="B602" s="8" t="s">
         <v>514</v>
@@ -12778,7 +12782,7 @@
       <c r="G602" s="3"/>
       <c r="H602" s="8"/>
     </row>
-    <row r="603" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A603" s="3"/>
       <c r="B603" s="8" t="s">
         <v>515</v>
@@ -12794,7 +12798,7 @@
       <c r="G603" s="3"/>
       <c r="H603" s="8"/>
     </row>
-    <row r="604" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A604" s="3"/>
       <c r="B604" s="8" t="s">
         <v>516</v>
@@ -12810,7 +12814,7 @@
       <c r="G604" s="3"/>
       <c r="H604" s="8"/>
     </row>
-    <row r="605" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A605" s="3"/>
       <c r="B605" s="8" t="s">
         <v>517</v>
@@ -12826,7 +12830,7 @@
       <c r="G605" s="3"/>
       <c r="H605" s="8"/>
     </row>
-    <row r="606" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A606" s="3"/>
       <c r="B606" s="8" t="s">
         <v>519</v>
@@ -12842,7 +12846,7 @@
       <c r="G606" s="3"/>
       <c r="H606" s="8"/>
     </row>
-    <row r="607" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A607" s="3"/>
       <c r="B607" s="8"/>
       <c r="C607" s="3"/>
@@ -12852,7 +12856,7 @@
       <c r="G607" s="3"/>
       <c r="H607" s="8"/>
     </row>
-    <row r="608" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A608" s="3"/>
       <c r="B608" s="8"/>
       <c r="C608" s="3"/>
@@ -12862,7 +12866,7 @@
       <c r="G608" s="3"/>
       <c r="H608" s="8"/>
     </row>
-    <row r="609" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A609" s="3"/>
       <c r="B609" s="8"/>
       <c r="C609" s="3"/>
@@ -12872,7 +12876,7 @@
       <c r="G609" s="3"/>
       <c r="H609" s="8"/>
     </row>
-    <row r="610" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A610" s="3"/>
       <c r="B610" s="8"/>
       <c r="C610" s="3"/>
@@ -12882,7 +12886,7 @@
       <c r="G610" s="3"/>
       <c r="H610" s="8"/>
     </row>
-    <row r="611" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A611" s="3"/>
       <c r="B611" s="8"/>
       <c r="C611" s="3"/>
@@ -12892,7 +12896,7 @@
       <c r="G611" s="3"/>
       <c r="H611" s="8"/>
     </row>
-    <row r="612" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A612" s="3"/>
       <c r="B612" s="8"/>
       <c r="C612" s="3"/>
@@ -12902,7 +12906,7 @@
       <c r="G612" s="3"/>
       <c r="H612" s="8"/>
     </row>
-    <row r="613" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A613" s="3"/>
       <c r="B613" s="8"/>
       <c r="C613" s="3"/>
@@ -12912,7 +12916,7 @@
       <c r="G613" s="3"/>
       <c r="H613" s="8"/>
     </row>
-    <row r="614" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A614" s="3"/>
       <c r="B614" s="8"/>
       <c r="C614" s="3"/>
@@ -12922,7 +12926,7 @@
       <c r="G614" s="3"/>
       <c r="H614" s="8"/>
     </row>
-    <row r="615" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A615" s="3"/>
       <c r="B615" s="8"/>
       <c r="C615" s="3"/>
@@ -12932,7 +12936,7 @@
       <c r="G615" s="3"/>
       <c r="H615" s="8"/>
     </row>
-    <row r="616" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A616" s="3"/>
       <c r="B616" s="8"/>
       <c r="C616" s="3"/>
@@ -12942,7 +12946,7 @@
       <c r="G616" s="3"/>
       <c r="H616" s="8"/>
     </row>
-    <row r="617" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A617" s="3"/>
       <c r="B617" s="8"/>
       <c r="C617" s="3"/>
@@ -12952,7 +12956,7 @@
       <c r="G617" s="3"/>
       <c r="H617" s="8"/>
     </row>
-    <row r="618" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A618" s="3"/>
       <c r="B618" s="8"/>
       <c r="C618" s="3"/>
@@ -12962,7 +12966,7 @@
       <c r="G618" s="3"/>
       <c r="H618" s="8"/>
     </row>
-    <row r="619" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A619" s="3"/>
       <c r="B619" s="8"/>
       <c r="C619" s="3"/>
@@ -12972,7 +12976,7 @@
       <c r="G619" s="3"/>
       <c r="H619" s="8"/>
     </row>
-    <row r="620" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A620" s="3"/>
       <c r="B620" s="8"/>
       <c r="C620" s="3"/>
@@ -12982,7 +12986,7 @@
       <c r="G620" s="3"/>
       <c r="H620" s="8"/>
     </row>
-    <row r="621" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A621" s="3"/>
       <c r="B621" s="8"/>
       <c r="C621" s="3"/>
@@ -12992,7 +12996,7 @@
       <c r="G621" s="3"/>
       <c r="H621" s="8"/>
     </row>
-    <row r="622" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A622" s="3"/>
       <c r="B622" s="8"/>
       <c r="C622" s="3"/>
@@ -13002,7 +13006,7 @@
       <c r="G622" s="3"/>
       <c r="H622" s="8"/>
     </row>
-    <row r="623" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A623" s="3"/>
       <c r="B623" s="8"/>
       <c r="C623" s="3"/>
@@ -13012,7 +13016,7 @@
       <c r="G623" s="3"/>
       <c r="H623" s="8"/>
     </row>
-    <row r="624" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A624" s="3"/>
       <c r="B624" s="8"/>
       <c r="C624" s="3"/>
@@ -13022,7 +13026,7 @@
       <c r="G624" s="3"/>
       <c r="H624" s="8"/>
     </row>
-    <row r="625" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A625" s="3"/>
       <c r="B625" s="8"/>
       <c r="C625" s="3"/>
@@ -13032,7 +13036,7 @@
       <c r="G625" s="3"/>
       <c r="H625" s="8"/>
     </row>
-    <row r="626" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A626" s="3"/>
       <c r="B626" s="8"/>
       <c r="C626" s="3"/>
@@ -13042,7 +13046,7 @@
       <c r="G626" s="3"/>
       <c r="H626" s="8"/>
     </row>
-    <row r="627" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A627" s="3"/>
       <c r="B627" s="8"/>
       <c r="C627" s="3"/>
@@ -13052,7 +13056,7 @@
       <c r="G627" s="3"/>
       <c r="H627" s="8"/>
     </row>
-    <row r="628" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A628" s="3"/>
       <c r="B628" s="8"/>
       <c r="C628" s="3"/>
@@ -13062,7 +13066,7 @@
       <c r="G628" s="3"/>
       <c r="H628" s="8"/>
     </row>
-    <row r="629" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A629" s="3"/>
       <c r="B629" s="8"/>
       <c r="C629" s="3"/>
@@ -13072,7 +13076,7 @@
       <c r="G629" s="3"/>
       <c r="H629" s="8"/>
     </row>
-    <row r="630" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A630" s="3"/>
       <c r="B630" s="8"/>
       <c r="C630" s="3"/>
@@ -13082,7 +13086,7 @@
       <c r="G630" s="3"/>
       <c r="H630" s="8"/>
     </row>
-    <row r="631" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A631" s="3"/>
       <c r="B631" s="8"/>
       <c r="C631" s="3"/>
@@ -13092,7 +13096,7 @@
       <c r="G631" s="3"/>
       <c r="H631" s="8"/>
     </row>
-    <row r="632" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A632" s="3"/>
       <c r="B632" s="8"/>
       <c r="C632" s="3"/>
@@ -13102,7 +13106,7 @@
       <c r="G632" s="3"/>
       <c r="H632" s="8"/>
     </row>
-    <row r="633" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A633" s="3"/>
       <c r="B633" s="8"/>
       <c r="C633" s="3"/>
@@ -13112,7 +13116,7 @@
       <c r="G633" s="3"/>
       <c r="H633" s="8"/>
     </row>
-    <row r="634" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A634" s="3"/>
       <c r="B634" s="8"/>
       <c r="C634" s="3"/>
@@ -13122,7 +13126,7 @@
       <c r="G634" s="3"/>
       <c r="H634" s="8"/>
     </row>
-    <row r="635" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A635" s="3"/>
       <c r="B635" s="8"/>
       <c r="C635" s="3"/>
@@ -13132,7 +13136,7 @@
       <c r="G635" s="3"/>
       <c r="H635" s="8"/>
     </row>
-    <row r="636" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A636" s="3"/>
       <c r="B636" s="8"/>
       <c r="C636" s="3"/>
@@ -13142,7 +13146,7 @@
       <c r="G636" s="3"/>
       <c r="H636" s="8"/>
     </row>
-    <row r="637" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A637" s="3"/>
       <c r="B637" s="8"/>
       <c r="C637" s="3"/>
@@ -13152,7 +13156,7 @@
       <c r="G637" s="3"/>
       <c r="H637" s="8"/>
     </row>
-    <row r="638" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A638" s="3"/>
       <c r="B638" s="8"/>
       <c r="C638" s="3"/>
@@ -13162,7 +13166,7 @@
       <c r="G638" s="3"/>
       <c r="H638" s="8"/>
     </row>
-    <row r="639" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A639" s="3"/>
       <c r="B639" s="8"/>
       <c r="C639" s="3"/>
@@ -13172,7 +13176,7 @@
       <c r="G639" s="3"/>
       <c r="H639" s="8"/>
     </row>
-    <row r="640" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A640" s="3"/>
       <c r="B640" s="8"/>
       <c r="C640" s="3"/>
@@ -13182,7 +13186,7 @@
       <c r="G640" s="3"/>
       <c r="H640" s="8"/>
     </row>
-    <row r="641" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A641" s="3"/>
       <c r="B641" s="8"/>
       <c r="C641" s="3"/>
@@ -13192,7 +13196,7 @@
       <c r="G641" s="3"/>
       <c r="H641" s="8"/>
     </row>
-    <row r="642" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A642" s="3"/>
       <c r="B642" s="8"/>
       <c r="C642" s="3"/>
@@ -13202,7 +13206,7 @@
       <c r="G642" s="3"/>
       <c r="H642" s="8"/>
     </row>
-    <row r="643" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A643" s="3"/>
       <c r="B643" s="8"/>
       <c r="C643" s="3"/>
@@ -13212,7 +13216,7 @@
       <c r="G643" s="3"/>
       <c r="H643" s="8"/>
     </row>
-    <row r="644" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A644" s="3"/>
       <c r="B644" s="8"/>
       <c r="C644" s="3"/>
@@ -13222,7 +13226,7 @@
       <c r="G644" s="3"/>
       <c r="H644" s="8"/>
     </row>
-    <row r="645" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A645" s="3"/>
       <c r="B645" s="8"/>
       <c r="C645" s="3"/>
@@ -13232,7 +13236,7 @@
       <c r="G645" s="3"/>
       <c r="H645" s="8"/>
     </row>
-    <row r="646" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A646" s="3"/>
       <c r="B646" s="8"/>
       <c r="C646" s="3"/>
@@ -13242,7 +13246,7 @@
       <c r="G646" s="3"/>
       <c r="H646" s="8"/>
     </row>
-    <row r="647" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A647" s="3"/>
       <c r="B647" s="8"/>
       <c r="C647" s="3"/>
@@ -13252,7 +13256,7 @@
       <c r="G647" s="3"/>
       <c r="H647" s="8"/>
     </row>
-    <row r="648" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A648" s="3"/>
       <c r="B648" s="8"/>
       <c r="C648" s="3"/>
@@ -13262,7 +13266,7 @@
       <c r="G648" s="3"/>
       <c r="H648" s="8"/>
     </row>
-    <row r="649" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A649" s="3"/>
       <c r="B649" s="8"/>
       <c r="C649" s="3"/>
@@ -13272,7 +13276,7 @@
       <c r="G649" s="3"/>
       <c r="H649" s="8"/>
     </row>
-    <row r="650" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A650" s="3"/>
       <c r="B650" s="8"/>
       <c r="C650" s="3"/>
@@ -13282,7 +13286,7 @@
       <c r="G650" s="3"/>
       <c r="H650" s="8"/>
     </row>
-    <row r="651" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A651" s="3"/>
       <c r="B651" s="8"/>
       <c r="C651" s="3"/>
@@ -13292,7 +13296,7 @@
       <c r="G651" s="3"/>
       <c r="H651" s="8"/>
     </row>
-    <row r="652" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A652" s="3"/>
       <c r="B652" s="8"/>
       <c r="C652" s="3"/>
@@ -13302,7 +13306,7 @@
       <c r="G652" s="3"/>
       <c r="H652" s="8"/>
     </row>
-    <row r="653" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A653" s="3"/>
       <c r="B653" s="8"/>
       <c r="C653" s="3"/>
@@ -13312,7 +13316,7 @@
       <c r="G653" s="3"/>
       <c r="H653" s="8"/>
     </row>
-    <row r="654" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A654" s="3"/>
       <c r="B654" s="8"/>
       <c r="C654" s="3"/>
@@ -13322,7 +13326,7 @@
       <c r="G654" s="3"/>
       <c r="H654" s="8"/>
     </row>
-    <row r="655" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A655" s="3"/>
       <c r="B655" s="8"/>
       <c r="C655" s="3"/>
@@ -13332,7 +13336,7 @@
       <c r="G655" s="3"/>
       <c r="H655" s="8"/>
     </row>
-    <row r="656" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A656" s="3"/>
       <c r="B656" s="8"/>
       <c r="C656" s="3"/>
@@ -13342,7 +13346,7 @@
       <c r="G656" s="3"/>
       <c r="H656" s="8"/>
     </row>
-    <row r="657" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A657" s="3"/>
       <c r="B657" s="8"/>
       <c r="C657" s="3"/>
@@ -13352,7 +13356,7 @@
       <c r="G657" s="3"/>
       <c r="H657" s="8"/>
     </row>
-    <row r="658" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A658" s="3"/>
       <c r="B658" s="8"/>
       <c r="C658" s="3"/>
@@ -13362,7 +13366,7 @@
       <c r="G658" s="3"/>
       <c r="H658" s="8"/>
     </row>
-    <row r="659" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A659" s="3"/>
       <c r="B659" s="8"/>
       <c r="C659" s="3"/>
@@ -13372,7 +13376,7 @@
       <c r="G659" s="3"/>
       <c r="H659" s="8"/>
     </row>
-    <row r="660" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A660" s="3"/>
       <c r="B660" s="8"/>
       <c r="C660" s="3"/>
@@ -13382,7 +13386,7 @@
       <c r="G660" s="3"/>
       <c r="H660" s="8"/>
     </row>
-    <row r="661" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A661" s="3"/>
       <c r="B661" s="8"/>
       <c r="C661" s="3"/>
@@ -13392,7 +13396,7 @@
       <c r="G661" s="3"/>
       <c r="H661" s="8"/>
     </row>
-    <row r="662" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A662" s="3"/>
       <c r="B662" s="8"/>
       <c r="C662" s="3"/>
@@ -13402,7 +13406,7 @@
       <c r="G662" s="3"/>
       <c r="H662" s="8"/>
     </row>
-    <row r="663" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A663" s="3"/>
       <c r="B663" s="8"/>
       <c r="C663" s="3"/>
@@ -13412,7 +13416,7 @@
       <c r="G663" s="3"/>
       <c r="H663" s="8"/>
     </row>
-    <row r="664" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A664" s="3"/>
       <c r="B664" s="8"/>
       <c r="C664" s="3"/>
@@ -13422,7 +13426,7 @@
       <c r="G664" s="3"/>
       <c r="H664" s="8"/>
     </row>
-    <row r="665" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A665" s="3"/>
       <c r="B665" s="8"/>
       <c r="C665" s="3"/>
@@ -13432,7 +13436,7 @@
       <c r="G665" s="3"/>
       <c r="H665" s="8"/>
     </row>
-    <row r="666" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A666" s="3"/>
       <c r="B666" s="8"/>
       <c r="C666" s="3"/>
@@ -13442,7 +13446,7 @@
       <c r="G666" s="3"/>
       <c r="H666" s="8"/>
     </row>
-    <row r="667" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A667" s="3"/>
       <c r="B667" s="8"/>
       <c r="C667" s="3"/>
@@ -13452,7 +13456,7 @@
       <c r="G667" s="3"/>
       <c r="H667" s="8"/>
     </row>
-    <row r="668" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A668" s="3"/>
       <c r="B668" s="8"/>
       <c r="C668" s="3"/>
@@ -13462,7 +13466,7 @@
       <c r="G668" s="3"/>
       <c r="H668" s="8"/>
     </row>
-    <row r="669" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A669" s="3"/>
       <c r="B669" s="8"/>
       <c r="C669" s="3"/>
@@ -13472,7 +13476,7 @@
       <c r="G669" s="3"/>
       <c r="H669" s="8"/>
     </row>
-    <row r="670" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A670" s="3"/>
       <c r="B670" s="8"/>
       <c r="C670" s="3"/>
@@ -13482,7 +13486,7 @@
       <c r="G670" s="3"/>
       <c r="H670" s="8"/>
     </row>
-    <row r="671" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A671" s="3"/>
       <c r="B671" s="8"/>
       <c r="C671" s="3"/>
@@ -13492,7 +13496,7 @@
       <c r="G671" s="3"/>
       <c r="H671" s="8"/>
     </row>
-    <row r="672" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A672" s="3"/>
       <c r="B672" s="8"/>
       <c r="C672" s="3"/>
@@ -13502,7 +13506,7 @@
       <c r="G672" s="3"/>
       <c r="H672" s="8"/>
     </row>
-    <row r="673" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A673" s="3"/>
       <c r="B673" s="8"/>
       <c r="C673" s="3"/>
@@ -13512,7 +13516,7 @@
       <c r="G673" s="3"/>
       <c r="H673" s="8"/>
     </row>
-    <row r="674" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A674" s="3"/>
       <c r="B674" s="8"/>
       <c r="C674" s="3"/>
@@ -13522,7 +13526,7 @@
       <c r="G674" s="3"/>
       <c r="H674" s="8"/>
     </row>
-    <row r="675" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A675" s="3"/>
       <c r="B675" s="8"/>
       <c r="C675" s="3"/>
@@ -13532,7 +13536,7 @@
       <c r="G675" s="3"/>
       <c r="H675" s="8"/>
     </row>
-    <row r="676" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A676" s="3"/>
       <c r="B676" s="8"/>
       <c r="C676" s="3"/>
@@ -13542,7 +13546,7 @@
       <c r="G676" s="3"/>
       <c r="H676" s="8"/>
     </row>
-    <row r="677" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A677" s="3"/>
       <c r="B677" s="8"/>
       <c r="C677" s="3"/>
@@ -13552,7 +13556,7 @@
       <c r="G677" s="3"/>
       <c r="H677" s="8"/>
     </row>
-    <row r="678" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A678" s="3"/>
       <c r="B678" s="8"/>
       <c r="C678" s="3"/>
@@ -13562,7 +13566,7 @@
       <c r="G678" s="3"/>
       <c r="H678" s="8"/>
     </row>
-    <row r="679" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A679" s="3"/>
       <c r="B679" s="8"/>
       <c r="C679" s="3"/>
@@ -13572,7 +13576,7 @@
       <c r="G679" s="3"/>
       <c r="H679" s="8"/>
     </row>
-    <row r="680" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A680" s="3"/>
       <c r="B680" s="8"/>
       <c r="C680" s="3"/>
@@ -13582,7 +13586,7 @@
       <c r="G680" s="3"/>
       <c r="H680" s="8"/>
     </row>
-    <row r="681" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A681" s="3"/>
       <c r="B681" s="8"/>
       <c r="C681" s="3"/>
@@ -13592,7 +13596,7 @@
       <c r="G681" s="3"/>
       <c r="H681" s="8"/>
     </row>
-    <row r="682" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A682" s="3"/>
       <c r="B682" s="8"/>
       <c r="C682" s="3"/>
@@ -13602,7 +13606,7 @@
       <c r="G682" s="3"/>
       <c r="H682" s="8"/>
     </row>
-    <row r="683" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A683" s="3"/>
       <c r="B683" s="8"/>
       <c r="C683" s="3"/>
@@ -13612,7 +13616,7 @@
       <c r="G683" s="3"/>
       <c r="H683" s="8"/>
     </row>
-    <row r="684" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A684" s="3"/>
       <c r="B684" s="8"/>
       <c r="C684" s="3"/>
@@ -13622,7 +13626,7 @@
       <c r="G684" s="3"/>
       <c r="H684" s="8"/>
     </row>
-    <row r="685" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A685" s="3"/>
       <c r="B685" s="8"/>
       <c r="C685" s="3"/>
@@ -13632,7 +13636,7 @@
       <c r="G685" s="3"/>
       <c r="H685" s="8"/>
     </row>
-    <row r="686" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A686" s="3"/>
       <c r="B686" s="8"/>
       <c r="C686" s="3"/>
@@ -13642,7 +13646,7 @@
       <c r="G686" s="3"/>
       <c r="H686" s="8"/>
     </row>
-    <row r="687" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A687" s="3"/>
       <c r="B687" s="8"/>
       <c r="C687" s="3"/>
@@ -13652,7 +13656,7 @@
       <c r="G687" s="3"/>
       <c r="H687" s="8"/>
     </row>
-    <row r="688" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A688" s="3"/>
       <c r="B688" s="8"/>
       <c r="C688" s="3"/>
@@ -13662,7 +13666,7 @@
       <c r="G688" s="3"/>
       <c r="H688" s="8"/>
     </row>
-    <row r="689" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A689" s="3"/>
       <c r="B689" s="8"/>
       <c r="C689" s="3"/>
@@ -13672,7 +13676,7 @@
       <c r="G689" s="3"/>
       <c r="H689" s="8"/>
     </row>
-    <row r="690" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A690" s="3"/>
       <c r="B690" s="8"/>
       <c r="C690" s="3"/>
@@ -13682,7 +13686,7 @@
       <c r="G690" s="3"/>
       <c r="H690" s="8"/>
     </row>
-    <row r="691" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A691" s="3"/>
       <c r="B691" s="8"/>
       <c r="C691" s="3"/>
@@ -13692,7 +13696,7 @@
       <c r="G691" s="3"/>
       <c r="H691" s="8"/>
     </row>
-    <row r="692" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A692" s="3"/>
       <c r="B692" s="8"/>
       <c r="C692" s="3"/>
@@ -13702,7 +13706,7 @@
       <c r="G692" s="3"/>
       <c r="H692" s="8"/>
     </row>
-    <row r="693" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A693" s="3"/>
       <c r="B693" s="8"/>
       <c r="C693" s="3"/>
@@ -13714,11 +13718,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="J310:J312"/>
-    <mergeCell ref="J59:J61"/>
-    <mergeCell ref="J316:J318"/>
-    <mergeCell ref="J40:J42"/>
-    <mergeCell ref="J28:J30"/>
     <mergeCell ref="J10:J12"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
@@ -13726,6 +13725,11 @@
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="J4:J6"/>
     <mergeCell ref="J2:J3"/>
+    <mergeCell ref="J310:J312"/>
+    <mergeCell ref="J59:J61"/>
+    <mergeCell ref="J316:J318"/>
+    <mergeCell ref="J40:J42"/>
+    <mergeCell ref="J28:J30"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
